--- a/Отчет_20-05-2025.xlsx
+++ b/Отчет_20-05-2025.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Лист1'!$A$1:$AK$26</definedName>
@@ -756,10 +756,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -771,19 +780,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -811,7 +811,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -912,12 +912,192 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -930,228 +1110,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1161,18 +1131,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1181,29 +1142,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -1547,26 +1493,26 @@
   </cols>
   <sheetData>
     <row r="1" ht="37.5" customHeight="1">
-      <c r="A1" s="103" t="inlineStr">
+      <c r="A1" s="85" t="inlineStr">
         <is>
           <t>ОТЧЕТ по сдаче продукции в литейном цехе</t>
         </is>
       </c>
-      <c r="AL1" s="103" t="n"/>
+      <c r="AL1" s="85" t="n"/>
     </row>
     <row r="2" ht="73.5" customHeight="1">
-      <c r="A2" s="127" t="inlineStr">
-        <is>
-          <t>20.05.2025</t>
-        </is>
-      </c>
-      <c r="L2" s="96" t="inlineStr">
-        <is>
-          <t>Контролеры:</t>
+      <c r="A2" s="63" t="inlineStr">
+        <is>
+          <t>Дата:  20.05.2025  2025 г.</t>
+        </is>
+      </c>
+      <c r="L2" s="95" t="inlineStr">
+        <is>
+          <t>Контролеры: Иванова</t>
         </is>
       </c>
       <c r="Q2" s="5" t="n"/>
-      <c r="R2" s="126" t="inlineStr">
+      <c r="R2" s="62" t="inlineStr">
         <is>
           <t>,</t>
         </is>
@@ -1602,7 +1548,7 @@
           <t>ОТЛИТО, шт.</t>
         </is>
       </c>
-      <c r="C4" s="97" t="inlineStr">
+      <c r="C4" s="86" t="inlineStr">
         <is>
           <t>БРАК НА ОПЕРАЦИЯХ, шт.</t>
         </is>
@@ -1627,7 +1573,7 @@
       </c>
       <c r="R4" s="132" t="n"/>
       <c r="S4" s="133" t="n"/>
-      <c r="T4" s="97" t="inlineStr">
+      <c r="T4" s="86" t="inlineStr">
         <is>
           <t>ДОРАБОТКА, шт.</t>
         </is>
@@ -1654,164 +1600,164 @@
     <row r="5" ht="114.75" customFormat="1" customHeight="1" s="9">
       <c r="A5" s="134" t="n"/>
       <c r="B5" s="134" t="n"/>
-      <c r="C5" s="97" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>недолив</t>
         </is>
       </c>
-      <c r="D5" s="135" t="inlineStr">
+      <c r="D5" s="41" t="inlineStr">
         <is>
           <t>раковины на корпусе</t>
         </is>
       </c>
-      <c r="E5" s="135" t="inlineStr">
+      <c r="E5" s="41" t="inlineStr">
         <is>
           <t>наруш. геом.</t>
         </is>
       </c>
-      <c r="F5" s="98" t="inlineStr">
+      <c r="F5" s="41" t="inlineStr">
         <is>
           <t>брак п/м</t>
         </is>
       </c>
-      <c r="G5" s="135" t="inlineStr">
+      <c r="G5" s="41" t="inlineStr">
         <is>
           <t>пригар песка</t>
         </is>
       </c>
-      <c r="H5" s="135" t="inlineStr">
+      <c r="H5" s="41" t="inlineStr">
         <is>
           <t>наплыв металла</t>
         </is>
       </c>
-      <c r="I5" s="98" t="inlineStr">
+      <c r="I5" s="41" t="inlineStr">
         <is>
           <t>вырыв</t>
         </is>
       </c>
-      <c r="J5" s="98" t="inlineStr">
+      <c r="J5" s="41" t="inlineStr">
         <is>
           <t>слом</t>
         </is>
       </c>
-      <c r="K5" s="98" t="inlineStr">
+      <c r="K5" s="41" t="inlineStr">
         <is>
           <t>зарез</t>
         </is>
       </c>
-      <c r="L5" s="135" t="inlineStr">
+      <c r="L5" s="41" t="inlineStr">
         <is>
           <t>несоотв. 
 внеш. вида</t>
         </is>
       </c>
-      <c r="M5" s="98" t="inlineStr">
+      <c r="M5" s="41" t="inlineStr">
         <is>
           <t>трещины</t>
         </is>
       </c>
-      <c r="N5" s="98" t="inlineStr">
+      <c r="N5" s="41" t="inlineStr">
         <is>
           <t>скол</t>
         </is>
       </c>
-      <c r="O5" s="135" t="inlineStr">
+      <c r="O5" s="41" t="inlineStr">
         <is>
           <t>нарушение маркировки</t>
         </is>
       </c>
-      <c r="P5" s="136" t="inlineStr">
+      <c r="P5" s="42" t="inlineStr">
         <is>
           <t>технол. брак (ЛПД)</t>
         </is>
       </c>
-      <c r="Q5" s="137" t="n"/>
-      <c r="S5" s="138" t="n"/>
-      <c r="T5" s="139" t="inlineStr">
+      <c r="Q5" s="135" t="n"/>
+      <c r="S5" s="136" t="n"/>
+      <c r="T5" s="90" t="inlineStr">
         <is>
           <t>Раковины</t>
         </is>
       </c>
-      <c r="U5" s="140" t="inlineStr">
+      <c r="U5" s="67" t="inlineStr">
         <is>
           <t>Зарез</t>
         </is>
       </c>
-      <c r="V5" s="141" t="inlineStr">
+      <c r="V5" s="67" t="inlineStr">
         <is>
           <t>Несоотв. размеров</t>
         </is>
       </c>
-      <c r="W5" s="141" t="inlineStr">
+      <c r="W5" s="67" t="inlineStr">
         <is>
           <t>Несоотв. 
 внеш. вида</t>
         </is>
       </c>
-      <c r="X5" s="141" t="inlineStr">
+      <c r="X5" s="67" t="inlineStr">
         <is>
           <t>Наплыв мет. 
 на пов-ти</t>
         </is>
       </c>
-      <c r="Y5" s="142" t="inlineStr">
+      <c r="Y5" s="80" t="inlineStr">
         <is>
           <t>Прорыв мет. в резьбе (вороток)</t>
         </is>
       </c>
-      <c r="Z5" s="143" t="inlineStr">
+      <c r="Z5" s="80" t="inlineStr">
         <is>
           <t>Вырыв</t>
         </is>
       </c>
-      <c r="AA5" s="140" t="inlineStr">
+      <c r="AA5" s="67" t="inlineStr">
         <is>
           <t>Облой</t>
         </is>
       </c>
-      <c r="AB5" s="141" t="inlineStr">
+      <c r="AB5" s="67" t="inlineStr">
         <is>
           <t>Песок на 
 пов-ти</t>
         </is>
       </c>
-      <c r="AC5" s="144" t="inlineStr">
+      <c r="AC5" s="82" t="inlineStr">
         <is>
           <t>Песок в резьбе (вороток)</t>
         </is>
       </c>
-      <c r="AD5" s="143" t="inlineStr">
+      <c r="AD5" s="80" t="inlineStr">
         <is>
           <t>Клей</t>
         </is>
       </c>
-      <c r="AE5" s="145" t="n"/>
-      <c r="AF5" s="146" t="inlineStr">
+      <c r="AE5" s="137" t="n"/>
+      <c r="AF5" s="84" t="inlineStr">
         <is>
           <t>Коробление</t>
         </is>
       </c>
-      <c r="AG5" s="141" t="inlineStr">
+      <c r="AG5" s="67" t="inlineStr">
         <is>
           <t>Дефект п/м (покрытие)</t>
         </is>
       </c>
-      <c r="AH5" s="140" t="inlineStr">
+      <c r="AH5" s="67" t="inlineStr">
         <is>
           <t>Лапы</t>
         </is>
       </c>
-      <c r="AI5" s="140" t="inlineStr">
+      <c r="AI5" s="67" t="inlineStr">
         <is>
           <t>Питатель</t>
         </is>
       </c>
-      <c r="AJ5" s="140" t="inlineStr">
+      <c r="AJ5" s="67" t="inlineStr">
         <is>
           <t>Коронв</t>
         </is>
       </c>
-      <c r="AK5" s="147" t="inlineStr">
+      <c r="AK5" s="70" t="inlineStr">
         <is>
           <t>Смещение</t>
         </is>
@@ -1819,60 +1765,60 @@
       <c r="AL5" s="8" t="n"/>
     </row>
     <row r="6" ht="31.5" customFormat="1" customHeight="1" s="9" thickBot="1">
-      <c r="A6" s="148" t="n"/>
-      <c r="B6" s="148" t="n"/>
-      <c r="C6" s="149" t="n"/>
-      <c r="D6" s="150" t="n"/>
-      <c r="E6" s="150" t="n"/>
-      <c r="F6" s="150" t="n"/>
-      <c r="G6" s="150" t="n"/>
-      <c r="H6" s="150" t="n"/>
-      <c r="I6" s="150" t="n"/>
-      <c r="J6" s="150" t="n"/>
-      <c r="K6" s="150" t="n"/>
-      <c r="L6" s="150" t="n"/>
-      <c r="M6" s="150" t="n"/>
-      <c r="N6" s="150" t="n"/>
-      <c r="O6" s="150" t="n"/>
-      <c r="P6" s="151" t="n"/>
-      <c r="Q6" s="152" t="n"/>
-      <c r="R6" s="153" t="n"/>
-      <c r="S6" s="154" t="n"/>
-      <c r="T6" s="149" t="n"/>
-      <c r="U6" s="150" t="n"/>
-      <c r="V6" s="150" t="n"/>
-      <c r="W6" s="150" t="n"/>
-      <c r="X6" s="150" t="n"/>
-      <c r="Y6" s="155" t="n"/>
-      <c r="Z6" s="155" t="n"/>
-      <c r="AA6" s="150" t="n"/>
-      <c r="AB6" s="150" t="n"/>
-      <c r="AC6" s="156" t="n"/>
-      <c r="AD6" s="157" t="inlineStr">
+      <c r="A6" s="138" t="n"/>
+      <c r="B6" s="138" t="n"/>
+      <c r="C6" s="139" t="n"/>
+      <c r="D6" s="140" t="n"/>
+      <c r="E6" s="140" t="n"/>
+      <c r="F6" s="140" t="n"/>
+      <c r="G6" s="140" t="n"/>
+      <c r="H6" s="140" t="n"/>
+      <c r="I6" s="140" t="n"/>
+      <c r="J6" s="140" t="n"/>
+      <c r="K6" s="140" t="n"/>
+      <c r="L6" s="140" t="n"/>
+      <c r="M6" s="140" t="n"/>
+      <c r="N6" s="140" t="n"/>
+      <c r="O6" s="140" t="n"/>
+      <c r="P6" s="141" t="n"/>
+      <c r="Q6" s="142" t="n"/>
+      <c r="R6" s="143" t="n"/>
+      <c r="S6" s="144" t="n"/>
+      <c r="T6" s="139" t="n"/>
+      <c r="U6" s="140" t="n"/>
+      <c r="V6" s="140" t="n"/>
+      <c r="W6" s="140" t="n"/>
+      <c r="X6" s="140" t="n"/>
+      <c r="Y6" s="145" t="n"/>
+      <c r="Z6" s="145" t="n"/>
+      <c r="AA6" s="140" t="n"/>
+      <c r="AB6" s="140" t="n"/>
+      <c r="AC6" s="146" t="n"/>
+      <c r="AD6" s="54" t="inlineStr">
         <is>
           <t>П</t>
         </is>
       </c>
-      <c r="AE6" s="157" t="inlineStr">
+      <c r="AE6" s="54" t="inlineStr">
         <is>
           <t>Ш</t>
         </is>
       </c>
-      <c r="AF6" s="158" t="n"/>
-      <c r="AG6" s="150" t="n"/>
-      <c r="AH6" s="150" t="n"/>
-      <c r="AI6" s="150" t="n"/>
-      <c r="AJ6" s="150" t="n"/>
-      <c r="AK6" s="151" t="n"/>
+      <c r="AF6" s="147" t="n"/>
+      <c r="AG6" s="140" t="n"/>
+      <c r="AH6" s="140" t="n"/>
+      <c r="AI6" s="140" t="n"/>
+      <c r="AJ6" s="140" t="n"/>
+      <c r="AK6" s="141" t="n"/>
       <c r="AL6" s="8" t="n"/>
     </row>
-    <row r="7" ht="104.25" customHeight="1">
-      <c r="A7" s="159" t="inlineStr">
+    <row r="7" hidden="1" ht="104.25" customHeight="1">
+      <c r="A7" s="53" t="inlineStr">
         <is>
           <t>Наименование_отливки</t>
         </is>
       </c>
-      <c r="B7" s="160" t="inlineStr">
+      <c r="B7" s="55" t="inlineStr">
         <is>
           <t>Контроль_отлито</t>
         </is>
@@ -1890,100 +1836,100 @@
       <c r="M7" s="50" t="n"/>
       <c r="N7" s="50" t="n"/>
       <c r="O7" s="50" t="n"/>
-      <c r="P7" s="86" t="n"/>
-      <c r="Q7" s="161" t="inlineStr">
+      <c r="P7" s="102" t="n"/>
+      <c r="Q7" s="148" t="inlineStr">
         <is>
           <t>Контроль_отлито</t>
         </is>
       </c>
       <c r="R7" s="128" t="n"/>
-      <c r="S7" s="145" t="n"/>
-      <c r="T7" s="160" t="inlineStr">
+      <c r="S7" s="137" t="n"/>
+      <c r="T7" s="55" t="inlineStr">
         <is>
           <t>Доработка_раковины</t>
         </is>
       </c>
-      <c r="U7" s="160" t="inlineStr">
+      <c r="U7" s="55" t="inlineStr">
         <is>
           <t>Доработка_зарез</t>
         </is>
       </c>
-      <c r="V7" s="160" t="inlineStr">
+      <c r="V7" s="55" t="inlineStr">
         <is>
           <t>Доработка_несоответствие_размеров</t>
         </is>
       </c>
-      <c r="W7" s="160" t="inlineStr">
+      <c r="W7" s="55" t="inlineStr">
         <is>
           <t>Доработка_несоответствие_внешнего_вида</t>
         </is>
       </c>
-      <c r="X7" s="160" t="inlineStr">
+      <c r="X7" s="55" t="inlineStr">
         <is>
           <t>Доработка_наплыв_металла</t>
         </is>
       </c>
-      <c r="Y7" s="160" t="inlineStr">
+      <c r="Y7" s="55" t="inlineStr">
         <is>
           <t>Доработка_прорыв_металла</t>
         </is>
       </c>
-      <c r="Z7" s="160" t="inlineStr">
+      <c r="Z7" s="55" t="inlineStr">
         <is>
           <t>Доработка_вырыв</t>
         </is>
       </c>
-      <c r="AA7" s="160" t="inlineStr">
+      <c r="AA7" s="55" t="inlineStr">
         <is>
           <t>Доработка_облой</t>
         </is>
       </c>
-      <c r="AB7" s="160" t="inlineStr">
+      <c r="AB7" s="55" t="inlineStr">
         <is>
           <t>Доработка_песок_на_поверхности</t>
         </is>
       </c>
-      <c r="AC7" s="160" t="inlineStr">
+      <c r="AC7" s="55" t="inlineStr">
         <is>
           <t>Доработка_песок_в_резьбе</t>
         </is>
       </c>
-      <c r="AD7" s="160" t="inlineStr">
+      <c r="AD7" s="55" t="inlineStr">
         <is>
           <t>Доработка_клей_подтёк</t>
         </is>
       </c>
-      <c r="AE7" s="160" t="inlineStr">
+      <c r="AE7" s="55" t="inlineStr">
         <is>
           <t>Доработка_клей_по_шву</t>
         </is>
       </c>
-      <c r="AF7" s="160" t="inlineStr">
+      <c r="AF7" s="55" t="inlineStr">
         <is>
           <t>Доработка_коробление</t>
         </is>
       </c>
-      <c r="AG7" s="160" t="inlineStr">
+      <c r="AG7" s="55" t="inlineStr">
         <is>
           <t>Доработка_дефект_пеномодели</t>
         </is>
       </c>
-      <c r="AH7" s="160" t="inlineStr">
+      <c r="AH7" s="55" t="inlineStr">
         <is>
           <t>Доработка_лапы</t>
         </is>
       </c>
-      <c r="AI7" s="160" t="inlineStr">
+      <c r="AI7" s="55" t="inlineStr">
         <is>
           <t>Доработка_питатель</t>
         </is>
       </c>
-      <c r="AJ7" s="160" t="inlineStr">
+      <c r="AJ7" s="55" t="inlineStr">
         <is>
           <t>Доработка_корона</t>
         </is>
       </c>
-      <c r="AK7" s="160" t="inlineStr">
+      <c r="AK7" s="55" t="inlineStr">
         <is>
           <t>Доработка_смещение</t>
         </is>
@@ -1991,7 +1937,11 @@
       <c r="AL7" s="17" t="n"/>
     </row>
     <row r="8" ht="104.25" customHeight="1">
-      <c r="A8" s="10" t="n"/>
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Вороток</t>
+        </is>
+      </c>
       <c r="B8" s="10" t="n"/>
       <c r="C8" s="16" t="n"/>
       <c r="D8" s="16" t="n"/>
@@ -2006,32 +1956,74 @@
       <c r="M8" s="16" t="n"/>
       <c r="N8" s="16" t="n"/>
       <c r="O8" s="16" t="n"/>
-      <c r="P8" s="89" t="n"/>
-      <c r="Q8" s="95" t="n"/>
-      <c r="R8" s="162" t="n"/>
-      <c r="S8" s="163" t="n"/>
-      <c r="T8" s="31" t="n"/>
-      <c r="U8" s="31" t="n"/>
-      <c r="V8" s="31" t="n"/>
-      <c r="W8" s="31" t="n"/>
-      <c r="X8" s="31" t="n"/>
-      <c r="Y8" s="31" t="n"/>
-      <c r="Z8" s="31" t="n"/>
-      <c r="AA8" s="31" t="n"/>
-      <c r="AB8" s="31" t="n"/>
-      <c r="AC8" s="31" t="n"/>
-      <c r="AD8" s="55" t="n"/>
-      <c r="AE8" s="31" t="n"/>
-      <c r="AF8" s="31" t="n"/>
-      <c r="AG8" s="31" t="n"/>
-      <c r="AH8" s="31" t="n"/>
-      <c r="AI8" s="31" t="n"/>
-      <c r="AJ8" s="31" t="n"/>
-      <c r="AK8" s="16" t="n"/>
+      <c r="P8" s="105" t="n"/>
+      <c r="Q8" s="111" t="n">
+        <v>666</v>
+      </c>
+      <c r="R8" s="149" t="n"/>
+      <c r="S8" s="150" t="n"/>
+      <c r="T8" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="W8" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z8" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA8" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB8" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC8" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE8" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF8" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI8" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ8" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK8" s="16" t="n">
+        <v>2</v>
+      </c>
       <c r="AL8" s="17" t="n"/>
     </row>
     <row r="9" ht="104.25" customHeight="1">
-      <c r="A9" s="10" t="n"/>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Ригель</t>
+        </is>
+      </c>
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="16" t="n"/>
       <c r="D9" s="16" t="n"/>
@@ -2046,32 +2038,74 @@
       <c r="M9" s="16" t="n"/>
       <c r="N9" s="16" t="n"/>
       <c r="O9" s="16" t="n"/>
-      <c r="P9" s="89" t="n"/>
-      <c r="Q9" s="95" t="n"/>
-      <c r="R9" s="162" t="n"/>
-      <c r="S9" s="163" t="n"/>
-      <c r="T9" s="16" t="n"/>
-      <c r="U9" s="16" t="n"/>
-      <c r="V9" s="16" t="n"/>
-      <c r="W9" s="16" t="n"/>
-      <c r="X9" s="16" t="n"/>
-      <c r="Y9" s="16" t="n"/>
-      <c r="Z9" s="16" t="n"/>
-      <c r="AA9" s="16" t="n"/>
-      <c r="AB9" s="16" t="n"/>
-      <c r="AC9" s="16" t="n"/>
-      <c r="AD9" s="16" t="n"/>
-      <c r="AE9" s="16" t="n"/>
-      <c r="AF9" s="16" t="n"/>
-      <c r="AG9" s="14" t="n"/>
-      <c r="AH9" s="16" t="n"/>
-      <c r="AI9" s="16" t="n"/>
-      <c r="AJ9" s="91" t="n"/>
-      <c r="AK9" s="16" t="n"/>
+      <c r="P9" s="105" t="n"/>
+      <c r="Q9" s="111" t="n">
+        <v>3000</v>
+      </c>
+      <c r="R9" s="149" t="n"/>
+      <c r="S9" s="150" t="n"/>
+      <c r="T9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="W9" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="X9" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y9" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z9" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA9" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="AB9" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC9" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="AD9" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE9" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="AF9" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG9" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="AH9" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI9" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="AJ9" s="107" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK9" s="16" t="n">
+        <v>43</v>
+      </c>
       <c r="AL9" s="17" t="n"/>
     </row>
     <row r="10" ht="104.25" customHeight="1">
-      <c r="A10" s="10" t="n"/>
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Ригель optima</t>
+        </is>
+      </c>
       <c r="B10" s="10" t="n"/>
       <c r="C10" s="16" t="n"/>
       <c r="D10" s="16" t="n"/>
@@ -2086,28 +2120,66 @@
       <c r="M10" s="16" t="n"/>
       <c r="N10" s="16" t="n"/>
       <c r="O10" s="16" t="n"/>
-      <c r="P10" s="89" t="n"/>
-      <c r="Q10" s="95" t="n"/>
-      <c r="R10" s="162" t="n"/>
-      <c r="S10" s="163" t="n"/>
-      <c r="T10" s="16" t="n"/>
-      <c r="U10" s="16" t="n"/>
-      <c r="V10" s="16" t="n"/>
-      <c r="W10" s="16" t="n"/>
-      <c r="X10" s="16" t="n"/>
-      <c r="Y10" s="16" t="n"/>
-      <c r="Z10" s="16" t="n"/>
-      <c r="AA10" s="16" t="n"/>
-      <c r="AB10" s="16" t="n"/>
-      <c r="AC10" s="16" t="n"/>
-      <c r="AD10" s="16" t="n"/>
-      <c r="AE10" s="16" t="n"/>
-      <c r="AF10" s="16" t="n"/>
-      <c r="AG10" s="14" t="n"/>
-      <c r="AH10" s="16" t="n"/>
-      <c r="AI10" s="16" t="n"/>
-      <c r="AJ10" s="91" t="n"/>
-      <c r="AK10" s="16" t="n"/>
+      <c r="P10" s="105" t="n"/>
+      <c r="Q10" s="111" t="n">
+        <v>1999</v>
+      </c>
+      <c r="R10" s="149" t="n"/>
+      <c r="S10" s="150" t="n"/>
+      <c r="T10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="W10" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="X10" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z10" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA10" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB10" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC10" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD10" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE10" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF10" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG10" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH10" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI10" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ10" s="107" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK10" s="16" t="n">
+        <v>4</v>
+      </c>
       <c r="AL10" s="17" t="n"/>
     </row>
     <row r="11" ht="104.25" customHeight="1">
@@ -2126,10 +2198,10 @@
       <c r="M11" s="19" t="n"/>
       <c r="N11" s="19" t="n"/>
       <c r="O11" s="19" t="n"/>
-      <c r="P11" s="89" t="n"/>
-      <c r="Q11" s="164" t="n"/>
-      <c r="R11" s="165" t="n"/>
-      <c r="S11" s="166" t="n"/>
+      <c r="P11" s="105" t="n"/>
+      <c r="Q11" s="151" t="n"/>
+      <c r="R11" s="152" t="n"/>
+      <c r="S11" s="153" t="n"/>
       <c r="T11" s="19" t="n"/>
       <c r="U11" s="19" t="n"/>
       <c r="V11" s="19" t="n"/>
@@ -2146,7 +2218,7 @@
       <c r="AG11" s="20" t="n"/>
       <c r="AH11" s="16" t="n"/>
       <c r="AI11" s="16" t="n"/>
-      <c r="AJ11" s="91" t="n"/>
+      <c r="AJ11" s="107" t="n"/>
       <c r="AK11" s="16" t="n"/>
       <c r="AL11" s="17" t="n"/>
     </row>
@@ -2166,10 +2238,10 @@
       <c r="M12" s="16" t="n"/>
       <c r="N12" s="16" t="n"/>
       <c r="O12" s="16" t="n"/>
-      <c r="P12" s="89" t="n"/>
-      <c r="Q12" s="95" t="n"/>
-      <c r="R12" s="162" t="n"/>
-      <c r="S12" s="163" t="n"/>
+      <c r="P12" s="105" t="n"/>
+      <c r="Q12" s="111" t="n"/>
+      <c r="R12" s="149" t="n"/>
+      <c r="S12" s="150" t="n"/>
       <c r="T12" s="16" t="n"/>
       <c r="U12" s="16" t="n"/>
       <c r="V12" s="16" t="n"/>
@@ -2186,7 +2258,7 @@
       <c r="AG12" s="14" t="n"/>
       <c r="AH12" s="16" t="n"/>
       <c r="AI12" s="16" t="n"/>
-      <c r="AJ12" s="91" t="n"/>
+      <c r="AJ12" s="107" t="n"/>
       <c r="AK12" s="16" t="n"/>
       <c r="AL12" s="17" t="n"/>
     </row>
@@ -2206,10 +2278,10 @@
       <c r="M13" s="19" t="n"/>
       <c r="N13" s="19" t="n"/>
       <c r="O13" s="19" t="n"/>
-      <c r="P13" s="89" t="n"/>
-      <c r="Q13" s="164" t="n"/>
-      <c r="R13" s="165" t="n"/>
-      <c r="S13" s="166" t="n"/>
+      <c r="P13" s="105" t="n"/>
+      <c r="Q13" s="151" t="n"/>
+      <c r="R13" s="152" t="n"/>
+      <c r="S13" s="153" t="n"/>
       <c r="T13" s="19" t="n"/>
       <c r="U13" s="19" t="n"/>
       <c r="V13" s="19" t="n"/>
@@ -2226,7 +2298,7 @@
       <c r="AG13" s="20" t="n"/>
       <c r="AH13" s="16" t="n"/>
       <c r="AI13" s="16" t="n"/>
-      <c r="AJ13" s="91" t="n"/>
+      <c r="AJ13" s="107" t="n"/>
       <c r="AK13" s="16" t="n"/>
       <c r="AL13" s="17" t="n"/>
     </row>
@@ -2246,10 +2318,10 @@
       <c r="M14" s="16" t="n"/>
       <c r="N14" s="16" t="n"/>
       <c r="O14" s="16" t="n"/>
-      <c r="P14" s="89" t="n"/>
-      <c r="Q14" s="95" t="n"/>
-      <c r="R14" s="162" t="n"/>
-      <c r="S14" s="163" t="n"/>
+      <c r="P14" s="105" t="n"/>
+      <c r="Q14" s="111" t="n"/>
+      <c r="R14" s="149" t="n"/>
+      <c r="S14" s="150" t="n"/>
       <c r="T14" s="16" t="n"/>
       <c r="U14" s="16" t="n"/>
       <c r="V14" s="16" t="n"/>
@@ -2266,13 +2338,13 @@
       <c r="AG14" s="14" t="n"/>
       <c r="AH14" s="16" t="n"/>
       <c r="AI14" s="16" t="n"/>
-      <c r="AJ14" s="91" t="n"/>
+      <c r="AJ14" s="107" t="n"/>
       <c r="AK14" s="16" t="n"/>
       <c r="AL14" s="17" t="n"/>
     </row>
     <row r="15" ht="73.5" customHeight="1" thickBot="1">
       <c r="A15" s="4" t="n"/>
-      <c r="L15" s="96" t="n"/>
+      <c r="L15" s="95" t="n"/>
       <c r="Q15" s="5" t="n"/>
       <c r="R15" s="5" t="n"/>
       <c r="S15" s="28" t="n"/>
@@ -2295,17 +2367,17 @@
       <c r="AJ15" s="5" t="n"/>
     </row>
     <row r="16" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A16" s="167" t="inlineStr">
+      <c r="A16" s="98" t="inlineStr">
         <is>
           <t>НОМЕР И НАИМЕНОВАНИЕ ОТЛИВКИ</t>
         </is>
       </c>
-      <c r="B16" s="168" t="inlineStr">
+      <c r="B16" s="100" t="inlineStr">
         <is>
           <t>ГОДНЫЕ, шт.</t>
         </is>
       </c>
-      <c r="C16" s="169" t="inlineStr">
+      <c r="C16" s="112" t="inlineStr">
         <is>
           <t>ОКОНЧАТЕЛЬНЫЙ БРАК, шт.</t>
         </is>
@@ -2331,22 +2403,22 @@
       <c r="V16" s="130" t="n"/>
       <c r="W16" s="130" t="n"/>
       <c r="X16" s="131" t="n"/>
-      <c r="Y16" s="170" t="inlineStr">
+      <c r="Y16" s="154" t="inlineStr">
         <is>
           <t>2 СОРТ, шт.</t>
         </is>
       </c>
       <c r="Z16" s="130" t="n"/>
       <c r="AA16" s="130" t="n"/>
-      <c r="AB16" s="171" t="n"/>
-      <c r="AC16" s="172" t="inlineStr">
+      <c r="AB16" s="155" t="n"/>
+      <c r="AC16" s="156" t="inlineStr">
         <is>
           <t>НЕДОСТАЧА, 
 шт.</t>
         </is>
       </c>
       <c r="AD16" s="133" t="n"/>
-      <c r="AE16" s="172" t="inlineStr">
+      <c r="AE16" s="156" t="inlineStr">
         <is>
           <t>НОМЕРА ПЛАВОК</t>
         </is>
@@ -2359,153 +2431,153 @@
       <c r="AK16" s="133" t="n"/>
     </row>
     <row r="17" ht="135.75" customHeight="1" thickBot="1">
-      <c r="A17" s="173" t="n"/>
-      <c r="B17" s="173" t="n"/>
-      <c r="C17" s="174" t="inlineStr">
+      <c r="A17" s="157" t="n"/>
+      <c r="B17" s="157" t="n"/>
+      <c r="C17" s="40" t="inlineStr">
         <is>
           <t>Раковины на корпусе</t>
         </is>
       </c>
-      <c r="D17" s="98" t="inlineStr">
+      <c r="D17" s="41" t="inlineStr">
         <is>
           <t>Коробление</t>
         </is>
       </c>
-      <c r="E17" s="98" t="inlineStr">
+      <c r="E17" s="41" t="inlineStr">
         <is>
           <t>Спай</t>
         </is>
       </c>
-      <c r="F17" s="98" t="inlineStr">
+      <c r="F17" s="41" t="inlineStr">
         <is>
           <t>Трещины</t>
         </is>
       </c>
-      <c r="G17" s="98" t="inlineStr">
+      <c r="G17" s="41" t="inlineStr">
         <is>
           <t>Недолив</t>
         </is>
       </c>
-      <c r="H17" s="135" t="inlineStr">
+      <c r="H17" s="41" t="inlineStr">
         <is>
           <t>Пригар песка</t>
         </is>
       </c>
-      <c r="I17" s="98" t="inlineStr">
+      <c r="I17" s="41" t="inlineStr">
         <is>
           <t>Пористость</t>
         </is>
       </c>
-      <c r="J17" s="98" t="inlineStr">
+      <c r="J17" s="41" t="inlineStr">
         <is>
           <t>Вырыв</t>
         </is>
       </c>
-      <c r="K17" s="98" t="inlineStr">
+      <c r="K17" s="41" t="inlineStr">
         <is>
           <t>Скол</t>
         </is>
       </c>
-      <c r="L17" s="98" t="inlineStr">
+      <c r="L17" s="41" t="inlineStr">
         <is>
           <t>Слом</t>
         </is>
       </c>
-      <c r="M17" s="135" t="inlineStr">
+      <c r="M17" s="41" t="inlineStr">
         <is>
           <t>Зарез литейный</t>
         </is>
       </c>
-      <c r="N17" s="135" t="inlineStr">
+      <c r="N17" s="41" t="inlineStr">
         <is>
           <t>Зарез пеномодельный</t>
         </is>
       </c>
-      <c r="O17" s="135" t="inlineStr">
+      <c r="O17" s="41" t="inlineStr">
         <is>
           <t>Нарушение геометрии</t>
         </is>
       </c>
-      <c r="P17" s="98" t="inlineStr">
+      <c r="P17" s="41" t="inlineStr">
         <is>
           <t>Рыхлота</t>
         </is>
       </c>
-      <c r="Q17" s="98" t="inlineStr">
+      <c r="Q17" s="41" t="inlineStr">
         <is>
           <t>Непрклей</t>
         </is>
       </c>
-      <c r="R17" s="98" t="inlineStr">
+      <c r="R17" s="41" t="inlineStr">
         <is>
           <t>Брак п/м</t>
         </is>
       </c>
-      <c r="S17" s="135" t="inlineStr">
+      <c r="S17" s="41" t="inlineStr">
         <is>
           <t>Наплыв металла</t>
         </is>
       </c>
-      <c r="T17" s="135" t="inlineStr">
+      <c r="T17" s="41" t="inlineStr">
         <is>
           <t>Несоответствие размеров</t>
         </is>
       </c>
-      <c r="U17" s="135" t="inlineStr">
+      <c r="U17" s="41" t="inlineStr">
         <is>
           <t>Несоответствие внешнего вида</t>
         </is>
       </c>
-      <c r="V17" s="135" t="inlineStr">
+      <c r="V17" s="41" t="inlineStr">
         <is>
           <t>Нарушение маркировки</t>
         </is>
       </c>
-      <c r="W17" s="98" t="inlineStr">
+      <c r="W17" s="41" t="inlineStr">
         <is>
           <t>Неслитина</t>
         </is>
       </c>
-      <c r="X17" s="175" t="inlineStr">
+      <c r="X17" s="56" t="inlineStr">
         <is>
           <t>Прочее</t>
         </is>
       </c>
-      <c r="Y17" s="97" t="inlineStr">
+      <c r="Y17" s="40" t="inlineStr">
         <is>
           <t>Раковины</t>
         </is>
       </c>
-      <c r="Z17" s="135" t="inlineStr">
+      <c r="Z17" s="41" t="inlineStr">
         <is>
           <t>Зарез литейный</t>
         </is>
       </c>
-      <c r="AA17" s="135" t="inlineStr">
+      <c r="AA17" s="41" t="inlineStr">
         <is>
           <t>Зарез пеномодельный</t>
         </is>
       </c>
-      <c r="AB17" s="99" t="inlineStr">
+      <c r="AB17" s="42" t="inlineStr">
         <is>
           <t>Прочее</t>
         </is>
       </c>
-      <c r="AC17" s="152" t="n"/>
-      <c r="AD17" s="154" t="n"/>
-      <c r="AE17" s="152" t="n"/>
-      <c r="AF17" s="153" t="n"/>
-      <c r="AG17" s="153" t="n"/>
-      <c r="AH17" s="153" t="n"/>
-      <c r="AI17" s="153" t="n"/>
-      <c r="AJ17" s="153" t="n"/>
-      <c r="AK17" s="154" t="n"/>
+      <c r="AC17" s="142" t="n"/>
+      <c r="AD17" s="144" t="n"/>
+      <c r="AE17" s="142" t="n"/>
+      <c r="AF17" s="143" t="n"/>
+      <c r="AG17" s="143" t="n"/>
+      <c r="AH17" s="143" t="n"/>
+      <c r="AI17" s="143" t="n"/>
+      <c r="AJ17" s="143" t="n"/>
+      <c r="AK17" s="144" t="n"/>
       <c r="AL17" s="22" t="n"/>
       <c r="AM17" s="23" t="n"/>
       <c r="AN17" s="5" t="n"/>
       <c r="BK17" s="28" t="n"/>
     </row>
-    <row r="18" ht="99" customHeight="1">
+    <row r="18" hidden="1" ht="99" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
           <t>Наименование_отливки</t>
@@ -2642,9 +2714,9 @@
         </is>
       </c>
       <c r="AB18" s="39" t="n"/>
-      <c r="AC18" s="66" t="n"/>
-      <c r="AD18" s="145" t="n"/>
-      <c r="AE18" s="176" t="inlineStr">
+      <c r="AC18" s="126" t="n"/>
+      <c r="AD18" s="137" t="n"/>
+      <c r="AE18" s="158" t="inlineStr">
         <is>
           <t>Номер_плавки</t>
         </is>
@@ -2654,136 +2726,316 @@
       <c r="AH18" s="128" t="n"/>
       <c r="AI18" s="128" t="n"/>
       <c r="AJ18" s="128" t="n"/>
-      <c r="AK18" s="145" t="n"/>
+      <c r="AK18" s="137" t="n"/>
       <c r="AL18" s="27" t="n"/>
       <c r="AM18" s="28" t="n"/>
       <c r="AN18" s="5" t="n"/>
       <c r="BK18" s="28" t="n"/>
     </row>
     <row r="19" ht="99" customHeight="1">
-      <c r="A19" s="32" t="n"/>
-      <c r="B19" s="32" t="n"/>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="31" t="n"/>
-      <c r="E19" s="55" t="n"/>
-      <c r="F19" s="31" t="n"/>
-      <c r="G19" s="31" t="n"/>
-      <c r="H19" s="31" t="n"/>
-      <c r="I19" s="31" t="n"/>
-      <c r="J19" s="31" t="n"/>
-      <c r="K19" s="31" t="n"/>
-      <c r="L19" s="31" t="n"/>
-      <c r="M19" s="55" t="n"/>
-      <c r="N19" s="31" t="n"/>
-      <c r="O19" s="31" t="n"/>
-      <c r="P19" s="31" t="n"/>
-      <c r="Q19" s="31" t="n"/>
-      <c r="R19" s="31" t="n"/>
-      <c r="S19" s="32" t="n"/>
-      <c r="T19" s="31" t="n"/>
-      <c r="U19" s="31" t="n"/>
-      <c r="V19" s="31" t="n"/>
-      <c r="W19" s="31" t="n"/>
-      <c r="X19" s="58" t="n"/>
-      <c r="Y19" s="45" t="n"/>
-      <c r="Z19" s="26" t="n"/>
-      <c r="AA19" s="32" t="n"/>
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>Вороток</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="n">
+        <v>584</v>
+      </c>
+      <c r="C19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="W19" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y19" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z19" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA19" s="32" t="n">
+        <v>2</v>
+      </c>
       <c r="AB19" s="34" t="n"/>
-      <c r="AC19" s="63" t="n"/>
-      <c r="AD19" s="163" t="n"/>
-      <c r="AE19" s="177" t="n"/>
-      <c r="AF19" s="162" t="n"/>
-      <c r="AG19" s="162" t="n"/>
-      <c r="AH19" s="162" t="n"/>
-      <c r="AI19" s="162" t="n"/>
-      <c r="AJ19" s="162" t="n"/>
-      <c r="AK19" s="163" t="n"/>
+      <c r="AC19" s="65" t="n"/>
+      <c r="AD19" s="150" t="n"/>
+      <c r="AE19" s="159" t="inlineStr">
+        <is>
+          <t>5-107/25</t>
+        </is>
+      </c>
+      <c r="AF19" s="149" t="n"/>
+      <c r="AG19" s="149" t="n"/>
+      <c r="AH19" s="149" t="n"/>
+      <c r="AI19" s="149" t="n"/>
+      <c r="AJ19" s="149" t="n"/>
+      <c r="AK19" s="150" t="n"/>
       <c r="AL19" s="27" t="n"/>
       <c r="AM19" s="28" t="n"/>
       <c r="AN19" s="5" t="n"/>
       <c r="BK19" s="28" t="n"/>
     </row>
     <row r="20" ht="99" customHeight="1">
-      <c r="A20" s="32" t="n"/>
-      <c r="B20" s="44" t="n"/>
-      <c r="C20" s="46" t="n"/>
-      <c r="D20" s="31" t="n"/>
-      <c r="E20" s="31" t="n"/>
-      <c r="F20" s="31" t="n"/>
-      <c r="G20" s="31" t="n"/>
-      <c r="H20" s="31" t="n"/>
-      <c r="I20" s="31" t="n"/>
-      <c r="J20" s="31" t="n"/>
-      <c r="K20" s="31" t="n"/>
-      <c r="L20" s="31" t="n"/>
-      <c r="M20" s="31" t="n"/>
-      <c r="N20" s="31" t="n"/>
-      <c r="O20" s="31" t="n"/>
-      <c r="P20" s="31" t="n"/>
-      <c r="Q20" s="31" t="n"/>
-      <c r="R20" s="31" t="n"/>
-      <c r="S20" s="31" t="n"/>
-      <c r="T20" s="31" t="n"/>
-      <c r="U20" s="31" t="n"/>
-      <c r="V20" s="31" t="n"/>
-      <c r="W20" s="31" t="n"/>
-      <c r="X20" s="59" t="n"/>
-      <c r="Y20" s="45" t="n"/>
-      <c r="Z20" s="26" t="n"/>
-      <c r="AA20" s="32" t="n"/>
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>Ригель</t>
+        </is>
+      </c>
+      <c r="B20" s="44" t="n">
+        <v>1217</v>
+      </c>
+      <c r="C20" s="46" t="n">
+        <v>43</v>
+      </c>
+      <c r="D20" s="31" t="n">
+        <v>44</v>
+      </c>
+      <c r="E20" s="31" t="n">
+        <v>43</v>
+      </c>
+      <c r="F20" s="31" t="n">
+        <v>44</v>
+      </c>
+      <c r="G20" s="31" t="n">
+        <v>44</v>
+      </c>
+      <c r="H20" s="31" t="n">
+        <v>43</v>
+      </c>
+      <c r="I20" s="31" t="n">
+        <v>44</v>
+      </c>
+      <c r="J20" s="31" t="n">
+        <v>43</v>
+      </c>
+      <c r="K20" s="31" t="n">
+        <v>44</v>
+      </c>
+      <c r="L20" s="31" t="n">
+        <v>43</v>
+      </c>
+      <c r="M20" s="31" t="n">
+        <v>44</v>
+      </c>
+      <c r="N20" s="31" t="n">
+        <v>43</v>
+      </c>
+      <c r="O20" s="31" t="n">
+        <v>44</v>
+      </c>
+      <c r="P20" s="31" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q20" s="31" t="n">
+        <v>44</v>
+      </c>
+      <c r="R20" s="31" t="n">
+        <v>43</v>
+      </c>
+      <c r="S20" s="31" t="n">
+        <v>44</v>
+      </c>
+      <c r="T20" s="31" t="n">
+        <v>43</v>
+      </c>
+      <c r="U20" s="31" t="n">
+        <v>44</v>
+      </c>
+      <c r="V20" s="31" t="n">
+        <v>43</v>
+      </c>
+      <c r="W20" s="31" t="n">
+        <v>44</v>
+      </c>
+      <c r="X20" s="59" t="n">
+        <v>43</v>
+      </c>
+      <c r="Y20" s="45" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z20" s="26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA20" s="32" t="n">
+        <v>43</v>
+      </c>
       <c r="AB20" s="34" t="n"/>
-      <c r="AC20" s="63" t="n"/>
-      <c r="AD20" s="163" t="n"/>
-      <c r="AE20" s="177" t="n"/>
-      <c r="AF20" s="162" t="n"/>
-      <c r="AG20" s="162" t="n"/>
-      <c r="AH20" s="162" t="n"/>
-      <c r="AI20" s="162" t="n"/>
-      <c r="AJ20" s="162" t="n"/>
-      <c r="AK20" s="163" t="n"/>
+      <c r="AC20" s="65" t="n"/>
+      <c r="AD20" s="150" t="n"/>
+      <c r="AE20" s="159" t="inlineStr">
+        <is>
+          <t>5-134/25, 5-133/25, 5-132/25</t>
+        </is>
+      </c>
+      <c r="AF20" s="149" t="n"/>
+      <c r="AG20" s="149" t="n"/>
+      <c r="AH20" s="149" t="n"/>
+      <c r="AI20" s="149" t="n"/>
+      <c r="AJ20" s="149" t="n"/>
+      <c r="AK20" s="150" t="n"/>
       <c r="AL20" s="27" t="n"/>
       <c r="AM20" s="28" t="n"/>
       <c r="AN20" s="5" t="n"/>
       <c r="BK20" s="28" t="n"/>
     </row>
     <row r="21" ht="99" customHeight="1">
-      <c r="A21" s="24" t="n"/>
-      <c r="B21" s="43" t="n"/>
-      <c r="C21" s="45" t="n"/>
-      <c r="D21" s="26" t="n"/>
-      <c r="E21" s="26" t="n"/>
-      <c r="F21" s="26" t="n"/>
-      <c r="G21" s="26" t="n"/>
-      <c r="H21" s="26" t="n"/>
-      <c r="I21" s="26" t="n"/>
-      <c r="J21" s="26" t="n"/>
-      <c r="K21" s="26" t="n"/>
-      <c r="L21" s="26" t="n"/>
-      <c r="M21" s="26" t="n"/>
-      <c r="N21" s="26" t="n"/>
-      <c r="O21" s="26" t="n"/>
-      <c r="P21" s="26" t="n"/>
-      <c r="Q21" s="26" t="n"/>
-      <c r="R21" s="26" t="n"/>
-      <c r="S21" s="26" t="n"/>
-      <c r="T21" s="26" t="n"/>
-      <c r="U21" s="26" t="n"/>
-      <c r="V21" s="26" t="n"/>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="59" t="n"/>
-      <c r="Y21" s="45" t="n"/>
-      <c r="Z21" s="26" t="n"/>
-      <c r="AA21" s="32" t="n"/>
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>Ригель optima</t>
+        </is>
+      </c>
+      <c r="B21" s="43" t="n">
+        <v>1835</v>
+      </c>
+      <c r="C21" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="P21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="V21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="W21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X21" s="59" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA21" s="32" t="n">
+        <v>4</v>
+      </c>
       <c r="AB21" s="34" t="n"/>
-      <c r="AC21" s="63" t="n"/>
-      <c r="AD21" s="163" t="n"/>
-      <c r="AE21" s="177" t="n"/>
-      <c r="AF21" s="162" t="n"/>
-      <c r="AG21" s="162" t="n"/>
-      <c r="AH21" s="162" t="n"/>
-      <c r="AI21" s="162" t="n"/>
-      <c r="AJ21" s="162" t="n"/>
-      <c r="AK21" s="163" t="n"/>
+      <c r="AC21" s="65" t="n"/>
+      <c r="AD21" s="150" t="n"/>
+      <c r="AE21" s="159" t="inlineStr">
+        <is>
+          <t>3-332/25, 4-193/25</t>
+        </is>
+      </c>
+      <c r="AF21" s="149" t="n"/>
+      <c r="AG21" s="149" t="n"/>
+      <c r="AH21" s="149" t="n"/>
+      <c r="AI21" s="149" t="n"/>
+      <c r="AJ21" s="149" t="n"/>
+      <c r="AK21" s="150" t="n"/>
       <c r="AL21" s="27" t="n"/>
       <c r="AM21" s="28" t="n"/>
       <c r="AN21" s="5" t="n"/>
@@ -2818,15 +3070,15 @@
       <c r="Z22" s="26" t="n"/>
       <c r="AA22" s="32" t="n"/>
       <c r="AB22" s="34" t="n"/>
-      <c r="AC22" s="63" t="n"/>
-      <c r="AD22" s="163" t="n"/>
-      <c r="AE22" s="177" t="n"/>
-      <c r="AF22" s="162" t="n"/>
-      <c r="AG22" s="162" t="n"/>
-      <c r="AH22" s="162" t="n"/>
-      <c r="AI22" s="162" t="n"/>
-      <c r="AJ22" s="162" t="n"/>
-      <c r="AK22" s="163" t="n"/>
+      <c r="AC22" s="65" t="n"/>
+      <c r="AD22" s="150" t="n"/>
+      <c r="AE22" s="159" t="n"/>
+      <c r="AF22" s="149" t="n"/>
+      <c r="AG22" s="149" t="n"/>
+      <c r="AH22" s="149" t="n"/>
+      <c r="AI22" s="149" t="n"/>
+      <c r="AJ22" s="149" t="n"/>
+      <c r="AK22" s="150" t="n"/>
       <c r="AL22" s="27" t="n"/>
       <c r="AM22" s="28" t="n"/>
       <c r="AN22" s="5" t="n"/>
@@ -2861,15 +3113,15 @@
       <c r="Z23" s="26" t="n"/>
       <c r="AA23" s="32" t="n"/>
       <c r="AB23" s="34" t="n"/>
-      <c r="AC23" s="63" t="n"/>
-      <c r="AD23" s="163" t="n"/>
-      <c r="AE23" s="177" t="n"/>
-      <c r="AF23" s="162" t="n"/>
-      <c r="AG23" s="162" t="n"/>
-      <c r="AH23" s="162" t="n"/>
-      <c r="AI23" s="162" t="n"/>
-      <c r="AJ23" s="162" t="n"/>
-      <c r="AK23" s="163" t="n"/>
+      <c r="AC23" s="65" t="n"/>
+      <c r="AD23" s="150" t="n"/>
+      <c r="AE23" s="159" t="n"/>
+      <c r="AF23" s="149" t="n"/>
+      <c r="AG23" s="149" t="n"/>
+      <c r="AH23" s="149" t="n"/>
+      <c r="AI23" s="149" t="n"/>
+      <c r="AJ23" s="149" t="n"/>
+      <c r="AK23" s="150" t="n"/>
       <c r="AL23" s="27" t="n"/>
       <c r="AM23" s="28" t="n"/>
       <c r="AN23" s="5" t="n"/>
@@ -2904,15 +3156,15 @@
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="32" t="n"/>
       <c r="AB24" s="34" t="n"/>
-      <c r="AC24" s="63" t="n"/>
-      <c r="AD24" s="163" t="n"/>
-      <c r="AE24" s="177" t="n"/>
-      <c r="AF24" s="162" t="n"/>
-      <c r="AG24" s="162" t="n"/>
-      <c r="AH24" s="162" t="n"/>
-      <c r="AI24" s="162" t="n"/>
-      <c r="AJ24" s="162" t="n"/>
-      <c r="AK24" s="163" t="n"/>
+      <c r="AC24" s="65" t="n"/>
+      <c r="AD24" s="150" t="n"/>
+      <c r="AE24" s="159" t="n"/>
+      <c r="AF24" s="149" t="n"/>
+      <c r="AG24" s="149" t="n"/>
+      <c r="AH24" s="149" t="n"/>
+      <c r="AI24" s="149" t="n"/>
+      <c r="AJ24" s="149" t="n"/>
+      <c r="AK24" s="150" t="n"/>
       <c r="AL24" s="27" t="n"/>
       <c r="AM24" s="28" t="n"/>
       <c r="AN24" s="5" t="n"/>
@@ -2947,15 +3199,15 @@
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="32" t="n"/>
       <c r="AB25" s="34" t="n"/>
-      <c r="AC25" s="63" t="n"/>
-      <c r="AD25" s="163" t="n"/>
-      <c r="AE25" s="177" t="n"/>
-      <c r="AF25" s="162" t="n"/>
-      <c r="AG25" s="162" t="n"/>
-      <c r="AH25" s="162" t="n"/>
-      <c r="AI25" s="162" t="n"/>
-      <c r="AJ25" s="162" t="n"/>
-      <c r="AK25" s="163" t="n"/>
+      <c r="AC25" s="65" t="n"/>
+      <c r="AD25" s="150" t="n"/>
+      <c r="AE25" s="159" t="n"/>
+      <c r="AF25" s="149" t="n"/>
+      <c r="AG25" s="149" t="n"/>
+      <c r="AH25" s="149" t="n"/>
+      <c r="AI25" s="149" t="n"/>
+      <c r="AJ25" s="149" t="n"/>
+      <c r="AK25" s="150" t="n"/>
       <c r="AL25" s="27" t="n"/>
       <c r="AM25" s="28" t="n"/>
       <c r="AN25" s="5" t="n"/>
@@ -2990,15 +3242,15 @@
       <c r="Z26" s="36" t="n"/>
       <c r="AA26" s="37" t="n"/>
       <c r="AB26" s="38" t="n"/>
-      <c r="AC26" s="63" t="n"/>
-      <c r="AD26" s="163" t="n"/>
-      <c r="AE26" s="177" t="n"/>
-      <c r="AF26" s="162" t="n"/>
-      <c r="AG26" s="162" t="n"/>
-      <c r="AH26" s="162" t="n"/>
-      <c r="AI26" s="162" t="n"/>
-      <c r="AJ26" s="162" t="n"/>
-      <c r="AK26" s="163" t="n"/>
+      <c r="AC26" s="65" t="n"/>
+      <c r="AD26" s="150" t="n"/>
+      <c r="AE26" s="159" t="n"/>
+      <c r="AF26" s="149" t="n"/>
+      <c r="AG26" s="149" t="n"/>
+      <c r="AH26" s="149" t="n"/>
+      <c r="AI26" s="149" t="n"/>
+      <c r="AJ26" s="149" t="n"/>
+      <c r="AK26" s="150" t="n"/>
       <c r="AL26" s="27" t="n"/>
       <c r="AM26" s="28" t="n"/>
       <c r="AN26" s="5" t="n"/>
@@ -3010,18 +3262,19 @@
   </sheetData>
   <mergeCells count="73">
     <mergeCell ref="O5:O6"/>
+    <mergeCell ref="Q14:S14"/>
+    <mergeCell ref="AE19:AK19"/>
+    <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="Q14:S14"/>
+    <mergeCell ref="W5:W6"/>
     <mergeCell ref="L2:P2"/>
-    <mergeCell ref="W5:W6"/>
-    <mergeCell ref="AH5:AH6"/>
-    <mergeCell ref="AE19:AK19"/>
     <mergeCell ref="Y5:Y6"/>
     <mergeCell ref="Q10:S10"/>
     <mergeCell ref="Q4:S6"/>
+    <mergeCell ref="A16:A17"/>
     <mergeCell ref="AD5:AE5"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="F5:F6"/>
+    <mergeCell ref="AB5:AB6"/>
     <mergeCell ref="AE24:AK24"/>
     <mergeCell ref="AA5:AA6"/>
     <mergeCell ref="AC18:AD18"/>
@@ -3030,27 +3283,26 @@
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="AK5:AK6"/>
     <mergeCell ref="A4:A6"/>
+    <mergeCell ref="C4:P4"/>
     <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C4:P4"/>
     <mergeCell ref="AF5:AF6"/>
-    <mergeCell ref="AC24:AD24"/>
+    <mergeCell ref="L15:P15"/>
     <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="L15:P15"/>
     <mergeCell ref="AE20:AK20"/>
     <mergeCell ref="AE26:AK26"/>
-    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="AC24:AD24"/>
+    <mergeCell ref="AE16:AK17"/>
     <mergeCell ref="AC23:AD23"/>
     <mergeCell ref="AE25:AK25"/>
     <mergeCell ref="X5:X6"/>
+    <mergeCell ref="Z5:Z6"/>
     <mergeCell ref="I5:I6"/>
-    <mergeCell ref="Z5:Z6"/>
+    <mergeCell ref="AC26:AD26"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="AE22:AK22"/>
     <mergeCell ref="G5:G6"/>
-    <mergeCell ref="Q11:S11"/>
     <mergeCell ref="AJ5:AJ6"/>
-    <mergeCell ref="R2:AH2"/>
-    <mergeCell ref="AC26:AD26"/>
     <mergeCell ref="U5:U6"/>
-    <mergeCell ref="AE22:AK22"/>
     <mergeCell ref="AC20:AD20"/>
     <mergeCell ref="AE18:AK18"/>
     <mergeCell ref="AC19:AD19"/>
@@ -3059,29 +3311,29 @@
     <mergeCell ref="AE21:AK21"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="AC22:AD22"/>
     <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="AC22:AD22"/>
     <mergeCell ref="AC16:AD17"/>
     <mergeCell ref="D5:D6"/>
+    <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="P5:P6"/>
-    <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="C16:X16"/>
+    <mergeCell ref="AI5:AI6"/>
     <mergeCell ref="H5:H6"/>
-    <mergeCell ref="AI5:AI6"/>
     <mergeCell ref="AC21:AD21"/>
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="AE23:AK23"/>
     <mergeCell ref="K5:K6"/>
+    <mergeCell ref="Y16:AB16"/>
     <mergeCell ref="C5:C6"/>
-    <mergeCell ref="Y16:AB16"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="Q8:S8"/>
     <mergeCell ref="T5:T6"/>
     <mergeCell ref="V5:V6"/>
-    <mergeCell ref="AB5:AB6"/>
+    <mergeCell ref="R2:AH2"/>
     <mergeCell ref="T4:AK4"/>
-    <mergeCell ref="AE16:AK17"/>
+    <mergeCell ref="M5:M6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1181102362204725" right="0.1181102362204725" top="0.7480314960629921" bottom="0.3543307086614174" header="0.3149606299212598" footer="0.3149606299212598"/>

--- a/Отчет_20-05-2025.xlsx
+++ b/Отчет_20-05-2025.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <charset val="204"/>
@@ -104,6 +104,29 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -756,6 +779,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -769,21 +807,6 @@
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -811,7 +834,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -838,15 +861,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -855,22 +872,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -881,13 +886,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -906,39 +904,150 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -966,156 +1075,126 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1137,23 +1216,20 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1471,12 +1547,12 @@
   <dimension ref="A1:BK26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27.85546875" customWidth="1" style="28" min="1" max="1"/>
-    <col width="14.85546875" customWidth="1" style="28" min="2" max="2"/>
+    <col width="27.85546875" customWidth="1" style="22" min="1" max="1"/>
+    <col width="14.85546875" customWidth="1" style="22" min="2" max="2"/>
     <col width="11.7109375" customWidth="1" style="5" min="3" max="4"/>
     <col width="8.5703125" customWidth="1" style="5" min="5" max="16"/>
     <col width="7.85546875" customWidth="1" style="5" min="17" max="18"/>
-    <col width="8.5703125" customWidth="1" style="28" min="19" max="19"/>
+    <col width="8.5703125" customWidth="1" style="22" min="19" max="19"/>
     <col width="8.5703125" customWidth="1" style="5" min="20" max="23"/>
     <col width="9.85546875" customWidth="1" style="5" min="24" max="24"/>
     <col width="8.5703125" customWidth="1" style="5" min="25" max="25"/>
@@ -1485,279 +1561,279 @@
     <col width="9" customWidth="1" style="5" min="32" max="35"/>
     <col width="9.28515625" bestFit="1" customWidth="1" style="5" min="36" max="36"/>
     <col width="10" customWidth="1" style="5" min="37" max="38"/>
-    <col width="10" customWidth="1" style="28" min="39" max="39"/>
+    <col width="10" customWidth="1" style="22" min="39" max="39"/>
     <col width="5.42578125" customWidth="1" style="5" min="40" max="63"/>
-    <col width="13.85546875" customWidth="1" style="28" min="64" max="64"/>
-    <col width="24.28515625" customWidth="1" style="28" min="65" max="65"/>
-    <col width="9.140625" customWidth="1" style="28" min="66" max="16384"/>
+    <col width="13.85546875" customWidth="1" style="22" min="64" max="64"/>
+    <col width="24.28515625" customWidth="1" style="22" min="65" max="65"/>
+    <col width="9.140625" customWidth="1" style="22" min="66" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="37.5" customHeight="1">
-      <c r="A1" s="85" t="inlineStr">
+      <c r="A1" s="73" t="inlineStr">
         <is>
           <t>ОТЧЕТ по сдаче продукции в литейном цехе</t>
         </is>
       </c>
-      <c r="AL1" s="85" t="n"/>
+      <c r="AL1" s="73" t="n"/>
     </row>
     <row r="2" ht="73.5" customHeight="1">
-      <c r="A2" s="63" t="inlineStr">
+      <c r="A2" s="81" t="inlineStr">
         <is>
           <t>Дата:  20.05.2025  2025 г.</t>
         </is>
       </c>
-      <c r="L2" s="95" t="inlineStr">
-        <is>
-          <t>Контролеры: Иванова</t>
+      <c r="L2" s="60" t="inlineStr">
+        <is>
+          <t>Контролеры: Елхова, Лабуткина, Рябова, Улитина</t>
         </is>
       </c>
       <c r="Q2" s="5" t="n"/>
-      <c r="R2" s="62" t="inlineStr">
+      <c r="R2" s="80" t="inlineStr">
         <is>
           <t>,</t>
         </is>
       </c>
-      <c r="S2" s="128" t="n"/>
-      <c r="T2" s="128" t="n"/>
-      <c r="U2" s="128" t="n"/>
-      <c r="V2" s="128" t="n"/>
-      <c r="W2" s="128" t="n"/>
-      <c r="X2" s="128" t="n"/>
-      <c r="Y2" s="128" t="n"/>
-      <c r="Z2" s="128" t="n"/>
-      <c r="AA2" s="128" t="n"/>
-      <c r="AB2" s="128" t="n"/>
-      <c r="AC2" s="128" t="n"/>
-      <c r="AD2" s="128" t="n"/>
-      <c r="AE2" s="128" t="n"/>
-      <c r="AF2" s="128" t="n"/>
-      <c r="AG2" s="128" t="n"/>
-      <c r="AH2" s="128" t="n"/>
+      <c r="S2" s="130" t="n"/>
+      <c r="T2" s="130" t="n"/>
+      <c r="U2" s="130" t="n"/>
+      <c r="V2" s="130" t="n"/>
+      <c r="W2" s="130" t="n"/>
+      <c r="X2" s="130" t="n"/>
+      <c r="Y2" s="130" t="n"/>
+      <c r="Z2" s="130" t="n"/>
+      <c r="AA2" s="130" t="n"/>
+      <c r="AB2" s="130" t="n"/>
+      <c r="AC2" s="130" t="n"/>
+      <c r="AD2" s="130" t="n"/>
+      <c r="AE2" s="130" t="n"/>
+      <c r="AF2" s="130" t="n"/>
+      <c r="AG2" s="130" t="n"/>
+      <c r="AH2" s="130" t="n"/>
       <c r="AI2" s="5" t="n"/>
       <c r="AJ2" s="5" t="n"/>
     </row>
     <row r="3" ht="22.5" customHeight="1" thickBot="1"/>
     <row r="4" ht="26.25" customFormat="1" customHeight="1" s="7" thickBot="1">
-      <c r="A4" s="129" t="inlineStr">
+      <c r="A4" s="131" t="inlineStr">
         <is>
           <t>НОМЕР И НАИМЕНОВАНИЕ ОТЛИВКИ</t>
         </is>
       </c>
-      <c r="B4" s="129" t="inlineStr">
+      <c r="B4" s="131" t="inlineStr">
         <is>
           <t>ОТЛИТО, шт.</t>
         </is>
       </c>
-      <c r="C4" s="86" t="inlineStr">
+      <c r="C4" s="63" t="inlineStr">
         <is>
           <t>БРАК НА ОПЕРАЦИЯХ, шт.</t>
         </is>
       </c>
-      <c r="D4" s="130" t="n"/>
-      <c r="E4" s="130" t="n"/>
-      <c r="F4" s="130" t="n"/>
-      <c r="G4" s="130" t="n"/>
-      <c r="H4" s="130" t="n"/>
-      <c r="I4" s="130" t="n"/>
-      <c r="J4" s="130" t="n"/>
-      <c r="K4" s="130" t="n"/>
-      <c r="L4" s="130" t="n"/>
-      <c r="M4" s="130" t="n"/>
-      <c r="N4" s="130" t="n"/>
-      <c r="O4" s="130" t="n"/>
-      <c r="P4" s="131" t="n"/>
-      <c r="Q4" s="129" t="inlineStr">
+      <c r="D4" s="132" t="n"/>
+      <c r="E4" s="132" t="n"/>
+      <c r="F4" s="132" t="n"/>
+      <c r="G4" s="132" t="n"/>
+      <c r="H4" s="132" t="n"/>
+      <c r="I4" s="132" t="n"/>
+      <c r="J4" s="132" t="n"/>
+      <c r="K4" s="132" t="n"/>
+      <c r="L4" s="132" t="n"/>
+      <c r="M4" s="132" t="n"/>
+      <c r="N4" s="132" t="n"/>
+      <c r="O4" s="132" t="n"/>
+      <c r="P4" s="133" t="n"/>
+      <c r="Q4" s="131" t="inlineStr">
         <is>
           <t>ПОДАНО, шт.</t>
         </is>
       </c>
-      <c r="R4" s="132" t="n"/>
-      <c r="S4" s="133" t="n"/>
-      <c r="T4" s="86" t="inlineStr">
+      <c r="R4" s="134" t="n"/>
+      <c r="S4" s="135" t="n"/>
+      <c r="T4" s="63" t="inlineStr">
         <is>
           <t>ДОРАБОТКА, шт.</t>
         </is>
       </c>
-      <c r="U4" s="130" t="n"/>
-      <c r="V4" s="130" t="n"/>
-      <c r="W4" s="130" t="n"/>
-      <c r="X4" s="130" t="n"/>
-      <c r="Y4" s="130" t="n"/>
-      <c r="Z4" s="130" t="n"/>
-      <c r="AA4" s="130" t="n"/>
-      <c r="AB4" s="130" t="n"/>
-      <c r="AC4" s="130" t="n"/>
-      <c r="AD4" s="130" t="n"/>
-      <c r="AE4" s="130" t="n"/>
-      <c r="AF4" s="130" t="n"/>
-      <c r="AG4" s="130" t="n"/>
-      <c r="AH4" s="130" t="n"/>
-      <c r="AI4" s="130" t="n"/>
-      <c r="AJ4" s="130" t="n"/>
-      <c r="AK4" s="131" t="n"/>
+      <c r="U4" s="132" t="n"/>
+      <c r="V4" s="132" t="n"/>
+      <c r="W4" s="132" t="n"/>
+      <c r="X4" s="132" t="n"/>
+      <c r="Y4" s="132" t="n"/>
+      <c r="Z4" s="132" t="n"/>
+      <c r="AA4" s="132" t="n"/>
+      <c r="AB4" s="132" t="n"/>
+      <c r="AC4" s="132" t="n"/>
+      <c r="AD4" s="132" t="n"/>
+      <c r="AE4" s="132" t="n"/>
+      <c r="AF4" s="132" t="n"/>
+      <c r="AG4" s="132" t="n"/>
+      <c r="AH4" s="132" t="n"/>
+      <c r="AI4" s="132" t="n"/>
+      <c r="AJ4" s="132" t="n"/>
+      <c r="AK4" s="133" t="n"/>
       <c r="AL4" s="6" t="n"/>
     </row>
     <row r="5" ht="114.75" customFormat="1" customHeight="1" s="9">
-      <c r="A5" s="134" t="n"/>
-      <c r="B5" s="134" t="n"/>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="A5" s="136" t="n"/>
+      <c r="B5" s="136" t="n"/>
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>недолив</t>
         </is>
       </c>
-      <c r="D5" s="41" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>раковины на корпусе</t>
         </is>
       </c>
-      <c r="E5" s="41" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>наруш. геом.</t>
         </is>
       </c>
-      <c r="F5" s="41" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>брак п/м</t>
         </is>
       </c>
-      <c r="G5" s="41" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>пригар песка</t>
         </is>
       </c>
-      <c r="H5" s="41" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>наплыв металла</t>
         </is>
       </c>
-      <c r="I5" s="41" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>вырыв</t>
         </is>
       </c>
-      <c r="J5" s="41" t="inlineStr">
+      <c r="J5" s="25" t="inlineStr">
         <is>
           <t>слом</t>
         </is>
       </c>
-      <c r="K5" s="41" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t>зарез</t>
         </is>
       </c>
-      <c r="L5" s="41" t="inlineStr">
+      <c r="L5" s="25" t="inlineStr">
         <is>
           <t>несоотв. 
 внеш. вида</t>
         </is>
       </c>
-      <c r="M5" s="41" t="inlineStr">
+      <c r="M5" s="25" t="inlineStr">
         <is>
           <t>трещины</t>
         </is>
       </c>
-      <c r="N5" s="41" t="inlineStr">
+      <c r="N5" s="25" t="inlineStr">
         <is>
           <t>скол</t>
         </is>
       </c>
-      <c r="O5" s="41" t="inlineStr">
+      <c r="O5" s="25" t="inlineStr">
         <is>
           <t>нарушение маркировки</t>
         </is>
       </c>
-      <c r="P5" s="42" t="inlineStr">
+      <c r="P5" s="26" t="inlineStr">
         <is>
           <t>технол. брак (ЛПД)</t>
         </is>
       </c>
-      <c r="Q5" s="135" t="n"/>
-      <c r="S5" s="136" t="n"/>
-      <c r="T5" s="90" t="inlineStr">
+      <c r="Q5" s="137" t="n"/>
+      <c r="S5" s="138" t="n"/>
+      <c r="T5" s="67" t="inlineStr">
         <is>
           <t>Раковины</t>
         </is>
       </c>
-      <c r="U5" s="67" t="inlineStr">
+      <c r="U5" s="40" t="inlineStr">
         <is>
           <t>Зарез</t>
         </is>
       </c>
-      <c r="V5" s="67" t="inlineStr">
+      <c r="V5" s="40" t="inlineStr">
         <is>
           <t>Несоотв. размеров</t>
         </is>
       </c>
-      <c r="W5" s="67" t="inlineStr">
+      <c r="W5" s="40" t="inlineStr">
         <is>
           <t>Несоотв. 
 внеш. вида</t>
         </is>
       </c>
-      <c r="X5" s="67" t="inlineStr">
+      <c r="X5" s="40" t="inlineStr">
         <is>
           <t>Наплыв мет. 
 на пов-ти</t>
         </is>
       </c>
-      <c r="Y5" s="80" t="inlineStr">
+      <c r="Y5" s="61" t="inlineStr">
         <is>
           <t>Прорыв мет. в резьбе (вороток)</t>
         </is>
       </c>
-      <c r="Z5" s="80" t="inlineStr">
+      <c r="Z5" s="61" t="inlineStr">
         <is>
           <t>Вырыв</t>
         </is>
       </c>
-      <c r="AA5" s="67" t="inlineStr">
+      <c r="AA5" s="40" t="inlineStr">
         <is>
           <t>Облой</t>
         </is>
       </c>
-      <c r="AB5" s="67" t="inlineStr">
+      <c r="AB5" s="40" t="inlineStr">
         <is>
           <t>Песок на 
 пов-ти</t>
         </is>
       </c>
-      <c r="AC5" s="82" t="inlineStr">
+      <c r="AC5" s="70" t="inlineStr">
         <is>
           <t>Песок в резьбе (вороток)</t>
         </is>
       </c>
-      <c r="AD5" s="80" t="inlineStr">
+      <c r="AD5" s="61" t="inlineStr">
         <is>
           <t>Клей</t>
         </is>
       </c>
-      <c r="AE5" s="137" t="n"/>
-      <c r="AF5" s="84" t="inlineStr">
+      <c r="AE5" s="139" t="n"/>
+      <c r="AF5" s="72" t="inlineStr">
         <is>
           <t>Коробление</t>
         </is>
       </c>
-      <c r="AG5" s="67" t="inlineStr">
+      <c r="AG5" s="40" t="inlineStr">
         <is>
           <t>Дефект п/м (покрытие)</t>
         </is>
       </c>
-      <c r="AH5" s="67" t="inlineStr">
+      <c r="AH5" s="40" t="inlineStr">
         <is>
           <t>Лапы</t>
         </is>
       </c>
-      <c r="AI5" s="67" t="inlineStr">
+      <c r="AI5" s="40" t="inlineStr">
         <is>
           <t>Питатель</t>
         </is>
       </c>
-      <c r="AJ5" s="67" t="inlineStr">
+      <c r="AJ5" s="40" t="inlineStr">
         <is>
           <t>Коронв</t>
         </is>
       </c>
-      <c r="AK5" s="70" t="inlineStr">
+      <c r="AK5" s="79" t="inlineStr">
         <is>
           <t>Смещение</t>
         </is>
@@ -1765,176 +1841,176 @@
       <c r="AL5" s="8" t="n"/>
     </row>
     <row r="6" ht="31.5" customFormat="1" customHeight="1" s="9" thickBot="1">
-      <c r="A6" s="138" t="n"/>
-      <c r="B6" s="138" t="n"/>
-      <c r="C6" s="139" t="n"/>
-      <c r="D6" s="140" t="n"/>
-      <c r="E6" s="140" t="n"/>
-      <c r="F6" s="140" t="n"/>
-      <c r="G6" s="140" t="n"/>
-      <c r="H6" s="140" t="n"/>
-      <c r="I6" s="140" t="n"/>
-      <c r="J6" s="140" t="n"/>
-      <c r="K6" s="140" t="n"/>
-      <c r="L6" s="140" t="n"/>
-      <c r="M6" s="140" t="n"/>
-      <c r="N6" s="140" t="n"/>
-      <c r="O6" s="140" t="n"/>
-      <c r="P6" s="141" t="n"/>
-      <c r="Q6" s="142" t="n"/>
-      <c r="R6" s="143" t="n"/>
-      <c r="S6" s="144" t="n"/>
-      <c r="T6" s="139" t="n"/>
-      <c r="U6" s="140" t="n"/>
-      <c r="V6" s="140" t="n"/>
-      <c r="W6" s="140" t="n"/>
-      <c r="X6" s="140" t="n"/>
-      <c r="Y6" s="145" t="n"/>
-      <c r="Z6" s="145" t="n"/>
-      <c r="AA6" s="140" t="n"/>
-      <c r="AB6" s="140" t="n"/>
-      <c r="AC6" s="146" t="n"/>
-      <c r="AD6" s="54" t="inlineStr">
+      <c r="A6" s="140" t="n"/>
+      <c r="B6" s="140" t="n"/>
+      <c r="C6" s="141" t="n"/>
+      <c r="D6" s="142" t="n"/>
+      <c r="E6" s="142" t="n"/>
+      <c r="F6" s="142" t="n"/>
+      <c r="G6" s="142" t="n"/>
+      <c r="H6" s="142" t="n"/>
+      <c r="I6" s="142" t="n"/>
+      <c r="J6" s="142" t="n"/>
+      <c r="K6" s="142" t="n"/>
+      <c r="L6" s="142" t="n"/>
+      <c r="M6" s="142" t="n"/>
+      <c r="N6" s="142" t="n"/>
+      <c r="O6" s="142" t="n"/>
+      <c r="P6" s="143" t="n"/>
+      <c r="Q6" s="144" t="n"/>
+      <c r="R6" s="145" t="n"/>
+      <c r="S6" s="146" t="n"/>
+      <c r="T6" s="141" t="n"/>
+      <c r="U6" s="142" t="n"/>
+      <c r="V6" s="142" t="n"/>
+      <c r="W6" s="142" t="n"/>
+      <c r="X6" s="142" t="n"/>
+      <c r="Y6" s="147" t="n"/>
+      <c r="Z6" s="147" t="n"/>
+      <c r="AA6" s="142" t="n"/>
+      <c r="AB6" s="142" t="n"/>
+      <c r="AC6" s="148" t="n"/>
+      <c r="AD6" s="31" t="inlineStr">
         <is>
           <t>П</t>
         </is>
       </c>
-      <c r="AE6" s="54" t="inlineStr">
+      <c r="AE6" s="31" t="inlineStr">
         <is>
           <t>Ш</t>
         </is>
       </c>
-      <c r="AF6" s="147" t="n"/>
-      <c r="AG6" s="140" t="n"/>
-      <c r="AH6" s="140" t="n"/>
-      <c r="AI6" s="140" t="n"/>
-      <c r="AJ6" s="140" t="n"/>
-      <c r="AK6" s="141" t="n"/>
+      <c r="AF6" s="149" t="n"/>
+      <c r="AG6" s="142" t="n"/>
+      <c r="AH6" s="142" t="n"/>
+      <c r="AI6" s="142" t="n"/>
+      <c r="AJ6" s="142" t="n"/>
+      <c r="AK6" s="143" t="n"/>
       <c r="AL6" s="8" t="n"/>
     </row>
     <row r="7" hidden="1" ht="104.25" customHeight="1">
-      <c r="A7" s="53" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>Наименование_отливки</t>
         </is>
       </c>
-      <c r="B7" s="55" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Контроль_отлито</t>
         </is>
       </c>
-      <c r="C7" s="50" t="n"/>
-      <c r="D7" s="50" t="n"/>
-      <c r="E7" s="51" t="n"/>
-      <c r="F7" s="50" t="n"/>
-      <c r="G7" s="50" t="n"/>
-      <c r="H7" s="50" t="n"/>
-      <c r="I7" s="50" t="n"/>
-      <c r="J7" s="50" t="n"/>
-      <c r="K7" s="50" t="n"/>
-      <c r="L7" s="50" t="n"/>
-      <c r="M7" s="50" t="n"/>
-      <c r="N7" s="50" t="n"/>
-      <c r="O7" s="50" t="n"/>
-      <c r="P7" s="102" t="n"/>
-      <c r="Q7" s="148" t="inlineStr">
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="27" t="n"/>
+      <c r="H7" s="27" t="n"/>
+      <c r="I7" s="27" t="n"/>
+      <c r="J7" s="27" t="n"/>
+      <c r="K7" s="27" t="n"/>
+      <c r="L7" s="27" t="n"/>
+      <c r="M7" s="27" t="n"/>
+      <c r="N7" s="27" t="n"/>
+      <c r="O7" s="27" t="n"/>
+      <c r="P7" s="57" t="n"/>
+      <c r="Q7" s="150" t="inlineStr">
         <is>
           <t>Контроль_отлито</t>
         </is>
       </c>
-      <c r="R7" s="128" t="n"/>
-      <c r="S7" s="137" t="n"/>
-      <c r="T7" s="55" t="inlineStr">
+      <c r="R7" s="130" t="n"/>
+      <c r="S7" s="139" t="n"/>
+      <c r="T7" s="32" t="inlineStr">
         <is>
           <t>Доработка_раковины</t>
         </is>
       </c>
-      <c r="U7" s="55" t="inlineStr">
+      <c r="U7" s="32" t="inlineStr">
         <is>
           <t>Доработка_зарез</t>
         </is>
       </c>
-      <c r="V7" s="55" t="inlineStr">
+      <c r="V7" s="32" t="inlineStr">
         <is>
           <t>Доработка_несоответствие_размеров</t>
         </is>
       </c>
-      <c r="W7" s="55" t="inlineStr">
+      <c r="W7" s="32" t="inlineStr">
         <is>
           <t>Доработка_несоответствие_внешнего_вида</t>
         </is>
       </c>
-      <c r="X7" s="55" t="inlineStr">
+      <c r="X7" s="32" t="inlineStr">
         <is>
           <t>Доработка_наплыв_металла</t>
         </is>
       </c>
-      <c r="Y7" s="55" t="inlineStr">
+      <c r="Y7" s="32" t="inlineStr">
         <is>
           <t>Доработка_прорыв_металла</t>
         </is>
       </c>
-      <c r="Z7" s="55" t="inlineStr">
+      <c r="Z7" s="32" t="inlineStr">
         <is>
           <t>Доработка_вырыв</t>
         </is>
       </c>
-      <c r="AA7" s="55" t="inlineStr">
+      <c r="AA7" s="32" t="inlineStr">
         <is>
           <t>Доработка_облой</t>
         </is>
       </c>
-      <c r="AB7" s="55" t="inlineStr">
+      <c r="AB7" s="32" t="inlineStr">
         <is>
           <t>Доработка_песок_на_поверхности</t>
         </is>
       </c>
-      <c r="AC7" s="55" t="inlineStr">
+      <c r="AC7" s="32" t="inlineStr">
         <is>
           <t>Доработка_песок_в_резьбе</t>
         </is>
       </c>
-      <c r="AD7" s="55" t="inlineStr">
+      <c r="AD7" s="32" t="inlineStr">
         <is>
           <t>Доработка_клей_подтёк</t>
         </is>
       </c>
-      <c r="AE7" s="55" t="inlineStr">
+      <c r="AE7" s="32" t="inlineStr">
         <is>
           <t>Доработка_клей_по_шву</t>
         </is>
       </c>
-      <c r="AF7" s="55" t="inlineStr">
+      <c r="AF7" s="32" t="inlineStr">
         <is>
           <t>Доработка_коробление</t>
         </is>
       </c>
-      <c r="AG7" s="55" t="inlineStr">
+      <c r="AG7" s="32" t="inlineStr">
         <is>
           <t>Доработка_дефект_пеномодели</t>
         </is>
       </c>
-      <c r="AH7" s="55" t="inlineStr">
+      <c r="AH7" s="32" t="inlineStr">
         <is>
           <t>Доработка_лапы</t>
         </is>
       </c>
-      <c r="AI7" s="55" t="inlineStr">
+      <c r="AI7" s="32" t="inlineStr">
         <is>
           <t>Доработка_питатель</t>
         </is>
       </c>
-      <c r="AJ7" s="55" t="inlineStr">
+      <c r="AJ7" s="32" t="inlineStr">
         <is>
           <t>Доработка_корона</t>
         </is>
       </c>
-      <c r="AK7" s="55" t="inlineStr">
+      <c r="AK7" s="32" t="inlineStr">
         <is>
           <t>Доработка_смещение</t>
         </is>
       </c>
-      <c r="AL7" s="17" t="n"/>
+      <c r="AL7" s="14" t="n"/>
     </row>
     <row r="8" ht="104.25" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
@@ -1943,80 +2019,80 @@
         </is>
       </c>
       <c r="B8" s="10" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="16" t="n"/>
-      <c r="G8" s="16" t="n"/>
-      <c r="H8" s="16" t="n"/>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="16" t="n"/>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="16" t="n"/>
-      <c r="M8" s="16" t="n"/>
-      <c r="N8" s="16" t="n"/>
-      <c r="O8" s="16" t="n"/>
-      <c r="P8" s="105" t="n"/>
-      <c r="Q8" s="111" t="n">
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="11" t="n"/>
+      <c r="I8" s="11" t="n"/>
+      <c r="J8" s="11" t="n"/>
+      <c r="K8" s="11" t="n"/>
+      <c r="L8" s="11" t="n"/>
+      <c r="M8" s="11" t="n"/>
+      <c r="N8" s="11" t="n"/>
+      <c r="O8" s="11" t="n"/>
+      <c r="P8" s="13" t="n"/>
+      <c r="Q8" s="104" t="n">
         <v>666</v>
       </c>
-      <c r="R8" s="149" t="n"/>
-      <c r="S8" s="150" t="n"/>
-      <c r="T8" s="31" t="n">
+      <c r="R8" s="151" t="n"/>
+      <c r="S8" s="152" t="n"/>
+      <c r="T8" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="U8" s="31" t="n">
+      <c r="U8" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="W8" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="X8" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y8" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z8" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA8" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB8" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC8" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD8" s="55" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE8" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF8" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG8" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH8" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI8" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ8" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK8" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL8" s="17" t="n"/>
+      <c r="V8" s="93" t="n">
+        <v>2</v>
+      </c>
+      <c r="W8" s="93" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" s="93" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="93" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z8" s="93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA8" s="93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB8" s="93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC8" s="93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE8" s="93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF8" s="93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" s="93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" s="93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI8" s="93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ8" s="93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK8" s="94" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL8" s="14" t="n"/>
     </row>
     <row r="9" ht="104.25" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -2025,80 +2101,80 @@
         </is>
       </c>
       <c r="B9" s="10" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="16" t="n"/>
-      <c r="G9" s="16" t="n"/>
-      <c r="H9" s="16" t="n"/>
-      <c r="I9" s="16" t="n"/>
-      <c r="J9" s="16" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="16" t="n"/>
-      <c r="M9" s="16" t="n"/>
-      <c r="N9" s="16" t="n"/>
-      <c r="O9" s="16" t="n"/>
-      <c r="P9" s="105" t="n"/>
-      <c r="Q9" s="111" t="n">
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="11" t="n"/>
+      <c r="I9" s="11" t="n"/>
+      <c r="J9" s="11" t="n"/>
+      <c r="K9" s="11" t="n"/>
+      <c r="L9" s="11" t="n"/>
+      <c r="M9" s="11" t="n"/>
+      <c r="N9" s="11" t="n"/>
+      <c r="O9" s="11" t="n"/>
+      <c r="P9" s="13" t="n"/>
+      <c r="Q9" s="104" t="n">
         <v>3000</v>
       </c>
-      <c r="R9" s="149" t="n"/>
-      <c r="S9" s="150" t="n"/>
-      <c r="T9" s="16" t="n">
+      <c r="R9" s="151" t="n"/>
+      <c r="S9" s="152" t="n"/>
+      <c r="T9" s="94" t="n">
         <v>0</v>
       </c>
-      <c r="U9" s="16" t="n">
+      <c r="U9" s="94" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="16" t="n">
+      <c r="V9" s="94" t="n">
         <v>44</v>
       </c>
-      <c r="W9" s="16" t="n">
+      <c r="W9" s="94" t="n">
         <v>43</v>
       </c>
-      <c r="X9" s="16" t="n">
+      <c r="X9" s="94" t="n">
         <v>44</v>
       </c>
-      <c r="Y9" s="16" t="n">
+      <c r="Y9" s="94" t="n">
         <v>43</v>
       </c>
-      <c r="Z9" s="16" t="n">
+      <c r="Z9" s="94" t="n">
         <v>44</v>
       </c>
-      <c r="AA9" s="16" t="n">
+      <c r="AA9" s="94" t="n">
         <v>43</v>
       </c>
-      <c r="AB9" s="16" t="n">
+      <c r="AB9" s="94" t="n">
         <v>44</v>
       </c>
-      <c r="AC9" s="16" t="n">
+      <c r="AC9" s="94" t="n">
         <v>43</v>
       </c>
-      <c r="AD9" s="16" t="n">
+      <c r="AD9" s="94" t="n">
         <v>44</v>
       </c>
-      <c r="AE9" s="16" t="n">
+      <c r="AE9" s="94" t="n">
         <v>43</v>
       </c>
-      <c r="AF9" s="16" t="n">
+      <c r="AF9" s="94" t="n">
         <v>44</v>
       </c>
-      <c r="AG9" s="14" t="n">
+      <c r="AG9" s="95" t="n">
         <v>43</v>
       </c>
-      <c r="AH9" s="16" t="n">
+      <c r="AH9" s="94" t="n">
         <v>44</v>
       </c>
-      <c r="AI9" s="16" t="n">
+      <c r="AI9" s="94" t="n">
         <v>43</v>
       </c>
-      <c r="AJ9" s="107" t="n">
+      <c r="AJ9" s="92" t="n">
         <v>44</v>
       </c>
-      <c r="AK9" s="16" t="n">
+      <c r="AK9" s="94" t="n">
         <v>43</v>
       </c>
-      <c r="AL9" s="17" t="n"/>
+      <c r="AL9" s="14" t="n"/>
     </row>
     <row r="10" ht="104.25" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
@@ -2107,247 +2183,247 @@
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="16" t="n"/>
-      <c r="G10" s="16" t="n"/>
-      <c r="H10" s="16" t="n"/>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="16" t="n"/>
-      <c r="K10" s="16" t="n"/>
-      <c r="L10" s="16" t="n"/>
-      <c r="M10" s="16" t="n"/>
-      <c r="N10" s="16" t="n"/>
-      <c r="O10" s="16" t="n"/>
-      <c r="P10" s="105" t="n"/>
-      <c r="Q10" s="111" t="n">
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="11" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="11" t="n"/>
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="11" t="n"/>
+      <c r="K10" s="11" t="n"/>
+      <c r="L10" s="11" t="n"/>
+      <c r="M10" s="11" t="n"/>
+      <c r="N10" s="11" t="n"/>
+      <c r="O10" s="11" t="n"/>
+      <c r="P10" s="13" t="n"/>
+      <c r="Q10" s="104" t="n">
         <v>1999</v>
       </c>
-      <c r="R10" s="149" t="n"/>
-      <c r="S10" s="150" t="n"/>
-      <c r="T10" s="16" t="n">
+      <c r="R10" s="151" t="n"/>
+      <c r="S10" s="152" t="n"/>
+      <c r="T10" s="94" t="n">
         <v>0</v>
       </c>
-      <c r="U10" s="16" t="n">
+      <c r="U10" s="94" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="W10" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="X10" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y10" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z10" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA10" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB10" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC10" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD10" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE10" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF10" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG10" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH10" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI10" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ10" s="107" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK10" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL10" s="17" t="n"/>
+      <c r="V10" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="W10" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="X10" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z10" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA10" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB10" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC10" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD10" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE10" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF10" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG10" s="95" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH10" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI10" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ10" s="92" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK10" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL10" s="14" t="n"/>
     </row>
     <row r="11" ht="104.25" customHeight="1">
-      <c r="A11" s="18" t="n"/>
-      <c r="B11" s="18" t="n"/>
-      <c r="C11" s="19" t="n"/>
-      <c r="D11" s="19" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="19" t="n"/>
-      <c r="G11" s="19" t="n"/>
-      <c r="H11" s="19" t="n"/>
-      <c r="I11" s="19" t="n"/>
-      <c r="J11" s="19" t="n"/>
-      <c r="K11" s="19" t="n"/>
-      <c r="L11" s="19" t="n"/>
-      <c r="M11" s="19" t="n"/>
-      <c r="N11" s="19" t="n"/>
-      <c r="O11" s="19" t="n"/>
-      <c r="P11" s="105" t="n"/>
-      <c r="Q11" s="151" t="n"/>
-      <c r="R11" s="152" t="n"/>
-      <c r="S11" s="153" t="n"/>
-      <c r="T11" s="19" t="n"/>
-      <c r="U11" s="19" t="n"/>
-      <c r="V11" s="19" t="n"/>
-      <c r="W11" s="19" t="n"/>
-      <c r="X11" s="19" t="n"/>
-      <c r="Y11" s="16" t="n"/>
-      <c r="Z11" s="16" t="n"/>
-      <c r="AA11" s="19" t="n"/>
-      <c r="AB11" s="19" t="n"/>
-      <c r="AC11" s="19" t="n"/>
-      <c r="AD11" s="19" t="n"/>
-      <c r="AE11" s="19" t="n"/>
-      <c r="AF11" s="19" t="n"/>
-      <c r="AG11" s="20" t="n"/>
-      <c r="AH11" s="16" t="n"/>
-      <c r="AI11" s="16" t="n"/>
-      <c r="AJ11" s="107" t="n"/>
-      <c r="AK11" s="16" t="n"/>
-      <c r="AL11" s="17" t="n"/>
+      <c r="A11" s="15" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="16" t="n"/>
+      <c r="I11" s="16" t="n"/>
+      <c r="J11" s="16" t="n"/>
+      <c r="K11" s="16" t="n"/>
+      <c r="L11" s="16" t="n"/>
+      <c r="M11" s="16" t="n"/>
+      <c r="N11" s="16" t="n"/>
+      <c r="O11" s="16" t="n"/>
+      <c r="P11" s="13" t="n"/>
+      <c r="Q11" s="153" t="n"/>
+      <c r="R11" s="154" t="n"/>
+      <c r="S11" s="155" t="n"/>
+      <c r="T11" s="96" t="n"/>
+      <c r="U11" s="96" t="n"/>
+      <c r="V11" s="96" t="n"/>
+      <c r="W11" s="96" t="n"/>
+      <c r="X11" s="96" t="n"/>
+      <c r="Y11" s="94" t="n"/>
+      <c r="Z11" s="94" t="n"/>
+      <c r="AA11" s="96" t="n"/>
+      <c r="AB11" s="96" t="n"/>
+      <c r="AC11" s="96" t="n"/>
+      <c r="AD11" s="96" t="n"/>
+      <c r="AE11" s="96" t="n"/>
+      <c r="AF11" s="96" t="n"/>
+      <c r="AG11" s="97" t="n"/>
+      <c r="AH11" s="94" t="n"/>
+      <c r="AI11" s="94" t="n"/>
+      <c r="AJ11" s="92" t="n"/>
+      <c r="AK11" s="94" t="n"/>
+      <c r="AL11" s="14" t="n"/>
     </row>
     <row r="12" ht="104.25" customHeight="1">
       <c r="A12" s="10" t="n"/>
       <c r="B12" s="10" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="16" t="n"/>
-      <c r="H12" s="16" t="n"/>
-      <c r="I12" s="16" t="n"/>
-      <c r="J12" s="16" t="n"/>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="16" t="n"/>
-      <c r="M12" s="16" t="n"/>
-      <c r="N12" s="16" t="n"/>
-      <c r="O12" s="16" t="n"/>
-      <c r="P12" s="105" t="n"/>
-      <c r="Q12" s="111" t="n"/>
-      <c r="R12" s="149" t="n"/>
-      <c r="S12" s="150" t="n"/>
-      <c r="T12" s="16" t="n"/>
-      <c r="U12" s="16" t="n"/>
-      <c r="V12" s="16" t="n"/>
-      <c r="W12" s="16" t="n"/>
-      <c r="X12" s="16" t="n"/>
-      <c r="Y12" s="16" t="n"/>
-      <c r="Z12" s="16" t="n"/>
-      <c r="AA12" s="16" t="n"/>
-      <c r="AB12" s="16" t="n"/>
-      <c r="AC12" s="16" t="n"/>
-      <c r="AD12" s="16" t="n"/>
-      <c r="AE12" s="16" t="n"/>
-      <c r="AF12" s="16" t="n"/>
-      <c r="AG12" s="14" t="n"/>
-      <c r="AH12" s="16" t="n"/>
-      <c r="AI12" s="16" t="n"/>
-      <c r="AJ12" s="107" t="n"/>
-      <c r="AK12" s="16" t="n"/>
-      <c r="AL12" s="17" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="11" t="n"/>
+      <c r="J12" s="11" t="n"/>
+      <c r="K12" s="11" t="n"/>
+      <c r="L12" s="11" t="n"/>
+      <c r="M12" s="11" t="n"/>
+      <c r="N12" s="11" t="n"/>
+      <c r="O12" s="11" t="n"/>
+      <c r="P12" s="13" t="n"/>
+      <c r="Q12" s="104" t="n"/>
+      <c r="R12" s="151" t="n"/>
+      <c r="S12" s="152" t="n"/>
+      <c r="T12" s="94" t="n"/>
+      <c r="U12" s="94" t="n"/>
+      <c r="V12" s="94" t="n"/>
+      <c r="W12" s="94" t="n"/>
+      <c r="X12" s="94" t="n"/>
+      <c r="Y12" s="94" t="n"/>
+      <c r="Z12" s="94" t="n"/>
+      <c r="AA12" s="94" t="n"/>
+      <c r="AB12" s="94" t="n"/>
+      <c r="AC12" s="94" t="n"/>
+      <c r="AD12" s="94" t="n"/>
+      <c r="AE12" s="94" t="n"/>
+      <c r="AF12" s="94" t="n"/>
+      <c r="AG12" s="95" t="n"/>
+      <c r="AH12" s="94" t="n"/>
+      <c r="AI12" s="94" t="n"/>
+      <c r="AJ12" s="92" t="n"/>
+      <c r="AK12" s="94" t="n"/>
+      <c r="AL12" s="14" t="n"/>
     </row>
     <row r="13" ht="104.25" customHeight="1">
-      <c r="A13" s="18" t="n"/>
-      <c r="B13" s="18" t="n"/>
-      <c r="C13" s="19" t="n"/>
-      <c r="D13" s="19" t="n"/>
-      <c r="E13" s="14" t="n"/>
-      <c r="F13" s="19" t="n"/>
-      <c r="G13" s="19" t="n"/>
-      <c r="H13" s="19" t="n"/>
-      <c r="I13" s="19" t="n"/>
-      <c r="J13" s="19" t="n"/>
-      <c r="K13" s="19" t="n"/>
-      <c r="L13" s="19" t="n"/>
-      <c r="M13" s="19" t="n"/>
-      <c r="N13" s="19" t="n"/>
-      <c r="O13" s="19" t="n"/>
-      <c r="P13" s="105" t="n"/>
-      <c r="Q13" s="151" t="n"/>
-      <c r="R13" s="152" t="n"/>
-      <c r="S13" s="153" t="n"/>
-      <c r="T13" s="19" t="n"/>
-      <c r="U13" s="19" t="n"/>
-      <c r="V13" s="19" t="n"/>
-      <c r="W13" s="19" t="n"/>
-      <c r="X13" s="19" t="n"/>
-      <c r="Y13" s="16" t="n"/>
-      <c r="Z13" s="16" t="n"/>
-      <c r="AA13" s="19" t="n"/>
-      <c r="AB13" s="19" t="n"/>
-      <c r="AC13" s="19" t="n"/>
-      <c r="AD13" s="19" t="n"/>
-      <c r="AE13" s="19" t="n"/>
-      <c r="AF13" s="19" t="n"/>
-      <c r="AG13" s="20" t="n"/>
-      <c r="AH13" s="16" t="n"/>
-      <c r="AI13" s="16" t="n"/>
-      <c r="AJ13" s="107" t="n"/>
-      <c r="AK13" s="16" t="n"/>
-      <c r="AL13" s="17" t="n"/>
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="16" t="n"/>
+      <c r="I13" s="16" t="n"/>
+      <c r="J13" s="16" t="n"/>
+      <c r="K13" s="16" t="n"/>
+      <c r="L13" s="16" t="n"/>
+      <c r="M13" s="16" t="n"/>
+      <c r="N13" s="16" t="n"/>
+      <c r="O13" s="16" t="n"/>
+      <c r="P13" s="13" t="n"/>
+      <c r="Q13" s="153" t="n"/>
+      <c r="R13" s="154" t="n"/>
+      <c r="S13" s="155" t="n"/>
+      <c r="T13" s="96" t="n"/>
+      <c r="U13" s="96" t="n"/>
+      <c r="V13" s="96" t="n"/>
+      <c r="W13" s="96" t="n"/>
+      <c r="X13" s="96" t="n"/>
+      <c r="Y13" s="94" t="n"/>
+      <c r="Z13" s="94" t="n"/>
+      <c r="AA13" s="96" t="n"/>
+      <c r="AB13" s="96" t="n"/>
+      <c r="AC13" s="96" t="n"/>
+      <c r="AD13" s="96" t="n"/>
+      <c r="AE13" s="96" t="n"/>
+      <c r="AF13" s="96" t="n"/>
+      <c r="AG13" s="97" t="n"/>
+      <c r="AH13" s="94" t="n"/>
+      <c r="AI13" s="94" t="n"/>
+      <c r="AJ13" s="92" t="n"/>
+      <c r="AK13" s="94" t="n"/>
+      <c r="AL13" s="14" t="n"/>
     </row>
     <row r="14" ht="104.25" customHeight="1">
       <c r="A14" s="10" t="n"/>
       <c r="B14" s="10" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="16" t="n"/>
-      <c r="I14" s="16" t="n"/>
-      <c r="J14" s="16" t="n"/>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="16" t="n"/>
-      <c r="M14" s="16" t="n"/>
-      <c r="N14" s="16" t="n"/>
-      <c r="O14" s="16" t="n"/>
-      <c r="P14" s="105" t="n"/>
-      <c r="Q14" s="111" t="n"/>
-      <c r="R14" s="149" t="n"/>
-      <c r="S14" s="150" t="n"/>
-      <c r="T14" s="16" t="n"/>
-      <c r="U14" s="16" t="n"/>
-      <c r="V14" s="16" t="n"/>
-      <c r="W14" s="16" t="n"/>
-      <c r="X14" s="16" t="n"/>
-      <c r="Y14" s="16" t="n"/>
-      <c r="Z14" s="16" t="n"/>
-      <c r="AA14" s="16" t="n"/>
-      <c r="AB14" s="16" t="n"/>
-      <c r="AC14" s="16" t="n"/>
-      <c r="AD14" s="16" t="n"/>
-      <c r="AE14" s="16" t="n"/>
-      <c r="AF14" s="16" t="n"/>
-      <c r="AG14" s="14" t="n"/>
-      <c r="AH14" s="16" t="n"/>
-      <c r="AI14" s="16" t="n"/>
-      <c r="AJ14" s="107" t="n"/>
-      <c r="AK14" s="16" t="n"/>
-      <c r="AL14" s="17" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="11" t="n"/>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="11" t="n"/>
+      <c r="K14" s="11" t="n"/>
+      <c r="L14" s="11" t="n"/>
+      <c r="M14" s="11" t="n"/>
+      <c r="N14" s="11" t="n"/>
+      <c r="O14" s="11" t="n"/>
+      <c r="P14" s="13" t="n"/>
+      <c r="Q14" s="104" t="n"/>
+      <c r="R14" s="151" t="n"/>
+      <c r="S14" s="152" t="n"/>
+      <c r="T14" s="94" t="n"/>
+      <c r="U14" s="94" t="n"/>
+      <c r="V14" s="94" t="n"/>
+      <c r="W14" s="94" t="n"/>
+      <c r="X14" s="94" t="n"/>
+      <c r="Y14" s="94" t="n"/>
+      <c r="Z14" s="94" t="n"/>
+      <c r="AA14" s="94" t="n"/>
+      <c r="AB14" s="94" t="n"/>
+      <c r="AC14" s="94" t="n"/>
+      <c r="AD14" s="94" t="n"/>
+      <c r="AE14" s="94" t="n"/>
+      <c r="AF14" s="94" t="n"/>
+      <c r="AG14" s="95" t="n"/>
+      <c r="AH14" s="94" t="n"/>
+      <c r="AI14" s="94" t="n"/>
+      <c r="AJ14" s="92" t="n"/>
+      <c r="AK14" s="94" t="n"/>
+      <c r="AL14" s="14" t="n"/>
     </row>
     <row r="15" ht="73.5" customHeight="1" thickBot="1">
       <c r="A15" s="4" t="n"/>
-      <c r="L15" s="95" t="n"/>
+      <c r="L15" s="60" t="n"/>
       <c r="Q15" s="5" t="n"/>
       <c r="R15" s="5" t="n"/>
-      <c r="S15" s="28" t="n"/>
+      <c r="S15" s="22" t="n"/>
       <c r="T15" s="5" t="n"/>
       <c r="U15" s="5" t="n"/>
       <c r="V15" s="5" t="n"/>
@@ -2367,894 +2443,894 @@
       <c r="AJ15" s="5" t="n"/>
     </row>
     <row r="16" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A16" s="98" t="inlineStr">
+      <c r="A16" s="53" t="inlineStr">
         <is>
           <t>НОМЕР И НАИМЕНОВАНИЕ ОТЛИВКИ</t>
         </is>
       </c>
-      <c r="B16" s="100" t="inlineStr">
+      <c r="B16" s="55" t="inlineStr">
         <is>
           <t>ГОДНЫЕ, шт.</t>
         </is>
       </c>
-      <c r="C16" s="112" t="inlineStr">
+      <c r="C16" s="41" t="inlineStr">
         <is>
           <t>ОКОНЧАТЕЛЬНЫЙ БРАК, шт.</t>
         </is>
       </c>
-      <c r="D16" s="130" t="n"/>
-      <c r="E16" s="130" t="n"/>
-      <c r="F16" s="130" t="n"/>
-      <c r="G16" s="130" t="n"/>
-      <c r="H16" s="130" t="n"/>
-      <c r="I16" s="130" t="n"/>
-      <c r="J16" s="130" t="n"/>
-      <c r="K16" s="130" t="n"/>
-      <c r="L16" s="130" t="n"/>
-      <c r="M16" s="130" t="n"/>
-      <c r="N16" s="130" t="n"/>
-      <c r="O16" s="130" t="n"/>
-      <c r="P16" s="130" t="n"/>
-      <c r="Q16" s="130" t="n"/>
-      <c r="R16" s="130" t="n"/>
-      <c r="S16" s="130" t="n"/>
-      <c r="T16" s="130" t="n"/>
-      <c r="U16" s="130" t="n"/>
-      <c r="V16" s="130" t="n"/>
-      <c r="W16" s="130" t="n"/>
-      <c r="X16" s="131" t="n"/>
-      <c r="Y16" s="154" t="inlineStr">
+      <c r="D16" s="132" t="n"/>
+      <c r="E16" s="132" t="n"/>
+      <c r="F16" s="132" t="n"/>
+      <c r="G16" s="132" t="n"/>
+      <c r="H16" s="132" t="n"/>
+      <c r="I16" s="132" t="n"/>
+      <c r="J16" s="132" t="n"/>
+      <c r="K16" s="132" t="n"/>
+      <c r="L16" s="132" t="n"/>
+      <c r="M16" s="132" t="n"/>
+      <c r="N16" s="132" t="n"/>
+      <c r="O16" s="132" t="n"/>
+      <c r="P16" s="132" t="n"/>
+      <c r="Q16" s="132" t="n"/>
+      <c r="R16" s="132" t="n"/>
+      <c r="S16" s="132" t="n"/>
+      <c r="T16" s="132" t="n"/>
+      <c r="U16" s="132" t="n"/>
+      <c r="V16" s="132" t="n"/>
+      <c r="W16" s="132" t="n"/>
+      <c r="X16" s="133" t="n"/>
+      <c r="Y16" s="156" t="inlineStr">
         <is>
           <t>2 СОРТ, шт.</t>
         </is>
       </c>
-      <c r="Z16" s="130" t="n"/>
-      <c r="AA16" s="130" t="n"/>
-      <c r="AB16" s="155" t="n"/>
-      <c r="AC16" s="156" t="inlineStr">
+      <c r="Z16" s="132" t="n"/>
+      <c r="AA16" s="132" t="n"/>
+      <c r="AB16" s="157" t="n"/>
+      <c r="AC16" s="158" t="inlineStr">
         <is>
           <t>НЕДОСТАЧА, 
 шт.</t>
         </is>
       </c>
-      <c r="AD16" s="133" t="n"/>
-      <c r="AE16" s="156" t="inlineStr">
+      <c r="AD16" s="135" t="n"/>
+      <c r="AE16" s="158" t="inlineStr">
         <is>
           <t>НОМЕРА ПЛАВОК</t>
         </is>
       </c>
-      <c r="AF16" s="132" t="n"/>
-      <c r="AG16" s="132" t="n"/>
-      <c r="AH16" s="132" t="n"/>
-      <c r="AI16" s="132" t="n"/>
-      <c r="AJ16" s="132" t="n"/>
-      <c r="AK16" s="133" t="n"/>
+      <c r="AF16" s="134" t="n"/>
+      <c r="AG16" s="134" t="n"/>
+      <c r="AH16" s="134" t="n"/>
+      <c r="AI16" s="134" t="n"/>
+      <c r="AJ16" s="134" t="n"/>
+      <c r="AK16" s="135" t="n"/>
     </row>
     <row r="17" ht="135.75" customHeight="1" thickBot="1">
-      <c r="A17" s="157" t="n"/>
-      <c r="B17" s="157" t="n"/>
-      <c r="C17" s="40" t="inlineStr">
+      <c r="A17" s="159" t="n"/>
+      <c r="B17" s="159" t="n"/>
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>Раковины на корпусе</t>
         </is>
       </c>
-      <c r="D17" s="41" t="inlineStr">
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>Коробление</t>
         </is>
       </c>
-      <c r="E17" s="41" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t>Спай</t>
         </is>
       </c>
-      <c r="F17" s="41" t="inlineStr">
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>Трещины</t>
         </is>
       </c>
-      <c r="G17" s="41" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>Недолив</t>
         </is>
       </c>
-      <c r="H17" s="41" t="inlineStr">
+      <c r="H17" s="25" t="inlineStr">
         <is>
           <t>Пригар песка</t>
         </is>
       </c>
-      <c r="I17" s="41" t="inlineStr">
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t>Пористость</t>
         </is>
       </c>
-      <c r="J17" s="41" t="inlineStr">
+      <c r="J17" s="25" t="inlineStr">
         <is>
           <t>Вырыв</t>
         </is>
       </c>
-      <c r="K17" s="41" t="inlineStr">
+      <c r="K17" s="25" t="inlineStr">
         <is>
           <t>Скол</t>
         </is>
       </c>
-      <c r="L17" s="41" t="inlineStr">
+      <c r="L17" s="25" t="inlineStr">
         <is>
           <t>Слом</t>
         </is>
       </c>
-      <c r="M17" s="41" t="inlineStr">
+      <c r="M17" s="25" t="inlineStr">
         <is>
           <t>Зарез литейный</t>
         </is>
       </c>
-      <c r="N17" s="41" t="inlineStr">
+      <c r="N17" s="25" t="inlineStr">
         <is>
           <t>Зарез пеномодельный</t>
         </is>
       </c>
-      <c r="O17" s="41" t="inlineStr">
+      <c r="O17" s="25" t="inlineStr">
         <is>
           <t>Нарушение геометрии</t>
         </is>
       </c>
-      <c r="P17" s="41" t="inlineStr">
+      <c r="P17" s="25" t="inlineStr">
         <is>
           <t>Рыхлота</t>
         </is>
       </c>
-      <c r="Q17" s="41" t="inlineStr">
+      <c r="Q17" s="25" t="inlineStr">
         <is>
           <t>Непрклей</t>
         </is>
       </c>
-      <c r="R17" s="41" t="inlineStr">
+      <c r="R17" s="25" t="inlineStr">
         <is>
           <t>Брак п/м</t>
         </is>
       </c>
-      <c r="S17" s="41" t="inlineStr">
+      <c r="S17" s="25" t="inlineStr">
         <is>
           <t>Наплыв металла</t>
         </is>
       </c>
-      <c r="T17" s="41" t="inlineStr">
+      <c r="T17" s="25" t="inlineStr">
         <is>
           <t>Несоответствие размеров</t>
         </is>
       </c>
-      <c r="U17" s="41" t="inlineStr">
+      <c r="U17" s="25" t="inlineStr">
         <is>
           <t>Несоответствие внешнего вида</t>
         </is>
       </c>
-      <c r="V17" s="41" t="inlineStr">
+      <c r="V17" s="25" t="inlineStr">
         <is>
           <t>Нарушение маркировки</t>
         </is>
       </c>
-      <c r="W17" s="41" t="inlineStr">
+      <c r="W17" s="25" t="inlineStr">
         <is>
           <t>Неслитина</t>
         </is>
       </c>
-      <c r="X17" s="56" t="inlineStr">
+      <c r="X17" s="33" t="inlineStr">
         <is>
           <t>Прочее</t>
         </is>
       </c>
-      <c r="Y17" s="40" t="inlineStr">
+      <c r="Y17" s="24" t="inlineStr">
         <is>
           <t>Раковины</t>
         </is>
       </c>
-      <c r="Z17" s="41" t="inlineStr">
+      <c r="Z17" s="25" t="inlineStr">
         <is>
           <t>Зарез литейный</t>
         </is>
       </c>
-      <c r="AA17" s="41" t="inlineStr">
+      <c r="AA17" s="25" t="inlineStr">
         <is>
           <t>Зарез пеномодельный</t>
         </is>
       </c>
-      <c r="AB17" s="42" t="inlineStr">
+      <c r="AB17" s="26" t="inlineStr">
         <is>
           <t>Прочее</t>
         </is>
       </c>
-      <c r="AC17" s="142" t="n"/>
-      <c r="AD17" s="144" t="n"/>
-      <c r="AE17" s="142" t="n"/>
-      <c r="AF17" s="143" t="n"/>
-      <c r="AG17" s="143" t="n"/>
-      <c r="AH17" s="143" t="n"/>
-      <c r="AI17" s="143" t="n"/>
-      <c r="AJ17" s="143" t="n"/>
-      <c r="AK17" s="144" t="n"/>
-      <c r="AL17" s="22" t="n"/>
-      <c r="AM17" s="23" t="n"/>
+      <c r="AC17" s="144" t="n"/>
+      <c r="AD17" s="146" t="n"/>
+      <c r="AE17" s="144" t="n"/>
+      <c r="AF17" s="145" t="n"/>
+      <c r="AG17" s="145" t="n"/>
+      <c r="AH17" s="145" t="n"/>
+      <c r="AI17" s="145" t="n"/>
+      <c r="AJ17" s="145" t="n"/>
+      <c r="AK17" s="146" t="n"/>
+      <c r="AL17" s="18" t="n"/>
+      <c r="AM17" s="19" t="n"/>
       <c r="AN17" s="5" t="n"/>
-      <c r="BK17" s="28" t="n"/>
+      <c r="BK17" s="22" t="n"/>
     </row>
     <row r="18" hidden="1" ht="99" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Наименование_отливки</t>
         </is>
       </c>
-      <c r="B18" s="55" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>Контроль_принято</t>
         </is>
       </c>
-      <c r="C18" s="55" t="inlineStr">
+      <c r="C18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_раковины</t>
         </is>
       </c>
-      <c r="D18" s="55" t="inlineStr">
+      <c r="D18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_коробление</t>
         </is>
       </c>
-      <c r="E18" s="55" t="inlineStr">
+      <c r="E18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_спай</t>
         </is>
       </c>
-      <c r="F18" s="55" t="inlineStr">
+      <c r="F18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_трещины</t>
         </is>
       </c>
-      <c r="G18" s="55" t="inlineStr">
+      <c r="G18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_недолив</t>
         </is>
       </c>
-      <c r="H18" s="55" t="inlineStr">
+      <c r="H18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_пригар_песка</t>
         </is>
       </c>
-      <c r="I18" s="55" t="inlineStr">
+      <c r="I18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_пористость</t>
         </is>
       </c>
-      <c r="J18" s="55" t="inlineStr">
+      <c r="J18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_вырыв</t>
         </is>
       </c>
-      <c r="K18" s="55" t="inlineStr">
+      <c r="K18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_скол</t>
         </is>
       </c>
-      <c r="L18" s="55" t="inlineStr">
+      <c r="L18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_слом</t>
         </is>
       </c>
-      <c r="M18" s="55" t="inlineStr">
+      <c r="M18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_зарез_литейный</t>
         </is>
       </c>
-      <c r="N18" s="55" t="inlineStr">
+      <c r="N18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_зарез_пеномодельный</t>
         </is>
       </c>
-      <c r="O18" s="55" t="inlineStr">
+      <c r="O18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_нарушение_геометрии</t>
         </is>
       </c>
-      <c r="P18" s="55" t="inlineStr">
+      <c r="P18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_рыхлота</t>
         </is>
       </c>
-      <c r="Q18" s="55" t="inlineStr">
+      <c r="Q18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_непроклей</t>
         </is>
       </c>
-      <c r="R18" s="55" t="inlineStr">
+      <c r="R18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_пеномодель</t>
         </is>
       </c>
-      <c r="S18" s="55" t="inlineStr">
+      <c r="S18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_наплыв_металла</t>
         </is>
       </c>
-      <c r="T18" s="55" t="inlineStr">
+      <c r="T18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_несоответствие_размеров</t>
         </is>
       </c>
-      <c r="U18" s="55" t="inlineStr">
+      <c r="U18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_несоответствие_внешнего_вида</t>
         </is>
       </c>
-      <c r="V18" s="55" t="inlineStr">
+      <c r="V18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_нарушение_маркировки</t>
         </is>
       </c>
-      <c r="W18" s="55" t="inlineStr">
+      <c r="W18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_неслитина</t>
         </is>
       </c>
-      <c r="X18" s="57" t="inlineStr">
+      <c r="X18" s="34" t="inlineStr">
         <is>
           <t>Окончательный_брак_прочее</t>
         </is>
       </c>
-      <c r="Y18" s="61" t="inlineStr">
+      <c r="Y18" s="35" t="inlineStr">
         <is>
           <t>Второй_сорт_раковины</t>
         </is>
       </c>
-      <c r="Z18" s="55" t="inlineStr">
+      <c r="Z18" s="32" t="inlineStr">
         <is>
           <t>Второй_сорт_зарез_литейный</t>
         </is>
       </c>
-      <c r="AA18" s="55" t="inlineStr">
+      <c r="AA18" s="32" t="inlineStr">
         <is>
           <t>Второй_сорт_зарез_пеномодельный</t>
         </is>
       </c>
-      <c r="AB18" s="39" t="n"/>
-      <c r="AC18" s="126" t="n"/>
-      <c r="AD18" s="137" t="n"/>
-      <c r="AE18" s="158" t="inlineStr">
+      <c r="AB18" s="23" t="n"/>
+      <c r="AC18" s="38" t="n"/>
+      <c r="AD18" s="139" t="n"/>
+      <c r="AE18" s="160" t="inlineStr">
         <is>
           <t>Номер_плавки</t>
         </is>
       </c>
-      <c r="AF18" s="128" t="n"/>
-      <c r="AG18" s="128" t="n"/>
-      <c r="AH18" s="128" t="n"/>
-      <c r="AI18" s="128" t="n"/>
-      <c r="AJ18" s="128" t="n"/>
-      <c r="AK18" s="137" t="n"/>
-      <c r="AL18" s="27" t="n"/>
-      <c r="AM18" s="28" t="n"/>
+      <c r="AF18" s="130" t="n"/>
+      <c r="AG18" s="130" t="n"/>
+      <c r="AH18" s="130" t="n"/>
+      <c r="AI18" s="130" t="n"/>
+      <c r="AJ18" s="130" t="n"/>
+      <c r="AK18" s="139" t="n"/>
+      <c r="AL18" s="21" t="n"/>
+      <c r="AM18" s="22" t="n"/>
       <c r="AN18" s="5" t="n"/>
-      <c r="BK18" s="28" t="n"/>
+      <c r="BK18" s="22" t="n"/>
     </row>
     <row r="19" ht="99" customHeight="1">
-      <c r="A19" s="32" t="inlineStr">
+      <c r="A19" s="108" t="inlineStr">
         <is>
           <t>Вороток</t>
         </is>
       </c>
-      <c r="B19" s="32" t="n">
+      <c r="B19" s="108" t="n">
         <v>584</v>
       </c>
-      <c r="C19" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="55" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" s="55" t="n">
-        <v>2</v>
-      </c>
-      <c r="N19" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="O19" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="P19" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="S19" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="W19" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="X19" s="58" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y19" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z19" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA19" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB19" s="34" t="n"/>
-      <c r="AC19" s="65" t="n"/>
-      <c r="AD19" s="150" t="n"/>
-      <c r="AE19" s="159" t="inlineStr">
+      <c r="C19" s="116" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="116" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="116" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="116" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="116" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="116" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" s="116" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="116" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" s="116" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" s="116" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" s="116" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" s="116" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="116" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" s="116" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" s="108" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" s="116" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" s="116" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="116" t="n">
+        <v>2</v>
+      </c>
+      <c r="W19" s="116" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" s="110" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y19" s="120" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z19" s="121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA19" s="108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB19" s="113" t="n"/>
+      <c r="AC19" s="106" t="n"/>
+      <c r="AD19" s="152" t="n"/>
+      <c r="AE19" s="108" t="inlineStr">
         <is>
           <t>5-107/25</t>
         </is>
       </c>
-      <c r="AF19" s="149" t="n"/>
-      <c r="AG19" s="149" t="n"/>
-      <c r="AH19" s="149" t="n"/>
-      <c r="AI19" s="149" t="n"/>
-      <c r="AJ19" s="149" t="n"/>
-      <c r="AK19" s="150" t="n"/>
-      <c r="AL19" s="27" t="n"/>
-      <c r="AM19" s="28" t="n"/>
+      <c r="AF19" s="151" t="n"/>
+      <c r="AG19" s="151" t="n"/>
+      <c r="AH19" s="151" t="n"/>
+      <c r="AI19" s="151" t="n"/>
+      <c r="AJ19" s="151" t="n"/>
+      <c r="AK19" s="152" t="n"/>
+      <c r="AL19" s="21" t="n"/>
+      <c r="AM19" s="22" t="n"/>
       <c r="AN19" s="5" t="n"/>
-      <c r="BK19" s="28" t="n"/>
+      <c r="BK19" s="22" t="n"/>
     </row>
     <row r="20" ht="99" customHeight="1">
-      <c r="A20" s="32" t="inlineStr">
+      <c r="A20" s="108" t="inlineStr">
         <is>
           <t>Ригель</t>
         </is>
       </c>
-      <c r="B20" s="44" t="n">
+      <c r="B20" s="114" t="n">
         <v>1217</v>
       </c>
-      <c r="C20" s="46" t="n">
+      <c r="C20" s="115" t="n">
         <v>43</v>
       </c>
-      <c r="D20" s="31" t="n">
+      <c r="D20" s="116" t="n">
         <v>44</v>
       </c>
-      <c r="E20" s="31" t="n">
+      <c r="E20" s="116" t="n">
         <v>43</v>
       </c>
-      <c r="F20" s="31" t="n">
+      <c r="F20" s="116" t="n">
         <v>44</v>
       </c>
-      <c r="G20" s="31" t="n">
+      <c r="G20" s="116" t="n">
         <v>44</v>
       </c>
-      <c r="H20" s="31" t="n">
+      <c r="H20" s="116" t="n">
         <v>43</v>
       </c>
-      <c r="I20" s="31" t="n">
+      <c r="I20" s="116" t="n">
         <v>44</v>
       </c>
-      <c r="J20" s="31" t="n">
+      <c r="J20" s="116" t="n">
         <v>43</v>
       </c>
-      <c r="K20" s="31" t="n">
+      <c r="K20" s="116" t="n">
         <v>44</v>
       </c>
-      <c r="L20" s="31" t="n">
+      <c r="L20" s="116" t="n">
         <v>43</v>
       </c>
-      <c r="M20" s="31" t="n">
+      <c r="M20" s="116" t="n">
         <v>44</v>
       </c>
-      <c r="N20" s="31" t="n">
+      <c r="N20" s="116" t="n">
         <v>43</v>
       </c>
-      <c r="O20" s="31" t="n">
+      <c r="O20" s="116" t="n">
         <v>44</v>
       </c>
-      <c r="P20" s="31" t="n">
+      <c r="P20" s="116" t="n">
         <v>43</v>
       </c>
-      <c r="Q20" s="31" t="n">
+      <c r="Q20" s="116" t="n">
         <v>44</v>
       </c>
-      <c r="R20" s="31" t="n">
+      <c r="R20" s="116" t="n">
         <v>43</v>
       </c>
-      <c r="S20" s="31" t="n">
+      <c r="S20" s="116" t="n">
         <v>44</v>
       </c>
-      <c r="T20" s="31" t="n">
+      <c r="T20" s="116" t="n">
         <v>43</v>
       </c>
-      <c r="U20" s="31" t="n">
+      <c r="U20" s="116" t="n">
         <v>44</v>
       </c>
-      <c r="V20" s="31" t="n">
+      <c r="V20" s="116" t="n">
         <v>43</v>
       </c>
-      <c r="W20" s="31" t="n">
+      <c r="W20" s="116" t="n">
         <v>44</v>
       </c>
-      <c r="X20" s="59" t="n">
+      <c r="X20" s="117" t="n">
         <v>43</v>
       </c>
-      <c r="Y20" s="45" t="n">
+      <c r="Y20" s="120" t="n">
         <v>43</v>
       </c>
-      <c r="Z20" s="26" t="n">
+      <c r="Z20" s="121" t="n">
         <v>44</v>
       </c>
-      <c r="AA20" s="32" t="n">
+      <c r="AA20" s="108" t="n">
         <v>43</v>
       </c>
-      <c r="AB20" s="34" t="n"/>
-      <c r="AC20" s="65" t="n"/>
-      <c r="AD20" s="150" t="n"/>
-      <c r="AE20" s="159" t="inlineStr">
+      <c r="AB20" s="113" t="n"/>
+      <c r="AC20" s="106" t="n"/>
+      <c r="AD20" s="152" t="n"/>
+      <c r="AE20" s="108" t="inlineStr">
         <is>
           <t>5-134/25, 5-133/25, 5-132/25</t>
         </is>
       </c>
-      <c r="AF20" s="149" t="n"/>
-      <c r="AG20" s="149" t="n"/>
-      <c r="AH20" s="149" t="n"/>
-      <c r="AI20" s="149" t="n"/>
-      <c r="AJ20" s="149" t="n"/>
-      <c r="AK20" s="150" t="n"/>
-      <c r="AL20" s="27" t="n"/>
-      <c r="AM20" s="28" t="n"/>
+      <c r="AF20" s="151" t="n"/>
+      <c r="AG20" s="151" t="n"/>
+      <c r="AH20" s="151" t="n"/>
+      <c r="AI20" s="151" t="n"/>
+      <c r="AJ20" s="151" t="n"/>
+      <c r="AK20" s="152" t="n"/>
+      <c r="AL20" s="21" t="n"/>
+      <c r="AM20" s="22" t="n"/>
       <c r="AN20" s="5" t="n"/>
-      <c r="BK20" s="28" t="n"/>
+      <c r="BK20" s="22" t="n"/>
     </row>
     <row r="21" ht="99" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="118" t="inlineStr">
         <is>
           <t>Ригель optima</t>
         </is>
       </c>
-      <c r="B21" s="43" t="n">
+      <c r="B21" s="119" t="n">
         <v>1835</v>
       </c>
-      <c r="C21" s="45" t="n">
-        <v>4</v>
-      </c>
-      <c r="D21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="E21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="G21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="I21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="K21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="L21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="M21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="N21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="O21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="P21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="R21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="S21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="T21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="U21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="V21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="W21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="X21" s="59" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y21" s="45" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z21" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA21" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB21" s="34" t="n"/>
-      <c r="AC21" s="65" t="n"/>
-      <c r="AD21" s="150" t="n"/>
-      <c r="AE21" s="159" t="inlineStr">
+      <c r="C21" s="120" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="M21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="P21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="R21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="S21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="V21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="W21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="X21" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="120" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA21" s="108" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB21" s="113" t="n"/>
+      <c r="AC21" s="106" t="n"/>
+      <c r="AD21" s="152" t="n"/>
+      <c r="AE21" s="108" t="inlineStr">
         <is>
           <t>3-332/25, 4-193/25</t>
         </is>
       </c>
-      <c r="AF21" s="149" t="n"/>
-      <c r="AG21" s="149" t="n"/>
-      <c r="AH21" s="149" t="n"/>
-      <c r="AI21" s="149" t="n"/>
-      <c r="AJ21" s="149" t="n"/>
-      <c r="AK21" s="150" t="n"/>
-      <c r="AL21" s="27" t="n"/>
-      <c r="AM21" s="28" t="n"/>
+      <c r="AF21" s="151" t="n"/>
+      <c r="AG21" s="151" t="n"/>
+      <c r="AH21" s="151" t="n"/>
+      <c r="AI21" s="151" t="n"/>
+      <c r="AJ21" s="151" t="n"/>
+      <c r="AK21" s="152" t="n"/>
+      <c r="AL21" s="21" t="n"/>
+      <c r="AM21" s="22" t="n"/>
       <c r="AN21" s="5" t="n"/>
-      <c r="BK21" s="28" t="n"/>
+      <c r="BK21" s="22" t="n"/>
     </row>
     <row r="22" ht="99" customHeight="1">
-      <c r="A22" s="32" t="n"/>
-      <c r="B22" s="44" t="n"/>
-      <c r="C22" s="46" t="n"/>
-      <c r="D22" s="31" t="n"/>
-      <c r="E22" s="31" t="n"/>
-      <c r="F22" s="31" t="n"/>
-      <c r="G22" s="31" t="n"/>
-      <c r="H22" s="31" t="n"/>
-      <c r="I22" s="31" t="n"/>
-      <c r="J22" s="31" t="n"/>
-      <c r="K22" s="31" t="n"/>
-      <c r="L22" s="31" t="n"/>
-      <c r="M22" s="31" t="n"/>
-      <c r="N22" s="31" t="n"/>
-      <c r="O22" s="31" t="n"/>
-      <c r="P22" s="31" t="n"/>
-      <c r="Q22" s="31" t="n"/>
-      <c r="R22" s="31" t="n"/>
-      <c r="S22" s="31" t="n"/>
-      <c r="T22" s="31" t="n"/>
-      <c r="U22" s="31" t="n"/>
-      <c r="V22" s="31" t="n"/>
-      <c r="W22" s="31" t="n"/>
-      <c r="X22" s="59" t="n"/>
-      <c r="Y22" s="45" t="n"/>
-      <c r="Z22" s="26" t="n"/>
-      <c r="AA22" s="32" t="n"/>
-      <c r="AB22" s="34" t="n"/>
-      <c r="AC22" s="65" t="n"/>
-      <c r="AD22" s="150" t="n"/>
-      <c r="AE22" s="159" t="n"/>
-      <c r="AF22" s="149" t="n"/>
-      <c r="AG22" s="149" t="n"/>
-      <c r="AH22" s="149" t="n"/>
-      <c r="AI22" s="149" t="n"/>
-      <c r="AJ22" s="149" t="n"/>
-      <c r="AK22" s="150" t="n"/>
-      <c r="AL22" s="27" t="n"/>
-      <c r="AM22" s="28" t="n"/>
+      <c r="A22" s="108" t="n"/>
+      <c r="B22" s="114" t="n"/>
+      <c r="C22" s="115" t="n"/>
+      <c r="D22" s="116" t="n"/>
+      <c r="E22" s="116" t="n"/>
+      <c r="F22" s="116" t="n"/>
+      <c r="G22" s="116" t="n"/>
+      <c r="H22" s="116" t="n"/>
+      <c r="I22" s="116" t="n"/>
+      <c r="J22" s="116" t="n"/>
+      <c r="K22" s="116" t="n"/>
+      <c r="L22" s="116" t="n"/>
+      <c r="M22" s="116" t="n"/>
+      <c r="N22" s="116" t="n"/>
+      <c r="O22" s="116" t="n"/>
+      <c r="P22" s="116" t="n"/>
+      <c r="Q22" s="116" t="n"/>
+      <c r="R22" s="116" t="n"/>
+      <c r="S22" s="116" t="n"/>
+      <c r="T22" s="116" t="n"/>
+      <c r="U22" s="116" t="n"/>
+      <c r="V22" s="116" t="n"/>
+      <c r="W22" s="116" t="n"/>
+      <c r="X22" s="117" t="n"/>
+      <c r="Y22" s="120" t="n"/>
+      <c r="Z22" s="121" t="n"/>
+      <c r="AA22" s="108" t="n"/>
+      <c r="AB22" s="113" t="n"/>
+      <c r="AC22" s="106" t="n"/>
+      <c r="AD22" s="152" t="n"/>
+      <c r="AE22" s="108" t="n"/>
+      <c r="AF22" s="151" t="n"/>
+      <c r="AG22" s="151" t="n"/>
+      <c r="AH22" s="151" t="n"/>
+      <c r="AI22" s="151" t="n"/>
+      <c r="AJ22" s="151" t="n"/>
+      <c r="AK22" s="152" t="n"/>
+      <c r="AL22" s="21" t="n"/>
+      <c r="AM22" s="22" t="n"/>
       <c r="AN22" s="5" t="n"/>
-      <c r="BK22" s="28" t="n"/>
+      <c r="BK22" s="22" t="n"/>
     </row>
     <row r="23" ht="99" customHeight="1">
-      <c r="A23" s="32" t="n"/>
-      <c r="B23" s="44" t="n"/>
-      <c r="C23" s="46" t="n"/>
-      <c r="D23" s="31" t="n"/>
-      <c r="E23" s="31" t="n"/>
-      <c r="F23" s="31" t="n"/>
-      <c r="G23" s="31" t="n"/>
-      <c r="H23" s="31" t="n"/>
-      <c r="I23" s="31" t="n"/>
-      <c r="J23" s="31" t="n"/>
-      <c r="K23" s="31" t="n"/>
-      <c r="L23" s="31" t="n"/>
-      <c r="M23" s="31" t="n"/>
-      <c r="N23" s="31" t="n"/>
-      <c r="O23" s="31" t="n"/>
-      <c r="P23" s="31" t="n"/>
-      <c r="Q23" s="31" t="n"/>
-      <c r="R23" s="31" t="n"/>
-      <c r="S23" s="31" t="n"/>
-      <c r="T23" s="31" t="n"/>
-      <c r="U23" s="31" t="n"/>
-      <c r="V23" s="31" t="n"/>
-      <c r="W23" s="31" t="n"/>
-      <c r="X23" s="59" t="n"/>
-      <c r="Y23" s="45" t="n"/>
-      <c r="Z23" s="26" t="n"/>
-      <c r="AA23" s="32" t="n"/>
-      <c r="AB23" s="34" t="n"/>
-      <c r="AC23" s="65" t="n"/>
-      <c r="AD23" s="150" t="n"/>
-      <c r="AE23" s="159" t="n"/>
-      <c r="AF23" s="149" t="n"/>
-      <c r="AG23" s="149" t="n"/>
-      <c r="AH23" s="149" t="n"/>
-      <c r="AI23" s="149" t="n"/>
-      <c r="AJ23" s="149" t="n"/>
-      <c r="AK23" s="150" t="n"/>
-      <c r="AL23" s="27" t="n"/>
-      <c r="AM23" s="28" t="n"/>
+      <c r="A23" s="108" t="n"/>
+      <c r="B23" s="114" t="n"/>
+      <c r="C23" s="115" t="n"/>
+      <c r="D23" s="116" t="n"/>
+      <c r="E23" s="116" t="n"/>
+      <c r="F23" s="116" t="n"/>
+      <c r="G23" s="116" t="n"/>
+      <c r="H23" s="116" t="n"/>
+      <c r="I23" s="116" t="n"/>
+      <c r="J23" s="116" t="n"/>
+      <c r="K23" s="116" t="n"/>
+      <c r="L23" s="116" t="n"/>
+      <c r="M23" s="116" t="n"/>
+      <c r="N23" s="116" t="n"/>
+      <c r="O23" s="116" t="n"/>
+      <c r="P23" s="116" t="n"/>
+      <c r="Q23" s="116" t="n"/>
+      <c r="R23" s="116" t="n"/>
+      <c r="S23" s="116" t="n"/>
+      <c r="T23" s="116" t="n"/>
+      <c r="U23" s="116" t="n"/>
+      <c r="V23" s="116" t="n"/>
+      <c r="W23" s="116" t="n"/>
+      <c r="X23" s="117" t="n"/>
+      <c r="Y23" s="120" t="n"/>
+      <c r="Z23" s="121" t="n"/>
+      <c r="AA23" s="108" t="n"/>
+      <c r="AB23" s="113" t="n"/>
+      <c r="AC23" s="106" t="n"/>
+      <c r="AD23" s="152" t="n"/>
+      <c r="AE23" s="108" t="n"/>
+      <c r="AF23" s="151" t="n"/>
+      <c r="AG23" s="151" t="n"/>
+      <c r="AH23" s="151" t="n"/>
+      <c r="AI23" s="151" t="n"/>
+      <c r="AJ23" s="151" t="n"/>
+      <c r="AK23" s="152" t="n"/>
+      <c r="AL23" s="21" t="n"/>
+      <c r="AM23" s="22" t="n"/>
       <c r="AN23" s="5" t="n"/>
-      <c r="BK23" s="28" t="n"/>
+      <c r="BK23" s="22" t="n"/>
     </row>
     <row r="24" ht="99" customHeight="1">
-      <c r="A24" s="32" t="n"/>
-      <c r="B24" s="44" t="n"/>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="31" t="n"/>
-      <c r="E24" s="31" t="n"/>
-      <c r="F24" s="31" t="n"/>
-      <c r="G24" s="31" t="n"/>
-      <c r="H24" s="31" t="n"/>
-      <c r="I24" s="31" t="n"/>
-      <c r="J24" s="31" t="n"/>
-      <c r="K24" s="31" t="n"/>
-      <c r="L24" s="31" t="n"/>
-      <c r="M24" s="31" t="n"/>
-      <c r="N24" s="31" t="n"/>
-      <c r="O24" s="31" t="n"/>
-      <c r="P24" s="31" t="n"/>
-      <c r="Q24" s="31" t="n"/>
-      <c r="R24" s="31" t="n"/>
-      <c r="S24" s="31" t="n"/>
-      <c r="T24" s="31" t="n"/>
-      <c r="U24" s="31" t="n"/>
-      <c r="V24" s="31" t="n"/>
-      <c r="W24" s="31" t="n"/>
-      <c r="X24" s="59" t="n"/>
-      <c r="Y24" s="45" t="n"/>
-      <c r="Z24" s="26" t="n"/>
-      <c r="AA24" s="32" t="n"/>
-      <c r="AB24" s="34" t="n"/>
-      <c r="AC24" s="65" t="n"/>
-      <c r="AD24" s="150" t="n"/>
-      <c r="AE24" s="159" t="n"/>
-      <c r="AF24" s="149" t="n"/>
-      <c r="AG24" s="149" t="n"/>
-      <c r="AH24" s="149" t="n"/>
-      <c r="AI24" s="149" t="n"/>
-      <c r="AJ24" s="149" t="n"/>
-      <c r="AK24" s="150" t="n"/>
-      <c r="AL24" s="27" t="n"/>
-      <c r="AM24" s="28" t="n"/>
+      <c r="A24" s="108" t="n"/>
+      <c r="B24" s="114" t="n"/>
+      <c r="C24" s="115" t="n"/>
+      <c r="D24" s="116" t="n"/>
+      <c r="E24" s="116" t="n"/>
+      <c r="F24" s="116" t="n"/>
+      <c r="G24" s="116" t="n"/>
+      <c r="H24" s="116" t="n"/>
+      <c r="I24" s="116" t="n"/>
+      <c r="J24" s="116" t="n"/>
+      <c r="K24" s="116" t="n"/>
+      <c r="L24" s="116" t="n"/>
+      <c r="M24" s="116" t="n"/>
+      <c r="N24" s="116" t="n"/>
+      <c r="O24" s="116" t="n"/>
+      <c r="P24" s="116" t="n"/>
+      <c r="Q24" s="116" t="n"/>
+      <c r="R24" s="116" t="n"/>
+      <c r="S24" s="116" t="n"/>
+      <c r="T24" s="116" t="n"/>
+      <c r="U24" s="116" t="n"/>
+      <c r="V24" s="116" t="n"/>
+      <c r="W24" s="116" t="n"/>
+      <c r="X24" s="117" t="n"/>
+      <c r="Y24" s="120" t="n"/>
+      <c r="Z24" s="121" t="n"/>
+      <c r="AA24" s="108" t="n"/>
+      <c r="AB24" s="113" t="n"/>
+      <c r="AC24" s="106" t="n"/>
+      <c r="AD24" s="152" t="n"/>
+      <c r="AE24" s="108" t="n"/>
+      <c r="AF24" s="151" t="n"/>
+      <c r="AG24" s="151" t="n"/>
+      <c r="AH24" s="151" t="n"/>
+      <c r="AI24" s="151" t="n"/>
+      <c r="AJ24" s="151" t="n"/>
+      <c r="AK24" s="152" t="n"/>
+      <c r="AL24" s="21" t="n"/>
+      <c r="AM24" s="22" t="n"/>
       <c r="AN24" s="5" t="n"/>
-      <c r="BK24" s="28" t="n"/>
+      <c r="BK24" s="22" t="n"/>
     </row>
     <row r="25" ht="99" customHeight="1">
-      <c r="A25" s="32" t="n"/>
-      <c r="B25" s="44" t="n"/>
-      <c r="C25" s="46" t="n"/>
-      <c r="D25" s="31" t="n"/>
-      <c r="E25" s="31" t="n"/>
-      <c r="F25" s="31" t="n"/>
-      <c r="G25" s="31" t="n"/>
-      <c r="H25" s="31" t="n"/>
-      <c r="I25" s="31" t="n"/>
-      <c r="J25" s="31" t="n"/>
-      <c r="K25" s="31" t="n"/>
-      <c r="L25" s="31" t="n"/>
-      <c r="M25" s="31" t="n"/>
-      <c r="N25" s="31" t="n"/>
-      <c r="O25" s="31" t="n"/>
-      <c r="P25" s="31" t="n"/>
-      <c r="Q25" s="31" t="n"/>
-      <c r="R25" s="31" t="n"/>
-      <c r="S25" s="31" t="n"/>
-      <c r="T25" s="31" t="n"/>
-      <c r="U25" s="31" t="n"/>
-      <c r="V25" s="31" t="n"/>
-      <c r="W25" s="31" t="n"/>
-      <c r="X25" s="59" t="n"/>
-      <c r="Y25" s="45" t="n"/>
-      <c r="Z25" s="26" t="n"/>
-      <c r="AA25" s="32" t="n"/>
-      <c r="AB25" s="34" t="n"/>
-      <c r="AC25" s="65" t="n"/>
-      <c r="AD25" s="150" t="n"/>
-      <c r="AE25" s="159" t="n"/>
-      <c r="AF25" s="149" t="n"/>
-      <c r="AG25" s="149" t="n"/>
-      <c r="AH25" s="149" t="n"/>
-      <c r="AI25" s="149" t="n"/>
-      <c r="AJ25" s="149" t="n"/>
-      <c r="AK25" s="150" t="n"/>
-      <c r="AL25" s="27" t="n"/>
-      <c r="AM25" s="28" t="n"/>
+      <c r="A25" s="108" t="n"/>
+      <c r="B25" s="114" t="n"/>
+      <c r="C25" s="115" t="n"/>
+      <c r="D25" s="116" t="n"/>
+      <c r="E25" s="116" t="n"/>
+      <c r="F25" s="116" t="n"/>
+      <c r="G25" s="116" t="n"/>
+      <c r="H25" s="116" t="n"/>
+      <c r="I25" s="116" t="n"/>
+      <c r="J25" s="116" t="n"/>
+      <c r="K25" s="116" t="n"/>
+      <c r="L25" s="116" t="n"/>
+      <c r="M25" s="116" t="n"/>
+      <c r="N25" s="116" t="n"/>
+      <c r="O25" s="116" t="n"/>
+      <c r="P25" s="116" t="n"/>
+      <c r="Q25" s="116" t="n"/>
+      <c r="R25" s="116" t="n"/>
+      <c r="S25" s="116" t="n"/>
+      <c r="T25" s="116" t="n"/>
+      <c r="U25" s="116" t="n"/>
+      <c r="V25" s="116" t="n"/>
+      <c r="W25" s="116" t="n"/>
+      <c r="X25" s="117" t="n"/>
+      <c r="Y25" s="120" t="n"/>
+      <c r="Z25" s="121" t="n"/>
+      <c r="AA25" s="108" t="n"/>
+      <c r="AB25" s="113" t="n"/>
+      <c r="AC25" s="106" t="n"/>
+      <c r="AD25" s="152" t="n"/>
+      <c r="AE25" s="108" t="n"/>
+      <c r="AF25" s="151" t="n"/>
+      <c r="AG25" s="151" t="n"/>
+      <c r="AH25" s="151" t="n"/>
+      <c r="AI25" s="151" t="n"/>
+      <c r="AJ25" s="151" t="n"/>
+      <c r="AK25" s="152" t="n"/>
+      <c r="AL25" s="21" t="n"/>
+      <c r="AM25" s="22" t="n"/>
       <c r="AN25" s="5" t="n"/>
-      <c r="BK25" s="28" t="n"/>
+      <c r="BK25" s="22" t="n"/>
     </row>
     <row r="26" ht="99" customHeight="1" thickBot="1">
-      <c r="A26" s="32" t="n"/>
-      <c r="B26" s="44" t="n"/>
-      <c r="C26" s="47" t="n"/>
-      <c r="D26" s="49" t="n"/>
-      <c r="E26" s="49" t="n"/>
-      <c r="F26" s="49" t="n"/>
-      <c r="G26" s="49" t="n"/>
-      <c r="H26" s="49" t="n"/>
-      <c r="I26" s="49" t="n"/>
-      <c r="J26" s="49" t="n"/>
-      <c r="K26" s="49" t="n"/>
-      <c r="L26" s="49" t="n"/>
-      <c r="M26" s="49" t="n"/>
-      <c r="N26" s="49" t="n"/>
-      <c r="O26" s="49" t="n"/>
-      <c r="P26" s="49" t="n"/>
-      <c r="Q26" s="49" t="n"/>
-      <c r="R26" s="49" t="n"/>
-      <c r="S26" s="49" t="n"/>
-      <c r="T26" s="49" t="n"/>
-      <c r="U26" s="49" t="n"/>
-      <c r="V26" s="49" t="n"/>
-      <c r="W26" s="49" t="n"/>
-      <c r="X26" s="60" t="n"/>
-      <c r="Y26" s="35" t="n"/>
-      <c r="Z26" s="36" t="n"/>
-      <c r="AA26" s="37" t="n"/>
-      <c r="AB26" s="38" t="n"/>
-      <c r="AC26" s="65" t="n"/>
-      <c r="AD26" s="150" t="n"/>
-      <c r="AE26" s="159" t="n"/>
-      <c r="AF26" s="149" t="n"/>
-      <c r="AG26" s="149" t="n"/>
-      <c r="AH26" s="149" t="n"/>
-      <c r="AI26" s="149" t="n"/>
-      <c r="AJ26" s="149" t="n"/>
-      <c r="AK26" s="150" t="n"/>
-      <c r="AL26" s="27" t="n"/>
-      <c r="AM26" s="28" t="n"/>
+      <c r="A26" s="108" t="n"/>
+      <c r="B26" s="114" t="n"/>
+      <c r="C26" s="122" t="n"/>
+      <c r="D26" s="124" t="n"/>
+      <c r="E26" s="124" t="n"/>
+      <c r="F26" s="124" t="n"/>
+      <c r="G26" s="124" t="n"/>
+      <c r="H26" s="124" t="n"/>
+      <c r="I26" s="124" t="n"/>
+      <c r="J26" s="124" t="n"/>
+      <c r="K26" s="124" t="n"/>
+      <c r="L26" s="124" t="n"/>
+      <c r="M26" s="124" t="n"/>
+      <c r="N26" s="124" t="n"/>
+      <c r="O26" s="124" t="n"/>
+      <c r="P26" s="124" t="n"/>
+      <c r="Q26" s="124" t="n"/>
+      <c r="R26" s="124" t="n"/>
+      <c r="S26" s="124" t="n"/>
+      <c r="T26" s="124" t="n"/>
+      <c r="U26" s="124" t="n"/>
+      <c r="V26" s="124" t="n"/>
+      <c r="W26" s="124" t="n"/>
+      <c r="X26" s="125" t="n"/>
+      <c r="Y26" s="126" t="n"/>
+      <c r="Z26" s="127" t="n"/>
+      <c r="AA26" s="128" t="n"/>
+      <c r="AB26" s="129" t="n"/>
+      <c r="AC26" s="106" t="n"/>
+      <c r="AD26" s="152" t="n"/>
+      <c r="AE26" s="108" t="n"/>
+      <c r="AF26" s="151" t="n"/>
+      <c r="AG26" s="151" t="n"/>
+      <c r="AH26" s="151" t="n"/>
+      <c r="AI26" s="151" t="n"/>
+      <c r="AJ26" s="151" t="n"/>
+      <c r="AK26" s="152" t="n"/>
+      <c r="AL26" s="21" t="n"/>
+      <c r="AM26" s="22" t="n"/>
       <c r="AN26" s="5" t="n"/>
-      <c r="BK26" s="28" t="n"/>
+      <c r="BK26" s="22" t="n"/>
     </row>
     <row r="27" ht="33" customHeight="1"/>
     <row r="28" ht="33" customHeight="1"/>
@@ -3262,47 +3338,47 @@
   </sheetData>
   <mergeCells count="73">
     <mergeCell ref="O5:O6"/>
+    <mergeCell ref="E5:E6"/>
     <mergeCell ref="Q14:S14"/>
+    <mergeCell ref="L2:P2"/>
+    <mergeCell ref="W5:W6"/>
+    <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AE19:AK19"/>
-    <mergeCell ref="AH5:AH6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="W5:W6"/>
-    <mergeCell ref="L2:P2"/>
     <mergeCell ref="Y5:Y6"/>
     <mergeCell ref="Q10:S10"/>
     <mergeCell ref="Q4:S6"/>
+    <mergeCell ref="AD5:AE5"/>
     <mergeCell ref="A16:A17"/>
-    <mergeCell ref="AD5:AE5"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="AB5:AB6"/>
     <mergeCell ref="AE24:AK24"/>
     <mergeCell ref="AA5:AA6"/>
     <mergeCell ref="AC18:AD18"/>
+    <mergeCell ref="AC5:AC6"/>
     <mergeCell ref="L5:L6"/>
-    <mergeCell ref="AC5:AC6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="AK5:AK6"/>
     <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
     <mergeCell ref="C4:P4"/>
-    <mergeCell ref="B4:B6"/>
     <mergeCell ref="AF5:AF6"/>
+    <mergeCell ref="AC24:AD24"/>
+    <mergeCell ref="Q9:S9"/>
     <mergeCell ref="L15:P15"/>
-    <mergeCell ref="Q9:S9"/>
     <mergeCell ref="AE20:AK20"/>
     <mergeCell ref="AE26:AK26"/>
-    <mergeCell ref="AC24:AD24"/>
-    <mergeCell ref="AE16:AK17"/>
+    <mergeCell ref="M5:M6"/>
     <mergeCell ref="AC23:AD23"/>
     <mergeCell ref="AE25:AK25"/>
     <mergeCell ref="X5:X6"/>
+    <mergeCell ref="I5:I6"/>
     <mergeCell ref="Z5:Z6"/>
-    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="AJ5:AJ6"/>
+    <mergeCell ref="R2:AH2"/>
     <mergeCell ref="AC26:AD26"/>
-    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="U5:U6"/>
     <mergeCell ref="AE22:AK22"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="AJ5:AJ6"/>
-    <mergeCell ref="U5:U6"/>
     <mergeCell ref="AC20:AD20"/>
     <mergeCell ref="AE18:AK18"/>
     <mergeCell ref="AC19:AD19"/>
@@ -3311,29 +3387,29 @@
     <mergeCell ref="AE21:AK21"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="Q12:S12"/>
     <mergeCell ref="AC22:AD22"/>
-    <mergeCell ref="Q12:S12"/>
     <mergeCell ref="AC16:AD17"/>
     <mergeCell ref="D5:D6"/>
+    <mergeCell ref="P5:P6"/>
     <mergeCell ref="AG5:AG6"/>
-    <mergeCell ref="P5:P6"/>
     <mergeCell ref="C16:X16"/>
+    <mergeCell ref="H5:H6"/>
     <mergeCell ref="AI5:AI6"/>
-    <mergeCell ref="H5:H6"/>
     <mergeCell ref="AC21:AD21"/>
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="AE23:AK23"/>
     <mergeCell ref="K5:K6"/>
+    <mergeCell ref="C5:C6"/>
     <mergeCell ref="Y16:AB16"/>
-    <mergeCell ref="C5:C6"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="Q8:S8"/>
     <mergeCell ref="T5:T6"/>
     <mergeCell ref="V5:V6"/>
-    <mergeCell ref="R2:AH2"/>
+    <mergeCell ref="AB5:AB6"/>
     <mergeCell ref="T4:AK4"/>
-    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="AE16:AK17"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1181102362204725" right="0.1181102362204725" top="0.7480314960629921" bottom="0.3543307086614174" header="0.3149606299212598" footer="0.3149606299212598"/>

--- a/Отчет_20-05-2025.xlsx
+++ b/Отчет_20-05-2025.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11835" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Лист1'!$A$1:$AK$26</definedName>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <charset val="204"/>
@@ -106,13 +106,6 @@
     </font>
     <font>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
       <charset val="204"/>
       <family val="2"/>
       <b val="1"/>
@@ -125,7 +118,22 @@
       <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
-      <sz val="10"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="16"/>
     </font>
   </fonts>
   <fills count="2">
@@ -779,10 +787,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -794,19 +811,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -834,7 +842,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -855,14 +863,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -907,6 +913,180 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -916,285 +1096,104 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1214,23 +1213,24 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1547,12 +1547,12 @@
   <dimension ref="A1:BK26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27.85546875" customWidth="1" style="22" min="1" max="1"/>
-    <col width="14.85546875" customWidth="1" style="22" min="2" max="2"/>
+    <col width="27.85546875" customWidth="1" style="20" min="1" max="1"/>
+    <col width="14.85546875" customWidth="1" style="20" min="2" max="2"/>
     <col width="11.7109375" customWidth="1" style="5" min="3" max="4"/>
     <col width="8.5703125" customWidth="1" style="5" min="5" max="16"/>
     <col width="7.85546875" customWidth="1" style="5" min="17" max="18"/>
-    <col width="8.5703125" customWidth="1" style="22" min="19" max="19"/>
+    <col width="8.5703125" customWidth="1" style="20" min="19" max="19"/>
     <col width="8.5703125" customWidth="1" style="5" min="20" max="23"/>
     <col width="9.85546875" customWidth="1" style="5" min="24" max="24"/>
     <col width="8.5703125" customWidth="1" style="5" min="25" max="25"/>
@@ -1561,279 +1561,257 @@
     <col width="9" customWidth="1" style="5" min="32" max="35"/>
     <col width="9.28515625" bestFit="1" customWidth="1" style="5" min="36" max="36"/>
     <col width="10" customWidth="1" style="5" min="37" max="38"/>
-    <col width="10" customWidth="1" style="22" min="39" max="39"/>
+    <col width="10" customWidth="1" style="20" min="39" max="39"/>
     <col width="5.42578125" customWidth="1" style="5" min="40" max="63"/>
-    <col width="13.85546875" customWidth="1" style="22" min="64" max="64"/>
-    <col width="24.28515625" customWidth="1" style="22" min="65" max="65"/>
-    <col width="9.140625" customWidth="1" style="22" min="66" max="16384"/>
+    <col width="13.85546875" customWidth="1" style="20" min="64" max="64"/>
+    <col width="24.28515625" customWidth="1" style="20" min="65" max="65"/>
+    <col width="9.140625" customWidth="1" style="20" min="66" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="37.5" customHeight="1">
-      <c r="A1" s="73" t="inlineStr">
+      <c r="A1" s="64" t="inlineStr">
         <is>
           <t>ОТЧЕТ по сдаче продукции в литейном цехе</t>
         </is>
       </c>
-      <c r="AL1" s="73" t="n"/>
+      <c r="AL1" s="64" t="n"/>
     </row>
     <row r="2" ht="73.5" customHeight="1">
-      <c r="A2" s="81" t="inlineStr">
+      <c r="A2" s="70" t="inlineStr">
         <is>
           <t>Дата:  20.05.2025  2025 г.</t>
         </is>
       </c>
-      <c r="L2" s="60" t="inlineStr">
+      <c r="L2" s="70" t="inlineStr">
         <is>
           <t>Контролеры: Елхова, Лабуткина, Рябова, Улитина</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="n"/>
-      <c r="R2" s="80" t="inlineStr">
-        <is>
-          <t>,</t>
-        </is>
-      </c>
-      <c r="S2" s="130" t="n"/>
-      <c r="T2" s="130" t="n"/>
-      <c r="U2" s="130" t="n"/>
-      <c r="V2" s="130" t="n"/>
-      <c r="W2" s="130" t="n"/>
-      <c r="X2" s="130" t="n"/>
-      <c r="Y2" s="130" t="n"/>
-      <c r="Z2" s="130" t="n"/>
-      <c r="AA2" s="130" t="n"/>
-      <c r="AB2" s="130" t="n"/>
-      <c r="AC2" s="130" t="n"/>
-      <c r="AD2" s="130" t="n"/>
-      <c r="AE2" s="130" t="n"/>
-      <c r="AF2" s="130" t="n"/>
-      <c r="AG2" s="130" t="n"/>
-      <c r="AH2" s="130" t="n"/>
       <c r="AI2" s="5" t="n"/>
       <c r="AJ2" s="5" t="n"/>
     </row>
     <row r="3" ht="22.5" customHeight="1" thickBot="1"/>
     <row r="4" ht="26.25" customFormat="1" customHeight="1" s="7" thickBot="1">
-      <c r="A4" s="131" t="inlineStr">
+      <c r="A4" s="126" t="inlineStr">
         <is>
           <t>НОМЕР И НАИМЕНОВАНИЕ ОТЛИВКИ</t>
         </is>
       </c>
-      <c r="B4" s="131" t="inlineStr">
+      <c r="B4" s="126" t="inlineStr">
         <is>
           <t>ОТЛИТО, шт.</t>
         </is>
       </c>
-      <c r="C4" s="63" t="inlineStr">
+      <c r="C4" s="55" t="inlineStr">
         <is>
           <t>БРАК НА ОПЕРАЦИЯХ, шт.</t>
         </is>
       </c>
-      <c r="D4" s="132" t="n"/>
-      <c r="E4" s="132" t="n"/>
-      <c r="F4" s="132" t="n"/>
-      <c r="G4" s="132" t="n"/>
-      <c r="H4" s="132" t="n"/>
-      <c r="I4" s="132" t="n"/>
-      <c r="J4" s="132" t="n"/>
-      <c r="K4" s="132" t="n"/>
-      <c r="L4" s="132" t="n"/>
-      <c r="M4" s="132" t="n"/>
-      <c r="N4" s="132" t="n"/>
-      <c r="O4" s="132" t="n"/>
-      <c r="P4" s="133" t="n"/>
-      <c r="Q4" s="131" t="inlineStr">
+      <c r="D4" s="127" t="n"/>
+      <c r="E4" s="127" t="n"/>
+      <c r="F4" s="127" t="n"/>
+      <c r="G4" s="127" t="n"/>
+      <c r="H4" s="127" t="n"/>
+      <c r="I4" s="127" t="n"/>
+      <c r="J4" s="127" t="n"/>
+      <c r="K4" s="127" t="n"/>
+      <c r="L4" s="127" t="n"/>
+      <c r="M4" s="127" t="n"/>
+      <c r="N4" s="127" t="n"/>
+      <c r="O4" s="127" t="n"/>
+      <c r="P4" s="128" t="n"/>
+      <c r="Q4" s="126" t="inlineStr">
         <is>
           <t>ПОДАНО, шт.</t>
         </is>
       </c>
-      <c r="R4" s="134" t="n"/>
-      <c r="S4" s="135" t="n"/>
-      <c r="T4" s="63" t="inlineStr">
+      <c r="R4" s="129" t="n"/>
+      <c r="S4" s="130" t="n"/>
+      <c r="T4" s="55" t="inlineStr">
         <is>
           <t>ДОРАБОТКА, шт.</t>
         </is>
       </c>
-      <c r="U4" s="132" t="n"/>
-      <c r="V4" s="132" t="n"/>
-      <c r="W4" s="132" t="n"/>
-      <c r="X4" s="132" t="n"/>
-      <c r="Y4" s="132" t="n"/>
-      <c r="Z4" s="132" t="n"/>
-      <c r="AA4" s="132" t="n"/>
-      <c r="AB4" s="132" t="n"/>
-      <c r="AC4" s="132" t="n"/>
-      <c r="AD4" s="132" t="n"/>
-      <c r="AE4" s="132" t="n"/>
-      <c r="AF4" s="132" t="n"/>
-      <c r="AG4" s="132" t="n"/>
-      <c r="AH4" s="132" t="n"/>
-      <c r="AI4" s="132" t="n"/>
-      <c r="AJ4" s="132" t="n"/>
-      <c r="AK4" s="133" t="n"/>
+      <c r="U4" s="127" t="n"/>
+      <c r="V4" s="127" t="n"/>
+      <c r="W4" s="127" t="n"/>
+      <c r="X4" s="127" t="n"/>
+      <c r="Y4" s="127" t="n"/>
+      <c r="Z4" s="127" t="n"/>
+      <c r="AA4" s="127" t="n"/>
+      <c r="AB4" s="127" t="n"/>
+      <c r="AC4" s="127" t="n"/>
+      <c r="AD4" s="127" t="n"/>
+      <c r="AE4" s="127" t="n"/>
+      <c r="AF4" s="127" t="n"/>
+      <c r="AG4" s="127" t="n"/>
+      <c r="AH4" s="127" t="n"/>
+      <c r="AI4" s="127" t="n"/>
+      <c r="AJ4" s="127" t="n"/>
+      <c r="AK4" s="128" t="n"/>
       <c r="AL4" s="6" t="n"/>
     </row>
     <row r="5" ht="114.75" customFormat="1" customHeight="1" s="9">
-      <c r="A5" s="136" t="n"/>
-      <c r="B5" s="136" t="n"/>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="A5" s="131" t="n"/>
+      <c r="B5" s="131" t="n"/>
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>недолив</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>раковины на корпусе</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>наруш. геом.</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>брак п/м</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>пригар песка</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t>наплыв металла</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t>вырыв</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="J5" s="23" t="inlineStr">
         <is>
           <t>слом</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t>зарез</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t>несоотв. 
 внеш. вида</t>
         </is>
       </c>
-      <c r="M5" s="25" t="inlineStr">
+      <c r="M5" s="23" t="inlineStr">
         <is>
           <t>трещины</t>
         </is>
       </c>
-      <c r="N5" s="25" t="inlineStr">
+      <c r="N5" s="23" t="inlineStr">
         <is>
           <t>скол</t>
         </is>
       </c>
-      <c r="O5" s="25" t="inlineStr">
+      <c r="O5" s="23" t="inlineStr">
         <is>
           <t>нарушение маркировки</t>
         </is>
       </c>
-      <c r="P5" s="26" t="inlineStr">
+      <c r="P5" s="24" t="inlineStr">
         <is>
           <t>технол. брак (ЛПД)</t>
         </is>
       </c>
-      <c r="Q5" s="137" t="n"/>
-      <c r="S5" s="138" t="n"/>
-      <c r="T5" s="67" t="inlineStr">
+      <c r="Q5" s="132" t="n"/>
+      <c r="S5" s="133" t="n"/>
+      <c r="T5" s="59" t="inlineStr">
         <is>
           <t>Раковины</t>
         </is>
       </c>
-      <c r="U5" s="40" t="inlineStr">
+      <c r="U5" s="41" t="inlineStr">
         <is>
           <t>Зарез</t>
         </is>
       </c>
-      <c r="V5" s="40" t="inlineStr">
+      <c r="V5" s="41" t="inlineStr">
         <is>
           <t>Несоотв. размеров</t>
         </is>
       </c>
-      <c r="W5" s="40" t="inlineStr">
+      <c r="W5" s="41" t="inlineStr">
         <is>
           <t>Несоотв. 
 внеш. вида</t>
         </is>
       </c>
-      <c r="X5" s="40" t="inlineStr">
+      <c r="X5" s="41" t="inlineStr">
         <is>
           <t>Наплыв мет. 
 на пов-ти</t>
         </is>
       </c>
-      <c r="Y5" s="61" t="inlineStr">
+      <c r="Y5" s="54" t="inlineStr">
         <is>
           <t>Прорыв мет. в резьбе (вороток)</t>
         </is>
       </c>
-      <c r="Z5" s="61" t="inlineStr">
+      <c r="Z5" s="54" t="inlineStr">
         <is>
           <t>Вырыв</t>
         </is>
       </c>
-      <c r="AA5" s="40" t="inlineStr">
+      <c r="AA5" s="41" t="inlineStr">
         <is>
           <t>Облой</t>
         </is>
       </c>
-      <c r="AB5" s="40" t="inlineStr">
+      <c r="AB5" s="41" t="inlineStr">
         <is>
           <t>Песок на 
 пов-ти</t>
         </is>
       </c>
-      <c r="AC5" s="70" t="inlineStr">
+      <c r="AC5" s="85" t="inlineStr">
         <is>
           <t>Песок в резьбе (вороток)</t>
         </is>
       </c>
-      <c r="AD5" s="61" t="inlineStr">
+      <c r="AD5" s="54" t="inlineStr">
         <is>
           <t>Клей</t>
         </is>
       </c>
-      <c r="AE5" s="139" t="n"/>
-      <c r="AF5" s="72" t="inlineStr">
+      <c r="AE5" s="134" t="n"/>
+      <c r="AF5" s="87" t="inlineStr">
         <is>
           <t>Коробление</t>
         </is>
       </c>
-      <c r="AG5" s="40" t="inlineStr">
+      <c r="AG5" s="41" t="inlineStr">
         <is>
           <t>Дефект п/м (покрытие)</t>
         </is>
       </c>
-      <c r="AH5" s="40" t="inlineStr">
+      <c r="AH5" s="41" t="inlineStr">
         <is>
           <t>Лапы</t>
         </is>
       </c>
-      <c r="AI5" s="40" t="inlineStr">
+      <c r="AI5" s="41" t="inlineStr">
         <is>
           <t>Питатель</t>
         </is>
       </c>
-      <c r="AJ5" s="40" t="inlineStr">
+      <c r="AJ5" s="41" t="inlineStr">
         <is>
           <t>Коронв</t>
         </is>
       </c>
-      <c r="AK5" s="79" t="inlineStr">
+      <c r="AK5" s="44" t="inlineStr">
         <is>
           <t>Смещение</t>
         </is>
@@ -1841,589 +1819,610 @@
       <c r="AL5" s="8" t="n"/>
     </row>
     <row r="6" ht="31.5" customFormat="1" customHeight="1" s="9" thickBot="1">
-      <c r="A6" s="140" t="n"/>
-      <c r="B6" s="140" t="n"/>
-      <c r="C6" s="141" t="n"/>
-      <c r="D6" s="142" t="n"/>
-      <c r="E6" s="142" t="n"/>
-      <c r="F6" s="142" t="n"/>
-      <c r="G6" s="142" t="n"/>
-      <c r="H6" s="142" t="n"/>
-      <c r="I6" s="142" t="n"/>
-      <c r="J6" s="142" t="n"/>
-      <c r="K6" s="142" t="n"/>
-      <c r="L6" s="142" t="n"/>
-      <c r="M6" s="142" t="n"/>
-      <c r="N6" s="142" t="n"/>
-      <c r="O6" s="142" t="n"/>
-      <c r="P6" s="143" t="n"/>
-      <c r="Q6" s="144" t="n"/>
-      <c r="R6" s="145" t="n"/>
-      <c r="S6" s="146" t="n"/>
-      <c r="T6" s="141" t="n"/>
-      <c r="U6" s="142" t="n"/>
-      <c r="V6" s="142" t="n"/>
-      <c r="W6" s="142" t="n"/>
-      <c r="X6" s="142" t="n"/>
-      <c r="Y6" s="147" t="n"/>
-      <c r="Z6" s="147" t="n"/>
-      <c r="AA6" s="142" t="n"/>
-      <c r="AB6" s="142" t="n"/>
-      <c r="AC6" s="148" t="n"/>
-      <c r="AD6" s="31" t="inlineStr">
+      <c r="A6" s="135" t="n"/>
+      <c r="B6" s="135" t="n"/>
+      <c r="C6" s="136" t="n"/>
+      <c r="D6" s="137" t="n"/>
+      <c r="E6" s="137" t="n"/>
+      <c r="F6" s="137" t="n"/>
+      <c r="G6" s="137" t="n"/>
+      <c r="H6" s="137" t="n"/>
+      <c r="I6" s="137" t="n"/>
+      <c r="J6" s="137" t="n"/>
+      <c r="K6" s="137" t="n"/>
+      <c r="L6" s="137" t="n"/>
+      <c r="M6" s="137" t="n"/>
+      <c r="N6" s="137" t="n"/>
+      <c r="O6" s="137" t="n"/>
+      <c r="P6" s="138" t="n"/>
+      <c r="Q6" s="139" t="n"/>
+      <c r="R6" s="140" t="n"/>
+      <c r="S6" s="141" t="n"/>
+      <c r="T6" s="136" t="n"/>
+      <c r="U6" s="137" t="n"/>
+      <c r="V6" s="137" t="n"/>
+      <c r="W6" s="137" t="n"/>
+      <c r="X6" s="137" t="n"/>
+      <c r="Y6" s="142" t="n"/>
+      <c r="Z6" s="142" t="n"/>
+      <c r="AA6" s="137" t="n"/>
+      <c r="AB6" s="137" t="n"/>
+      <c r="AC6" s="143" t="n"/>
+      <c r="AD6" s="29" t="inlineStr">
         <is>
           <t>П</t>
         </is>
       </c>
-      <c r="AE6" s="31" t="inlineStr">
+      <c r="AE6" s="29" t="inlineStr">
         <is>
           <t>Ш</t>
         </is>
       </c>
-      <c r="AF6" s="149" t="n"/>
-      <c r="AG6" s="142" t="n"/>
-      <c r="AH6" s="142" t="n"/>
-      <c r="AI6" s="142" t="n"/>
-      <c r="AJ6" s="142" t="n"/>
-      <c r="AK6" s="143" t="n"/>
+      <c r="AF6" s="144" t="n"/>
+      <c r="AG6" s="137" t="n"/>
+      <c r="AH6" s="137" t="n"/>
+      <c r="AI6" s="137" t="n"/>
+      <c r="AJ6" s="137" t="n"/>
+      <c r="AK6" s="138" t="n"/>
       <c r="AL6" s="8" t="n"/>
     </row>
     <row r="7" hidden="1" ht="104.25" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Наименование_отливки</t>
         </is>
       </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Контроль_отлито</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="28" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="27" t="n"/>
-      <c r="K7" s="27" t="n"/>
-      <c r="L7" s="27" t="n"/>
-      <c r="M7" s="27" t="n"/>
-      <c r="N7" s="27" t="n"/>
-      <c r="O7" s="27" t="n"/>
-      <c r="P7" s="57" t="n"/>
-      <c r="Q7" s="150" t="inlineStr">
+      <c r="C7" s="25" t="n"/>
+      <c r="D7" s="25" t="n"/>
+      <c r="E7" s="26" t="n"/>
+      <c r="F7" s="25" t="n"/>
+      <c r="G7" s="25" t="n"/>
+      <c r="H7" s="25" t="n"/>
+      <c r="I7" s="25" t="n"/>
+      <c r="J7" s="25" t="n"/>
+      <c r="K7" s="25" t="n"/>
+      <c r="L7" s="25" t="n"/>
+      <c r="M7" s="25" t="n"/>
+      <c r="N7" s="25" t="n"/>
+      <c r="O7" s="25" t="n"/>
+      <c r="P7" s="89" t="n"/>
+      <c r="Q7" s="145" t="inlineStr">
         <is>
           <t>Контроль_отлито</t>
         </is>
       </c>
-      <c r="R7" s="130" t="n"/>
-      <c r="S7" s="139" t="n"/>
-      <c r="T7" s="32" t="inlineStr">
+      <c r="R7" s="146" t="n"/>
+      <c r="S7" s="134" t="n"/>
+      <c r="T7" s="30" t="inlineStr">
         <is>
           <t>Доработка_раковины</t>
         </is>
       </c>
-      <c r="U7" s="32" t="inlineStr">
+      <c r="U7" s="30" t="inlineStr">
         <is>
           <t>Доработка_зарез</t>
         </is>
       </c>
-      <c r="V7" s="32" t="inlineStr">
+      <c r="V7" s="30" t="inlineStr">
         <is>
           <t>Доработка_несоответствие_размеров</t>
         </is>
       </c>
-      <c r="W7" s="32" t="inlineStr">
+      <c r="W7" s="30" t="inlineStr">
         <is>
           <t>Доработка_несоответствие_внешнего_вида</t>
         </is>
       </c>
-      <c r="X7" s="32" t="inlineStr">
+      <c r="X7" s="30" t="inlineStr">
         <is>
           <t>Доработка_наплыв_металла</t>
         </is>
       </c>
-      <c r="Y7" s="32" t="inlineStr">
+      <c r="Y7" s="30" t="inlineStr">
         <is>
           <t>Доработка_прорыв_металла</t>
         </is>
       </c>
-      <c r="Z7" s="32" t="inlineStr">
+      <c r="Z7" s="30" t="inlineStr">
         <is>
           <t>Доработка_вырыв</t>
         </is>
       </c>
-      <c r="AA7" s="32" t="inlineStr">
+      <c r="AA7" s="30" t="inlineStr">
         <is>
           <t>Доработка_облой</t>
         </is>
       </c>
-      <c r="AB7" s="32" t="inlineStr">
+      <c r="AB7" s="30" t="inlineStr">
         <is>
           <t>Доработка_песок_на_поверхности</t>
         </is>
       </c>
-      <c r="AC7" s="32" t="inlineStr">
+      <c r="AC7" s="30" t="inlineStr">
         <is>
           <t>Доработка_песок_в_резьбе</t>
         </is>
       </c>
-      <c r="AD7" s="32" t="inlineStr">
+      <c r="AD7" s="30" t="inlineStr">
         <is>
           <t>Доработка_клей_подтёк</t>
         </is>
       </c>
-      <c r="AE7" s="32" t="inlineStr">
+      <c r="AE7" s="30" t="inlineStr">
         <is>
           <t>Доработка_клей_по_шву</t>
         </is>
       </c>
-      <c r="AF7" s="32" t="inlineStr">
+      <c r="AF7" s="30" t="inlineStr">
         <is>
           <t>Доработка_коробление</t>
         </is>
       </c>
-      <c r="AG7" s="32" t="inlineStr">
+      <c r="AG7" s="30" t="inlineStr">
         <is>
           <t>Доработка_дефект_пеномодели</t>
         </is>
       </c>
-      <c r="AH7" s="32" t="inlineStr">
+      <c r="AH7" s="30" t="inlineStr">
         <is>
           <t>Доработка_лапы</t>
         </is>
       </c>
-      <c r="AI7" s="32" t="inlineStr">
+      <c r="AI7" s="30" t="inlineStr">
         <is>
           <t>Доработка_питатель</t>
         </is>
       </c>
-      <c r="AJ7" s="32" t="inlineStr">
+      <c r="AJ7" s="30" t="inlineStr">
         <is>
           <t>Доработка_корона</t>
         </is>
       </c>
-      <c r="AK7" s="32" t="inlineStr">
+      <c r="AK7" s="30" t="inlineStr">
         <is>
           <t>Доработка_смещение</t>
         </is>
       </c>
-      <c r="AL7" s="14" t="n"/>
+      <c r="AL7" s="13" t="n"/>
     </row>
     <row r="8" ht="104.25" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Вороток</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="11" t="n"/>
-      <c r="J8" s="11" t="n"/>
-      <c r="K8" s="11" t="n"/>
-      <c r="L8" s="11" t="n"/>
-      <c r="M8" s="11" t="n"/>
-      <c r="N8" s="11" t="n"/>
-      <c r="O8" s="11" t="n"/>
-      <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="104" t="n">
+      <c r="B8" s="34">
+        <f>Q8</f>
+        <v/>
+      </c>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="10" t="n"/>
+      <c r="J8" s="10" t="n"/>
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="10" t="n"/>
+      <c r="N8" s="10" t="n"/>
+      <c r="O8" s="10" t="n"/>
+      <c r="P8" s="12" t="n"/>
+      <c r="Q8" s="115" t="n">
         <v>666</v>
       </c>
-      <c r="R8" s="151" t="n"/>
-      <c r="S8" s="152" t="n"/>
-      <c r="T8" s="93" t="n">
+      <c r="R8" s="147" t="n"/>
+      <c r="S8" s="148" t="n"/>
+      <c r="T8" s="115" t="n">
         <v>0</v>
       </c>
-      <c r="U8" s="93" t="n">
+      <c r="U8" s="115" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="93" t="n">
-        <v>2</v>
-      </c>
-      <c r="W8" s="93" t="n">
-        <v>2</v>
-      </c>
-      <c r="X8" s="93" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y8" s="93" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z8" s="93" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA8" s="93" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB8" s="93" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC8" s="93" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD8" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE8" s="93" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF8" s="93" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG8" s="93" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH8" s="93" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI8" s="93" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ8" s="93" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK8" s="94" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL8" s="14" t="n"/>
+      <c r="V8" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="W8" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z8" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA8" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB8" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC8" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" s="101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE8" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF8" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI8" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ8" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK8" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL8" s="13" t="n"/>
     </row>
     <row r="9" ht="104.25" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Ригель</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="n"/>
-      <c r="J9" s="11" t="n"/>
-      <c r="K9" s="11" t="n"/>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="n"/>
-      <c r="N9" s="11" t="n"/>
-      <c r="O9" s="11" t="n"/>
-      <c r="P9" s="13" t="n"/>
-      <c r="Q9" s="104" t="n">
+      <c r="B9" s="34">
+        <f>Q9</f>
+        <v/>
+      </c>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="10" t="n"/>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="12" t="n"/>
+      <c r="Q9" s="115" t="n">
         <v>3000</v>
       </c>
-      <c r="R9" s="151" t="n"/>
-      <c r="S9" s="152" t="n"/>
-      <c r="T9" s="94" t="n">
+      <c r="R9" s="147" t="n"/>
+      <c r="S9" s="148" t="n"/>
+      <c r="T9" s="115" t="n">
         <v>0</v>
       </c>
-      <c r="U9" s="94" t="n">
+      <c r="U9" s="115" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="94" t="n">
+      <c r="V9" s="115" t="n">
         <v>44</v>
       </c>
-      <c r="W9" s="94" t="n">
+      <c r="W9" s="115" t="n">
         <v>43</v>
       </c>
-      <c r="X9" s="94" t="n">
+      <c r="X9" s="115" t="n">
         <v>44</v>
       </c>
-      <c r="Y9" s="94" t="n">
+      <c r="Y9" s="115" t="n">
         <v>43</v>
       </c>
-      <c r="Z9" s="94" t="n">
+      <c r="Z9" s="115" t="n">
         <v>44</v>
       </c>
-      <c r="AA9" s="94" t="n">
+      <c r="AA9" s="115" t="n">
         <v>43</v>
       </c>
-      <c r="AB9" s="94" t="n">
+      <c r="AB9" s="115" t="n">
         <v>44</v>
       </c>
-      <c r="AC9" s="94" t="n">
+      <c r="AC9" s="115" t="n">
         <v>43</v>
       </c>
-      <c r="AD9" s="94" t="n">
+      <c r="AD9" s="115" t="n">
         <v>44</v>
       </c>
-      <c r="AE9" s="94" t="n">
+      <c r="AE9" s="115" t="n">
         <v>43</v>
       </c>
-      <c r="AF9" s="94" t="n">
+      <c r="AF9" s="115" t="n">
         <v>44</v>
       </c>
-      <c r="AG9" s="95" t="n">
+      <c r="AG9" s="110" t="n">
         <v>43</v>
       </c>
-      <c r="AH9" s="94" t="n">
+      <c r="AH9" s="115" t="n">
         <v>44</v>
       </c>
-      <c r="AI9" s="94" t="n">
+      <c r="AI9" s="115" t="n">
         <v>43</v>
       </c>
-      <c r="AJ9" s="92" t="n">
+      <c r="AJ9" s="103" t="n">
         <v>44</v>
       </c>
-      <c r="AK9" s="94" t="n">
+      <c r="AK9" s="115" t="n">
         <v>43</v>
       </c>
-      <c r="AL9" s="14" t="n"/>
+      <c r="AL9" s="13" t="n"/>
     </row>
     <row r="10" ht="104.25" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Ригель optima</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n"/>
-      <c r="I10" s="11" t="n"/>
-      <c r="J10" s="11" t="n"/>
-      <c r="K10" s="11" t="n"/>
-      <c r="L10" s="11" t="n"/>
-      <c r="M10" s="11" t="n"/>
-      <c r="N10" s="11" t="n"/>
-      <c r="O10" s="11" t="n"/>
-      <c r="P10" s="13" t="n"/>
-      <c r="Q10" s="104" t="n">
+      <c r="B10" s="34">
+        <f>Q10</f>
+        <v/>
+      </c>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="10" t="n"/>
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="n"/>
+      <c r="O10" s="10" t="n"/>
+      <c r="P10" s="12" t="n"/>
+      <c r="Q10" s="115" t="n">
         <v>1999</v>
       </c>
-      <c r="R10" s="151" t="n"/>
-      <c r="S10" s="152" t="n"/>
-      <c r="T10" s="94" t="n">
+      <c r="R10" s="147" t="n"/>
+      <c r="S10" s="148" t="n"/>
+      <c r="T10" s="115" t="n">
         <v>0</v>
       </c>
-      <c r="U10" s="94" t="n">
+      <c r="U10" s="115" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="94" t="n">
-        <v>4</v>
-      </c>
-      <c r="W10" s="94" t="n">
-        <v>4</v>
-      </c>
-      <c r="X10" s="94" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y10" s="94" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z10" s="94" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA10" s="94" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB10" s="94" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC10" s="94" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD10" s="94" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE10" s="94" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF10" s="94" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG10" s="95" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH10" s="94" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI10" s="94" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ10" s="92" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK10" s="94" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL10" s="14" t="n"/>
+      <c r="V10" s="115" t="n">
+        <v>4</v>
+      </c>
+      <c r="W10" s="115" t="n">
+        <v>4</v>
+      </c>
+      <c r="X10" s="115" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="115" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z10" s="115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA10" s="115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB10" s="115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC10" s="115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD10" s="115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE10" s="115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF10" s="115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG10" s="110" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH10" s="115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI10" s="115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ10" s="103" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK10" s="115" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL10" s="13" t="n"/>
     </row>
     <row r="11" ht="104.25" customHeight="1">
-      <c r="A11" s="15" t="n"/>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="16" t="n"/>
-      <c r="I11" s="16" t="n"/>
-      <c r="J11" s="16" t="n"/>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="16" t="n"/>
-      <c r="M11" s="16" t="n"/>
-      <c r="N11" s="16" t="n"/>
-      <c r="O11" s="16" t="n"/>
-      <c r="P11" s="13" t="n"/>
-      <c r="Q11" s="153" t="n"/>
-      <c r="R11" s="154" t="n"/>
-      <c r="S11" s="155" t="n"/>
-      <c r="T11" s="96" t="n"/>
-      <c r="U11" s="96" t="n"/>
-      <c r="V11" s="96" t="n"/>
-      <c r="W11" s="96" t="n"/>
-      <c r="X11" s="96" t="n"/>
-      <c r="Y11" s="94" t="n"/>
-      <c r="Z11" s="94" t="n"/>
-      <c r="AA11" s="96" t="n"/>
-      <c r="AB11" s="96" t="n"/>
-      <c r="AC11" s="96" t="n"/>
-      <c r="AD11" s="96" t="n"/>
-      <c r="AE11" s="96" t="n"/>
-      <c r="AF11" s="96" t="n"/>
-      <c r="AG11" s="97" t="n"/>
-      <c r="AH11" s="94" t="n"/>
-      <c r="AI11" s="94" t="n"/>
-      <c r="AJ11" s="92" t="n"/>
-      <c r="AK11" s="94" t="n"/>
-      <c r="AL11" s="14" t="n"/>
+      <c r="A11" s="35" t="n"/>
+      <c r="B11" s="34">
+        <f>Q11</f>
+        <v/>
+      </c>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="n"/>
+      <c r="H11" s="14" t="n"/>
+      <c r="I11" s="14" t="n"/>
+      <c r="J11" s="14" t="n"/>
+      <c r="K11" s="14" t="n"/>
+      <c r="L11" s="14" t="n"/>
+      <c r="M11" s="14" t="n"/>
+      <c r="N11" s="14" t="n"/>
+      <c r="O11" s="14" t="n"/>
+      <c r="P11" s="12" t="n"/>
+      <c r="Q11" s="107" t="n"/>
+      <c r="R11" s="149" t="n"/>
+      <c r="S11" s="150" t="n"/>
+      <c r="T11" s="107" t="n"/>
+      <c r="U11" s="107" t="n"/>
+      <c r="V11" s="107" t="n"/>
+      <c r="W11" s="107" t="n"/>
+      <c r="X11" s="107" t="n"/>
+      <c r="Y11" s="115" t="n"/>
+      <c r="Z11" s="115" t="n"/>
+      <c r="AA11" s="107" t="n"/>
+      <c r="AB11" s="107" t="n"/>
+      <c r="AC11" s="107" t="n"/>
+      <c r="AD11" s="107" t="n"/>
+      <c r="AE11" s="107" t="n"/>
+      <c r="AF11" s="107" t="n"/>
+      <c r="AG11" s="108" t="n"/>
+      <c r="AH11" s="115" t="n"/>
+      <c r="AI11" s="115" t="n"/>
+      <c r="AJ11" s="103" t="n"/>
+      <c r="AK11" s="115" t="n"/>
+      <c r="AL11" s="13" t="n"/>
     </row>
     <row r="12" ht="104.25" customHeight="1">
-      <c r="A12" s="10" t="n"/>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="n"/>
-      <c r="J12" s="11" t="n"/>
-      <c r="K12" s="11" t="n"/>
-      <c r="L12" s="11" t="n"/>
-      <c r="M12" s="11" t="n"/>
-      <c r="N12" s="11" t="n"/>
-      <c r="O12" s="11" t="n"/>
-      <c r="P12" s="13" t="n"/>
-      <c r="Q12" s="104" t="n"/>
-      <c r="R12" s="151" t="n"/>
-      <c r="S12" s="152" t="n"/>
-      <c r="T12" s="94" t="n"/>
-      <c r="U12" s="94" t="n"/>
-      <c r="V12" s="94" t="n"/>
-      <c r="W12" s="94" t="n"/>
-      <c r="X12" s="94" t="n"/>
-      <c r="Y12" s="94" t="n"/>
-      <c r="Z12" s="94" t="n"/>
-      <c r="AA12" s="94" t="n"/>
-      <c r="AB12" s="94" t="n"/>
-      <c r="AC12" s="94" t="n"/>
-      <c r="AD12" s="94" t="n"/>
-      <c r="AE12" s="94" t="n"/>
-      <c r="AF12" s="94" t="n"/>
-      <c r="AG12" s="95" t="n"/>
-      <c r="AH12" s="94" t="n"/>
-      <c r="AI12" s="94" t="n"/>
-      <c r="AJ12" s="92" t="n"/>
-      <c r="AK12" s="94" t="n"/>
-      <c r="AL12" s="14" t="n"/>
+      <c r="A12" s="34" t="n"/>
+      <c r="B12" s="34">
+        <f>Q12</f>
+        <v/>
+      </c>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="10" t="n"/>
+      <c r="J12" s="10" t="n"/>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n"/>
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="10" t="n"/>
+      <c r="P12" s="12" t="n"/>
+      <c r="Q12" s="115" t="n"/>
+      <c r="R12" s="147" t="n"/>
+      <c r="S12" s="148" t="n"/>
+      <c r="T12" s="115" t="n"/>
+      <c r="U12" s="115" t="n"/>
+      <c r="V12" s="115" t="n"/>
+      <c r="W12" s="115" t="n"/>
+      <c r="X12" s="115" t="n"/>
+      <c r="Y12" s="115" t="n"/>
+      <c r="Z12" s="115" t="n"/>
+      <c r="AA12" s="115" t="n"/>
+      <c r="AB12" s="115" t="n"/>
+      <c r="AC12" s="115" t="n"/>
+      <c r="AD12" s="115" t="n"/>
+      <c r="AE12" s="115" t="n"/>
+      <c r="AF12" s="115" t="n"/>
+      <c r="AG12" s="110" t="n"/>
+      <c r="AH12" s="115" t="n"/>
+      <c r="AI12" s="115" t="n"/>
+      <c r="AJ12" s="103" t="n"/>
+      <c r="AK12" s="115" t="n"/>
+      <c r="AL12" s="13" t="n"/>
     </row>
     <row r="13" ht="104.25" customHeight="1">
-      <c r="A13" s="15" t="n"/>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="16" t="n"/>
-      <c r="H13" s="16" t="n"/>
-      <c r="I13" s="16" t="n"/>
-      <c r="J13" s="16" t="n"/>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="16" t="n"/>
-      <c r="M13" s="16" t="n"/>
-      <c r="N13" s="16" t="n"/>
-      <c r="O13" s="16" t="n"/>
-      <c r="P13" s="13" t="n"/>
-      <c r="Q13" s="153" t="n"/>
-      <c r="R13" s="154" t="n"/>
-      <c r="S13" s="155" t="n"/>
-      <c r="T13" s="96" t="n"/>
-      <c r="U13" s="96" t="n"/>
-      <c r="V13" s="96" t="n"/>
-      <c r="W13" s="96" t="n"/>
-      <c r="X13" s="96" t="n"/>
-      <c r="Y13" s="94" t="n"/>
-      <c r="Z13" s="94" t="n"/>
-      <c r="AA13" s="96" t="n"/>
-      <c r="AB13" s="96" t="n"/>
-      <c r="AC13" s="96" t="n"/>
-      <c r="AD13" s="96" t="n"/>
-      <c r="AE13" s="96" t="n"/>
-      <c r="AF13" s="96" t="n"/>
-      <c r="AG13" s="97" t="n"/>
-      <c r="AH13" s="94" t="n"/>
-      <c r="AI13" s="94" t="n"/>
-      <c r="AJ13" s="92" t="n"/>
-      <c r="AK13" s="94" t="n"/>
-      <c r="AL13" s="14" t="n"/>
+      <c r="A13" s="35" t="n"/>
+      <c r="B13" s="34">
+        <f>Q13</f>
+        <v/>
+      </c>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="14" t="n"/>
+      <c r="H13" s="14" t="n"/>
+      <c r="I13" s="14" t="n"/>
+      <c r="J13" s="14" t="n"/>
+      <c r="K13" s="14" t="n"/>
+      <c r="L13" s="14" t="n"/>
+      <c r="M13" s="14" t="n"/>
+      <c r="N13" s="14" t="n"/>
+      <c r="O13" s="14" t="n"/>
+      <c r="P13" s="12" t="n"/>
+      <c r="Q13" s="107" t="n"/>
+      <c r="R13" s="149" t="n"/>
+      <c r="S13" s="150" t="n"/>
+      <c r="T13" s="107" t="n"/>
+      <c r="U13" s="107" t="n"/>
+      <c r="V13" s="107" t="n"/>
+      <c r="W13" s="107" t="n"/>
+      <c r="X13" s="107" t="n"/>
+      <c r="Y13" s="115" t="n"/>
+      <c r="Z13" s="115" t="n"/>
+      <c r="AA13" s="107" t="n"/>
+      <c r="AB13" s="107" t="n"/>
+      <c r="AC13" s="107" t="n"/>
+      <c r="AD13" s="107" t="n"/>
+      <c r="AE13" s="107" t="n"/>
+      <c r="AF13" s="107" t="n"/>
+      <c r="AG13" s="108" t="n"/>
+      <c r="AH13" s="115" t="n"/>
+      <c r="AI13" s="115" t="n"/>
+      <c r="AJ13" s="103" t="n"/>
+      <c r="AK13" s="115" t="n"/>
+      <c r="AL13" s="13" t="n"/>
     </row>
     <row r="14" ht="104.25" customHeight="1">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n"/>
-      <c r="I14" s="11" t="n"/>
-      <c r="J14" s="11" t="n"/>
-      <c r="K14" s="11" t="n"/>
-      <c r="L14" s="11" t="n"/>
-      <c r="M14" s="11" t="n"/>
-      <c r="N14" s="11" t="n"/>
-      <c r="O14" s="11" t="n"/>
-      <c r="P14" s="13" t="n"/>
-      <c r="Q14" s="104" t="n"/>
-      <c r="R14" s="151" t="n"/>
-      <c r="S14" s="152" t="n"/>
-      <c r="T14" s="94" t="n"/>
-      <c r="U14" s="94" t="n"/>
-      <c r="V14" s="94" t="n"/>
-      <c r="W14" s="94" t="n"/>
-      <c r="X14" s="94" t="n"/>
-      <c r="Y14" s="94" t="n"/>
-      <c r="Z14" s="94" t="n"/>
-      <c r="AA14" s="94" t="n"/>
-      <c r="AB14" s="94" t="n"/>
-      <c r="AC14" s="94" t="n"/>
-      <c r="AD14" s="94" t="n"/>
-      <c r="AE14" s="94" t="n"/>
-      <c r="AF14" s="94" t="n"/>
-      <c r="AG14" s="95" t="n"/>
-      <c r="AH14" s="94" t="n"/>
-      <c r="AI14" s="94" t="n"/>
-      <c r="AJ14" s="92" t="n"/>
-      <c r="AK14" s="94" t="n"/>
-      <c r="AL14" s="14" t="n"/>
+      <c r="A14" s="34" t="n"/>
+      <c r="B14" s="34">
+        <f>Q14</f>
+        <v/>
+      </c>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="10" t="n"/>
+      <c r="J14" s="10" t="n"/>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="10" t="n"/>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="10" t="n"/>
+      <c r="O14" s="10" t="n"/>
+      <c r="P14" s="12" t="n"/>
+      <c r="Q14" s="115" t="n"/>
+      <c r="R14" s="147" t="n"/>
+      <c r="S14" s="148" t="n"/>
+      <c r="T14" s="115" t="n"/>
+      <c r="U14" s="115" t="n"/>
+      <c r="V14" s="115" t="n"/>
+      <c r="W14" s="115" t="n"/>
+      <c r="X14" s="115" t="n"/>
+      <c r="Y14" s="115" t="n"/>
+      <c r="Z14" s="115" t="n"/>
+      <c r="AA14" s="115" t="n"/>
+      <c r="AB14" s="115" t="n"/>
+      <c r="AC14" s="115" t="n"/>
+      <c r="AD14" s="115" t="n"/>
+      <c r="AE14" s="115" t="n"/>
+      <c r="AF14" s="115" t="n"/>
+      <c r="AG14" s="110" t="n"/>
+      <c r="AH14" s="115" t="n"/>
+      <c r="AI14" s="115" t="n"/>
+      <c r="AJ14" s="103" t="n"/>
+      <c r="AK14" s="115" t="n"/>
+      <c r="AL14" s="13" t="n"/>
     </row>
     <row r="15" ht="73.5" customHeight="1" thickBot="1">
       <c r="A15" s="4" t="n"/>
-      <c r="L15" s="60" t="n"/>
+      <c r="L15" s="88" t="n"/>
       <c r="Q15" s="5" t="n"/>
       <c r="R15" s="5" t="n"/>
-      <c r="S15" s="22" t="n"/>
+      <c r="S15" s="20" t="n"/>
       <c r="T15" s="5" t="n"/>
       <c r="U15" s="5" t="n"/>
       <c r="V15" s="5" t="n"/>
@@ -2443,942 +2442,942 @@
       <c r="AJ15" s="5" t="n"/>
     </row>
     <row r="16" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A16" s="53" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>НОМЕР И НАИМЕНОВАНИЕ ОТЛИВКИ</t>
         </is>
       </c>
-      <c r="B16" s="55" t="inlineStr">
+      <c r="B16" s="62" t="inlineStr">
         <is>
           <t>ГОДНЫЕ, шт.</t>
         </is>
       </c>
-      <c r="C16" s="41" t="inlineStr">
+      <c r="C16" s="71" t="inlineStr">
         <is>
           <t>ОКОНЧАТЕЛЬНЫЙ БРАК, шт.</t>
         </is>
       </c>
-      <c r="D16" s="132" t="n"/>
-      <c r="E16" s="132" t="n"/>
-      <c r="F16" s="132" t="n"/>
-      <c r="G16" s="132" t="n"/>
-      <c r="H16" s="132" t="n"/>
-      <c r="I16" s="132" t="n"/>
-      <c r="J16" s="132" t="n"/>
-      <c r="K16" s="132" t="n"/>
-      <c r="L16" s="132" t="n"/>
-      <c r="M16" s="132" t="n"/>
-      <c r="N16" s="132" t="n"/>
-      <c r="O16" s="132" t="n"/>
-      <c r="P16" s="132" t="n"/>
-      <c r="Q16" s="132" t="n"/>
-      <c r="R16" s="132" t="n"/>
-      <c r="S16" s="132" t="n"/>
-      <c r="T16" s="132" t="n"/>
-      <c r="U16" s="132" t="n"/>
-      <c r="V16" s="132" t="n"/>
-      <c r="W16" s="132" t="n"/>
-      <c r="X16" s="133" t="n"/>
-      <c r="Y16" s="156" t="inlineStr">
+      <c r="D16" s="127" t="n"/>
+      <c r="E16" s="127" t="n"/>
+      <c r="F16" s="127" t="n"/>
+      <c r="G16" s="127" t="n"/>
+      <c r="H16" s="127" t="n"/>
+      <c r="I16" s="127" t="n"/>
+      <c r="J16" s="127" t="n"/>
+      <c r="K16" s="127" t="n"/>
+      <c r="L16" s="127" t="n"/>
+      <c r="M16" s="127" t="n"/>
+      <c r="N16" s="127" t="n"/>
+      <c r="O16" s="127" t="n"/>
+      <c r="P16" s="127" t="n"/>
+      <c r="Q16" s="127" t="n"/>
+      <c r="R16" s="127" t="n"/>
+      <c r="S16" s="127" t="n"/>
+      <c r="T16" s="127" t="n"/>
+      <c r="U16" s="127" t="n"/>
+      <c r="V16" s="127" t="n"/>
+      <c r="W16" s="127" t="n"/>
+      <c r="X16" s="128" t="n"/>
+      <c r="Y16" s="151" t="inlineStr">
         <is>
           <t>2 СОРТ, шт.</t>
         </is>
       </c>
-      <c r="Z16" s="132" t="n"/>
-      <c r="AA16" s="132" t="n"/>
-      <c r="AB16" s="157" t="n"/>
-      <c r="AC16" s="158" t="inlineStr">
+      <c r="Z16" s="127" t="n"/>
+      <c r="AA16" s="127" t="n"/>
+      <c r="AB16" s="152" t="n"/>
+      <c r="AC16" s="153" t="inlineStr">
         <is>
           <t>НЕДОСТАЧА, 
 шт.</t>
         </is>
       </c>
-      <c r="AD16" s="135" t="n"/>
-      <c r="AE16" s="158" t="inlineStr">
+      <c r="AD16" s="130" t="n"/>
+      <c r="AE16" s="153" t="inlineStr">
         <is>
           <t>НОМЕРА ПЛАВОК</t>
         </is>
       </c>
-      <c r="AF16" s="134" t="n"/>
-      <c r="AG16" s="134" t="n"/>
-      <c r="AH16" s="134" t="n"/>
-      <c r="AI16" s="134" t="n"/>
-      <c r="AJ16" s="134" t="n"/>
-      <c r="AK16" s="135" t="n"/>
+      <c r="AF16" s="129" t="n"/>
+      <c r="AG16" s="129" t="n"/>
+      <c r="AH16" s="129" t="n"/>
+      <c r="AI16" s="129" t="n"/>
+      <c r="AJ16" s="129" t="n"/>
+      <c r="AK16" s="130" t="n"/>
     </row>
     <row r="17" ht="135.75" customHeight="1" thickBot="1">
-      <c r="A17" s="159" t="n"/>
-      <c r="B17" s="159" t="n"/>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="A17" s="154" t="n"/>
+      <c r="B17" s="154" t="n"/>
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>Раковины на корпусе</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>Коробление</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>Спай</t>
         </is>
       </c>
-      <c r="F17" s="25" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>Трещины</t>
         </is>
       </c>
-      <c r="G17" s="25" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>Недолив</t>
         </is>
       </c>
-      <c r="H17" s="25" t="inlineStr">
+      <c r="H17" s="23" t="inlineStr">
         <is>
           <t>Пригар песка</t>
         </is>
       </c>
-      <c r="I17" s="25" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>Пористость</t>
         </is>
       </c>
-      <c r="J17" s="25" t="inlineStr">
+      <c r="J17" s="23" t="inlineStr">
         <is>
           <t>Вырыв</t>
         </is>
       </c>
-      <c r="K17" s="25" t="inlineStr">
+      <c r="K17" s="23" t="inlineStr">
         <is>
           <t>Скол</t>
         </is>
       </c>
-      <c r="L17" s="25" t="inlineStr">
+      <c r="L17" s="23" t="inlineStr">
         <is>
           <t>Слом</t>
         </is>
       </c>
-      <c r="M17" s="25" t="inlineStr">
+      <c r="M17" s="23" t="inlineStr">
         <is>
           <t>Зарез литейный</t>
         </is>
       </c>
-      <c r="N17" s="25" t="inlineStr">
+      <c r="N17" s="23" t="inlineStr">
         <is>
           <t>Зарез пеномодельный</t>
         </is>
       </c>
-      <c r="O17" s="25" t="inlineStr">
+      <c r="O17" s="23" t="inlineStr">
         <is>
           <t>Нарушение геометрии</t>
         </is>
       </c>
-      <c r="P17" s="25" t="inlineStr">
+      <c r="P17" s="23" t="inlineStr">
         <is>
           <t>Рыхлота</t>
         </is>
       </c>
-      <c r="Q17" s="25" t="inlineStr">
+      <c r="Q17" s="23" t="inlineStr">
         <is>
           <t>Непрклей</t>
         </is>
       </c>
-      <c r="R17" s="25" t="inlineStr">
+      <c r="R17" s="23" t="inlineStr">
         <is>
           <t>Брак п/м</t>
         </is>
       </c>
-      <c r="S17" s="25" t="inlineStr">
+      <c r="S17" s="23" t="inlineStr">
         <is>
           <t>Наплыв металла</t>
         </is>
       </c>
-      <c r="T17" s="25" t="inlineStr">
+      <c r="T17" s="23" t="inlineStr">
         <is>
           <t>Несоответствие размеров</t>
         </is>
       </c>
-      <c r="U17" s="25" t="inlineStr">
+      <c r="U17" s="23" t="inlineStr">
         <is>
           <t>Несоответствие внешнего вида</t>
         </is>
       </c>
-      <c r="V17" s="25" t="inlineStr">
+      <c r="V17" s="23" t="inlineStr">
         <is>
           <t>Нарушение маркировки</t>
         </is>
       </c>
-      <c r="W17" s="25" t="inlineStr">
+      <c r="W17" s="23" t="inlineStr">
         <is>
           <t>Неслитина</t>
         </is>
       </c>
-      <c r="X17" s="33" t="inlineStr">
+      <c r="X17" s="31" t="inlineStr">
         <is>
           <t>Прочее</t>
         </is>
       </c>
-      <c r="Y17" s="24" t="inlineStr">
+      <c r="Y17" s="22" t="inlineStr">
         <is>
           <t>Раковины</t>
         </is>
       </c>
-      <c r="Z17" s="25" t="inlineStr">
+      <c r="Z17" s="23" t="inlineStr">
         <is>
           <t>Зарез литейный</t>
         </is>
       </c>
-      <c r="AA17" s="25" t="inlineStr">
+      <c r="AA17" s="23" t="inlineStr">
         <is>
           <t>Зарез пеномодельный</t>
         </is>
       </c>
-      <c r="AB17" s="26" t="inlineStr">
+      <c r="AB17" s="24" t="inlineStr">
         <is>
           <t>Прочее</t>
         </is>
       </c>
-      <c r="AC17" s="144" t="n"/>
-      <c r="AD17" s="146" t="n"/>
-      <c r="AE17" s="144" t="n"/>
-      <c r="AF17" s="145" t="n"/>
-      <c r="AG17" s="145" t="n"/>
-      <c r="AH17" s="145" t="n"/>
-      <c r="AI17" s="145" t="n"/>
-      <c r="AJ17" s="145" t="n"/>
-      <c r="AK17" s="146" t="n"/>
-      <c r="AL17" s="18" t="n"/>
-      <c r="AM17" s="19" t="n"/>
+      <c r="AC17" s="139" t="n"/>
+      <c r="AD17" s="141" t="n"/>
+      <c r="AE17" s="139" t="n"/>
+      <c r="AF17" s="140" t="n"/>
+      <c r="AG17" s="140" t="n"/>
+      <c r="AH17" s="140" t="n"/>
+      <c r="AI17" s="140" t="n"/>
+      <c r="AJ17" s="140" t="n"/>
+      <c r="AK17" s="141" t="n"/>
+      <c r="AL17" s="16" t="n"/>
+      <c r="AM17" s="17" t="n"/>
       <c r="AN17" s="5" t="n"/>
-      <c r="BK17" s="22" t="n"/>
+      <c r="BK17" s="20" t="n"/>
     </row>
     <row r="18" hidden="1" ht="99" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Наименование_отливки</t>
         </is>
       </c>
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Контроль_принято</t>
         </is>
       </c>
-      <c r="C18" s="32" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_раковины</t>
         </is>
       </c>
-      <c r="D18" s="32" t="inlineStr">
+      <c r="D18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_коробление</t>
         </is>
       </c>
-      <c r="E18" s="32" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_спай</t>
         </is>
       </c>
-      <c r="F18" s="32" t="inlineStr">
+      <c r="F18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_трещины</t>
         </is>
       </c>
-      <c r="G18" s="32" t="inlineStr">
+      <c r="G18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_недолив</t>
         </is>
       </c>
-      <c r="H18" s="32" t="inlineStr">
+      <c r="H18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_пригар_песка</t>
         </is>
       </c>
-      <c r="I18" s="32" t="inlineStr">
+      <c r="I18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_пористость</t>
         </is>
       </c>
-      <c r="J18" s="32" t="inlineStr">
+      <c r="J18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_вырыв</t>
         </is>
       </c>
-      <c r="K18" s="32" t="inlineStr">
+      <c r="K18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_скол</t>
         </is>
       </c>
-      <c r="L18" s="32" t="inlineStr">
+      <c r="L18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_слом</t>
         </is>
       </c>
-      <c r="M18" s="32" t="inlineStr">
+      <c r="M18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_зарез_литейный</t>
         </is>
       </c>
-      <c r="N18" s="32" t="inlineStr">
+      <c r="N18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_зарез_пеномодельный</t>
         </is>
       </c>
-      <c r="O18" s="32" t="inlineStr">
+      <c r="O18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_нарушение_геометрии</t>
         </is>
       </c>
-      <c r="P18" s="32" t="inlineStr">
+      <c r="P18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_рыхлота</t>
         </is>
       </c>
-      <c r="Q18" s="32" t="inlineStr">
+      <c r="Q18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_непроклей</t>
         </is>
       </c>
-      <c r="R18" s="32" t="inlineStr">
+      <c r="R18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_пеномодель</t>
         </is>
       </c>
-      <c r="S18" s="32" t="inlineStr">
+      <c r="S18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_наплыв_металла</t>
         </is>
       </c>
-      <c r="T18" s="32" t="inlineStr">
+      <c r="T18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_несоответствие_размеров</t>
         </is>
       </c>
-      <c r="U18" s="32" t="inlineStr">
+      <c r="U18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_несоответствие_внешнего_вида</t>
         </is>
       </c>
-      <c r="V18" s="32" t="inlineStr">
+      <c r="V18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_нарушение_маркировки</t>
         </is>
       </c>
-      <c r="W18" s="32" t="inlineStr">
+      <c r="W18" s="30" t="inlineStr">
         <is>
           <t>Окончательный_брак_неслитина</t>
         </is>
       </c>
-      <c r="X18" s="34" t="inlineStr">
+      <c r="X18" s="32" t="inlineStr">
         <is>
           <t>Окончательный_брак_прочее</t>
         </is>
       </c>
-      <c r="Y18" s="35" t="inlineStr">
+      <c r="Y18" s="33" t="inlineStr">
         <is>
           <t>Второй_сорт_раковины</t>
         </is>
       </c>
-      <c r="Z18" s="32" t="inlineStr">
+      <c r="Z18" s="30" t="inlineStr">
         <is>
           <t>Второй_сорт_зарез_литейный</t>
         </is>
       </c>
-      <c r="AA18" s="32" t="inlineStr">
+      <c r="AA18" s="30" t="inlineStr">
         <is>
           <t>Второй_сорт_зарез_пеномодельный</t>
         </is>
       </c>
-      <c r="AB18" s="23" t="n"/>
-      <c r="AC18" s="38" t="n"/>
-      <c r="AD18" s="139" t="n"/>
-      <c r="AE18" s="160" t="inlineStr">
+      <c r="AB18" s="21" t="n"/>
+      <c r="AC18" s="94" t="n"/>
+      <c r="AD18" s="134" t="n"/>
+      <c r="AE18" s="155" t="inlineStr">
         <is>
           <t>Номер_плавки</t>
         </is>
       </c>
-      <c r="AF18" s="130" t="n"/>
-      <c r="AG18" s="130" t="n"/>
-      <c r="AH18" s="130" t="n"/>
-      <c r="AI18" s="130" t="n"/>
-      <c r="AJ18" s="130" t="n"/>
-      <c r="AK18" s="139" t="n"/>
-      <c r="AL18" s="21" t="n"/>
-      <c r="AM18" s="22" t="n"/>
+      <c r="AF18" s="146" t="n"/>
+      <c r="AG18" s="146" t="n"/>
+      <c r="AH18" s="146" t="n"/>
+      <c r="AI18" s="146" t="n"/>
+      <c r="AJ18" s="146" t="n"/>
+      <c r="AK18" s="134" t="n"/>
+      <c r="AL18" s="19" t="n"/>
+      <c r="AM18" s="20" t="n"/>
       <c r="AN18" s="5" t="n"/>
-      <c r="BK18" s="22" t="n"/>
+      <c r="BK18" s="20" t="n"/>
     </row>
     <row r="19" ht="99" customHeight="1">
-      <c r="A19" s="108" t="inlineStr">
+      <c r="A19" s="115" t="inlineStr">
         <is>
           <t>Вороток</t>
         </is>
       </c>
-      <c r="B19" s="108" t="n">
+      <c r="B19" s="115" t="n">
         <v>584</v>
       </c>
-      <c r="C19" s="116" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="116" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="116" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" s="116" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" s="116" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="116" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" s="116" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" s="116" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" s="116" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="N19" s="116" t="n">
-        <v>2</v>
-      </c>
-      <c r="O19" s="116" t="n">
-        <v>2</v>
-      </c>
-      <c r="P19" s="116" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" s="116" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" s="116" t="n">
-        <v>2</v>
-      </c>
-      <c r="S19" s="108" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" s="116" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" s="116" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" s="116" t="n">
-        <v>2</v>
-      </c>
-      <c r="W19" s="116" t="n">
+      <c r="C19" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="101" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="101" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="115" t="n">
+        <v>2</v>
+      </c>
+      <c r="W19" s="115" t="n">
         <v>2</v>
       </c>
       <c r="X19" s="110" t="n">
         <v>2</v>
       </c>
-      <c r="Y19" s="120" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z19" s="121" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA19" s="108" t="n">
+      <c r="Y19" s="118" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z19" s="112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA19" s="115" t="n">
         <v>2</v>
       </c>
       <c r="AB19" s="113" t="n"/>
-      <c r="AC19" s="106" t="n"/>
-      <c r="AD19" s="152" t="n"/>
-      <c r="AE19" s="108" t="inlineStr">
+      <c r="AC19" s="39" t="n"/>
+      <c r="AD19" s="148" t="n"/>
+      <c r="AE19" s="156" t="inlineStr">
         <is>
           <t>5-107/25</t>
         </is>
       </c>
-      <c r="AF19" s="151" t="n"/>
-      <c r="AG19" s="151" t="n"/>
-      <c r="AH19" s="151" t="n"/>
-      <c r="AI19" s="151" t="n"/>
-      <c r="AJ19" s="151" t="n"/>
-      <c r="AK19" s="152" t="n"/>
-      <c r="AL19" s="21" t="n"/>
-      <c r="AM19" s="22" t="n"/>
+      <c r="AF19" s="147" t="n"/>
+      <c r="AG19" s="147" t="n"/>
+      <c r="AH19" s="147" t="n"/>
+      <c r="AI19" s="147" t="n"/>
+      <c r="AJ19" s="147" t="n"/>
+      <c r="AK19" s="148" t="n"/>
+      <c r="AL19" s="19" t="n"/>
+      <c r="AM19" s="20" t="n"/>
       <c r="AN19" s="5" t="n"/>
-      <c r="BK19" s="22" t="n"/>
+      <c r="BK19" s="20" t="n"/>
     </row>
     <row r="20" ht="99" customHeight="1">
-      <c r="A20" s="108" t="inlineStr">
+      <c r="A20" s="115" t="inlineStr">
         <is>
           <t>Ригель</t>
         </is>
       </c>
-      <c r="B20" s="114" t="n">
+      <c r="B20" s="110" t="n">
         <v>1217</v>
       </c>
-      <c r="C20" s="115" t="n">
+      <c r="C20" s="114" t="n">
         <v>43</v>
       </c>
-      <c r="D20" s="116" t="n">
+      <c r="D20" s="115" t="n">
         <v>44</v>
       </c>
-      <c r="E20" s="116" t="n">
+      <c r="E20" s="115" t="n">
         <v>43</v>
       </c>
-      <c r="F20" s="116" t="n">
+      <c r="F20" s="115" t="n">
         <v>44</v>
       </c>
-      <c r="G20" s="116" t="n">
+      <c r="G20" s="115" t="n">
         <v>44</v>
       </c>
-      <c r="H20" s="116" t="n">
+      <c r="H20" s="115" t="n">
         <v>43</v>
       </c>
-      <c r="I20" s="116" t="n">
+      <c r="I20" s="115" t="n">
         <v>44</v>
       </c>
-      <c r="J20" s="116" t="n">
+      <c r="J20" s="115" t="n">
         <v>43</v>
       </c>
-      <c r="K20" s="116" t="n">
+      <c r="K20" s="115" t="n">
         <v>44</v>
       </c>
-      <c r="L20" s="116" t="n">
+      <c r="L20" s="115" t="n">
         <v>43</v>
       </c>
-      <c r="M20" s="116" t="n">
+      <c r="M20" s="115" t="n">
         <v>44</v>
       </c>
-      <c r="N20" s="116" t="n">
+      <c r="N20" s="115" t="n">
         <v>43</v>
       </c>
-      <c r="O20" s="116" t="n">
+      <c r="O20" s="115" t="n">
         <v>44</v>
       </c>
-      <c r="P20" s="116" t="n">
+      <c r="P20" s="115" t="n">
         <v>43</v>
       </c>
-      <c r="Q20" s="116" t="n">
+      <c r="Q20" s="115" t="n">
         <v>44</v>
       </c>
-      <c r="R20" s="116" t="n">
+      <c r="R20" s="115" t="n">
         <v>43</v>
       </c>
-      <c r="S20" s="116" t="n">
+      <c r="S20" s="115" t="n">
         <v>44</v>
       </c>
-      <c r="T20" s="116" t="n">
+      <c r="T20" s="115" t="n">
         <v>43</v>
       </c>
-      <c r="U20" s="116" t="n">
+      <c r="U20" s="115" t="n">
         <v>44</v>
       </c>
-      <c r="V20" s="116" t="n">
+      <c r="V20" s="115" t="n">
         <v>43</v>
       </c>
-      <c r="W20" s="116" t="n">
+      <c r="W20" s="115" t="n">
         <v>44</v>
       </c>
       <c r="X20" s="117" t="n">
         <v>43</v>
       </c>
-      <c r="Y20" s="120" t="n">
+      <c r="Y20" s="118" t="n">
         <v>43</v>
       </c>
-      <c r="Z20" s="121" t="n">
+      <c r="Z20" s="112" t="n">
         <v>44</v>
       </c>
-      <c r="AA20" s="108" t="n">
+      <c r="AA20" s="115" t="n">
         <v>43</v>
       </c>
       <c r="AB20" s="113" t="n"/>
-      <c r="AC20" s="106" t="n"/>
-      <c r="AD20" s="152" t="n"/>
-      <c r="AE20" s="108" t="inlineStr">
+      <c r="AC20" s="39" t="n"/>
+      <c r="AD20" s="148" t="n"/>
+      <c r="AE20" s="156" t="inlineStr">
         <is>
           <t>5-134/25, 5-133/25, 5-132/25</t>
         </is>
       </c>
-      <c r="AF20" s="151" t="n"/>
-      <c r="AG20" s="151" t="n"/>
-      <c r="AH20" s="151" t="n"/>
-      <c r="AI20" s="151" t="n"/>
-      <c r="AJ20" s="151" t="n"/>
-      <c r="AK20" s="152" t="n"/>
-      <c r="AL20" s="21" t="n"/>
-      <c r="AM20" s="22" t="n"/>
+      <c r="AF20" s="147" t="n"/>
+      <c r="AG20" s="147" t="n"/>
+      <c r="AH20" s="147" t="n"/>
+      <c r="AI20" s="147" t="n"/>
+      <c r="AJ20" s="147" t="n"/>
+      <c r="AK20" s="148" t="n"/>
+      <c r="AL20" s="19" t="n"/>
+      <c r="AM20" s="20" t="n"/>
       <c r="AN20" s="5" t="n"/>
-      <c r="BK20" s="22" t="n"/>
+      <c r="BK20" s="20" t="n"/>
     </row>
     <row r="21" ht="99" customHeight="1">
-      <c r="A21" s="118" t="inlineStr">
+      <c r="A21" s="112" t="inlineStr">
         <is>
           <t>Ригель optima</t>
         </is>
       </c>
-      <c r="B21" s="119" t="n">
+      <c r="B21" s="117" t="n">
         <v>1835</v>
       </c>
-      <c r="C21" s="120" t="n">
-        <v>4</v>
-      </c>
-      <c r="D21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="E21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="G21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="I21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="K21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="L21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="M21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="N21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="O21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="P21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="R21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="S21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="T21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="U21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="V21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="W21" s="121" t="n">
+      <c r="C21" s="118" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="M21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="P21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="R21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="S21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="V21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="W21" s="112" t="n">
         <v>4</v>
       </c>
       <c r="X21" s="117" t="n">
         <v>4</v>
       </c>
-      <c r="Y21" s="120" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z21" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA21" s="108" t="n">
+      <c r="Y21" s="118" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="112" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA21" s="115" t="n">
         <v>4</v>
       </c>
       <c r="AB21" s="113" t="n"/>
-      <c r="AC21" s="106" t="n"/>
-      <c r="AD21" s="152" t="n"/>
-      <c r="AE21" s="108" t="inlineStr">
+      <c r="AC21" s="39" t="n"/>
+      <c r="AD21" s="148" t="n"/>
+      <c r="AE21" s="156" t="inlineStr">
         <is>
           <t>3-332/25, 4-193/25</t>
         </is>
       </c>
-      <c r="AF21" s="151" t="n"/>
-      <c r="AG21" s="151" t="n"/>
-      <c r="AH21" s="151" t="n"/>
-      <c r="AI21" s="151" t="n"/>
-      <c r="AJ21" s="151" t="n"/>
-      <c r="AK21" s="152" t="n"/>
-      <c r="AL21" s="21" t="n"/>
-      <c r="AM21" s="22" t="n"/>
+      <c r="AF21" s="147" t="n"/>
+      <c r="AG21" s="147" t="n"/>
+      <c r="AH21" s="147" t="n"/>
+      <c r="AI21" s="147" t="n"/>
+      <c r="AJ21" s="147" t="n"/>
+      <c r="AK21" s="148" t="n"/>
+      <c r="AL21" s="19" t="n"/>
+      <c r="AM21" s="20" t="n"/>
       <c r="AN21" s="5" t="n"/>
-      <c r="BK21" s="22" t="n"/>
+      <c r="BK21" s="20" t="n"/>
     </row>
     <row r="22" ht="99" customHeight="1">
-      <c r="A22" s="108" t="n"/>
-      <c r="B22" s="114" t="n"/>
-      <c r="C22" s="115" t="n"/>
-      <c r="D22" s="116" t="n"/>
-      <c r="E22" s="116" t="n"/>
-      <c r="F22" s="116" t="n"/>
-      <c r="G22" s="116" t="n"/>
-      <c r="H22" s="116" t="n"/>
-      <c r="I22" s="116" t="n"/>
-      <c r="J22" s="116" t="n"/>
-      <c r="K22" s="116" t="n"/>
-      <c r="L22" s="116" t="n"/>
-      <c r="M22" s="116" t="n"/>
-      <c r="N22" s="116" t="n"/>
-      <c r="O22" s="116" t="n"/>
-      <c r="P22" s="116" t="n"/>
-      <c r="Q22" s="116" t="n"/>
-      <c r="R22" s="116" t="n"/>
-      <c r="S22" s="116" t="n"/>
-      <c r="T22" s="116" t="n"/>
-      <c r="U22" s="116" t="n"/>
-      <c r="V22" s="116" t="n"/>
-      <c r="W22" s="116" t="n"/>
+      <c r="A22" s="115" t="n"/>
+      <c r="B22" s="110" t="n"/>
+      <c r="C22" s="114" t="n"/>
+      <c r="D22" s="115" t="n"/>
+      <c r="E22" s="115" t="n"/>
+      <c r="F22" s="115" t="n"/>
+      <c r="G22" s="115" t="n"/>
+      <c r="H22" s="115" t="n"/>
+      <c r="I22" s="115" t="n"/>
+      <c r="J22" s="115" t="n"/>
+      <c r="K22" s="115" t="n"/>
+      <c r="L22" s="115" t="n"/>
+      <c r="M22" s="115" t="n"/>
+      <c r="N22" s="115" t="n"/>
+      <c r="O22" s="115" t="n"/>
+      <c r="P22" s="115" t="n"/>
+      <c r="Q22" s="115" t="n"/>
+      <c r="R22" s="115" t="n"/>
+      <c r="S22" s="115" t="n"/>
+      <c r="T22" s="115" t="n"/>
+      <c r="U22" s="115" t="n"/>
+      <c r="V22" s="115" t="n"/>
+      <c r="W22" s="115" t="n"/>
       <c r="X22" s="117" t="n"/>
-      <c r="Y22" s="120" t="n"/>
-      <c r="Z22" s="121" t="n"/>
-      <c r="AA22" s="108" t="n"/>
+      <c r="Y22" s="118" t="n"/>
+      <c r="Z22" s="112" t="n"/>
+      <c r="AA22" s="115" t="n"/>
       <c r="AB22" s="113" t="n"/>
-      <c r="AC22" s="106" t="n"/>
-      <c r="AD22" s="152" t="n"/>
-      <c r="AE22" s="108" t="n"/>
-      <c r="AF22" s="151" t="n"/>
-      <c r="AG22" s="151" t="n"/>
-      <c r="AH22" s="151" t="n"/>
-      <c r="AI22" s="151" t="n"/>
-      <c r="AJ22" s="151" t="n"/>
-      <c r="AK22" s="152" t="n"/>
-      <c r="AL22" s="21" t="n"/>
-      <c r="AM22" s="22" t="n"/>
+      <c r="AC22" s="39" t="n"/>
+      <c r="AD22" s="148" t="n"/>
+      <c r="AE22" s="156" t="n"/>
+      <c r="AF22" s="147" t="n"/>
+      <c r="AG22" s="147" t="n"/>
+      <c r="AH22" s="147" t="n"/>
+      <c r="AI22" s="147" t="n"/>
+      <c r="AJ22" s="147" t="n"/>
+      <c r="AK22" s="148" t="n"/>
+      <c r="AL22" s="19" t="n"/>
+      <c r="AM22" s="20" t="n"/>
       <c r="AN22" s="5" t="n"/>
-      <c r="BK22" s="22" t="n"/>
+      <c r="BK22" s="20" t="n"/>
     </row>
     <row r="23" ht="99" customHeight="1">
-      <c r="A23" s="108" t="n"/>
-      <c r="B23" s="114" t="n"/>
-      <c r="C23" s="115" t="n"/>
-      <c r="D23" s="116" t="n"/>
-      <c r="E23" s="116" t="n"/>
-      <c r="F23" s="116" t="n"/>
-      <c r="G23" s="116" t="n"/>
-      <c r="H23" s="116" t="n"/>
-      <c r="I23" s="116" t="n"/>
-      <c r="J23" s="116" t="n"/>
-      <c r="K23" s="116" t="n"/>
-      <c r="L23" s="116" t="n"/>
-      <c r="M23" s="116" t="n"/>
-      <c r="N23" s="116" t="n"/>
-      <c r="O23" s="116" t="n"/>
-      <c r="P23" s="116" t="n"/>
-      <c r="Q23" s="116" t="n"/>
-      <c r="R23" s="116" t="n"/>
-      <c r="S23" s="116" t="n"/>
-      <c r="T23" s="116" t="n"/>
-      <c r="U23" s="116" t="n"/>
-      <c r="V23" s="116" t="n"/>
-      <c r="W23" s="116" t="n"/>
+      <c r="A23" s="115" t="n"/>
+      <c r="B23" s="110" t="n"/>
+      <c r="C23" s="114" t="n"/>
+      <c r="D23" s="115" t="n"/>
+      <c r="E23" s="115" t="n"/>
+      <c r="F23" s="115" t="n"/>
+      <c r="G23" s="115" t="n"/>
+      <c r="H23" s="115" t="n"/>
+      <c r="I23" s="115" t="n"/>
+      <c r="J23" s="115" t="n"/>
+      <c r="K23" s="115" t="n"/>
+      <c r="L23" s="115" t="n"/>
+      <c r="M23" s="115" t="n"/>
+      <c r="N23" s="115" t="n"/>
+      <c r="O23" s="115" t="n"/>
+      <c r="P23" s="115" t="n"/>
+      <c r="Q23" s="115" t="n"/>
+      <c r="R23" s="115" t="n"/>
+      <c r="S23" s="115" t="n"/>
+      <c r="T23" s="115" t="n"/>
+      <c r="U23" s="115" t="n"/>
+      <c r="V23" s="115" t="n"/>
+      <c r="W23" s="115" t="n"/>
       <c r="X23" s="117" t="n"/>
-      <c r="Y23" s="120" t="n"/>
-      <c r="Z23" s="121" t="n"/>
-      <c r="AA23" s="108" t="n"/>
+      <c r="Y23" s="118" t="n"/>
+      <c r="Z23" s="112" t="n"/>
+      <c r="AA23" s="115" t="n"/>
       <c r="AB23" s="113" t="n"/>
-      <c r="AC23" s="106" t="n"/>
-      <c r="AD23" s="152" t="n"/>
-      <c r="AE23" s="108" t="n"/>
-      <c r="AF23" s="151" t="n"/>
-      <c r="AG23" s="151" t="n"/>
-      <c r="AH23" s="151" t="n"/>
-      <c r="AI23" s="151" t="n"/>
-      <c r="AJ23" s="151" t="n"/>
-      <c r="AK23" s="152" t="n"/>
-      <c r="AL23" s="21" t="n"/>
-      <c r="AM23" s="22" t="n"/>
+      <c r="AC23" s="39" t="n"/>
+      <c r="AD23" s="148" t="n"/>
+      <c r="AE23" s="156" t="n"/>
+      <c r="AF23" s="147" t="n"/>
+      <c r="AG23" s="147" t="n"/>
+      <c r="AH23" s="147" t="n"/>
+      <c r="AI23" s="147" t="n"/>
+      <c r="AJ23" s="147" t="n"/>
+      <c r="AK23" s="148" t="n"/>
+      <c r="AL23" s="19" t="n"/>
+      <c r="AM23" s="20" t="n"/>
       <c r="AN23" s="5" t="n"/>
-      <c r="BK23" s="22" t="n"/>
+      <c r="BK23" s="20" t="n"/>
     </row>
     <row r="24" ht="99" customHeight="1">
-      <c r="A24" s="108" t="n"/>
-      <c r="B24" s="114" t="n"/>
-      <c r="C24" s="115" t="n"/>
-      <c r="D24" s="116" t="n"/>
-      <c r="E24" s="116" t="n"/>
-      <c r="F24" s="116" t="n"/>
-      <c r="G24" s="116" t="n"/>
-      <c r="H24" s="116" t="n"/>
-      <c r="I24" s="116" t="n"/>
-      <c r="J24" s="116" t="n"/>
-      <c r="K24" s="116" t="n"/>
-      <c r="L24" s="116" t="n"/>
-      <c r="M24" s="116" t="n"/>
-      <c r="N24" s="116" t="n"/>
-      <c r="O24" s="116" t="n"/>
-      <c r="P24" s="116" t="n"/>
-      <c r="Q24" s="116" t="n"/>
-      <c r="R24" s="116" t="n"/>
-      <c r="S24" s="116" t="n"/>
-      <c r="T24" s="116" t="n"/>
-      <c r="U24" s="116" t="n"/>
-      <c r="V24" s="116" t="n"/>
-      <c r="W24" s="116" t="n"/>
+      <c r="A24" s="115" t="n"/>
+      <c r="B24" s="110" t="n"/>
+      <c r="C24" s="114" t="n"/>
+      <c r="D24" s="115" t="n"/>
+      <c r="E24" s="115" t="n"/>
+      <c r="F24" s="115" t="n"/>
+      <c r="G24" s="115" t="n"/>
+      <c r="H24" s="115" t="n"/>
+      <c r="I24" s="115" t="n"/>
+      <c r="J24" s="115" t="n"/>
+      <c r="K24" s="115" t="n"/>
+      <c r="L24" s="115" t="n"/>
+      <c r="M24" s="115" t="n"/>
+      <c r="N24" s="115" t="n"/>
+      <c r="O24" s="115" t="n"/>
+      <c r="P24" s="115" t="n"/>
+      <c r="Q24" s="115" t="n"/>
+      <c r="R24" s="115" t="n"/>
+      <c r="S24" s="115" t="n"/>
+      <c r="T24" s="115" t="n"/>
+      <c r="U24" s="115" t="n"/>
+      <c r="V24" s="115" t="n"/>
+      <c r="W24" s="115" t="n"/>
       <c r="X24" s="117" t="n"/>
-      <c r="Y24" s="120" t="n"/>
-      <c r="Z24" s="121" t="n"/>
-      <c r="AA24" s="108" t="n"/>
+      <c r="Y24" s="118" t="n"/>
+      <c r="Z24" s="112" t="n"/>
+      <c r="AA24" s="115" t="n"/>
       <c r="AB24" s="113" t="n"/>
-      <c r="AC24" s="106" t="n"/>
-      <c r="AD24" s="152" t="n"/>
-      <c r="AE24" s="108" t="n"/>
-      <c r="AF24" s="151" t="n"/>
-      <c r="AG24" s="151" t="n"/>
-      <c r="AH24" s="151" t="n"/>
-      <c r="AI24" s="151" t="n"/>
-      <c r="AJ24" s="151" t="n"/>
-      <c r="AK24" s="152" t="n"/>
-      <c r="AL24" s="21" t="n"/>
-      <c r="AM24" s="22" t="n"/>
+      <c r="AC24" s="39" t="n"/>
+      <c r="AD24" s="148" t="n"/>
+      <c r="AE24" s="156" t="n"/>
+      <c r="AF24" s="147" t="n"/>
+      <c r="AG24" s="147" t="n"/>
+      <c r="AH24" s="147" t="n"/>
+      <c r="AI24" s="147" t="n"/>
+      <c r="AJ24" s="147" t="n"/>
+      <c r="AK24" s="148" t="n"/>
+      <c r="AL24" s="19" t="n"/>
+      <c r="AM24" s="20" t="n"/>
       <c r="AN24" s="5" t="n"/>
-      <c r="BK24" s="22" t="n"/>
+      <c r="BK24" s="20" t="n"/>
     </row>
     <row r="25" ht="99" customHeight="1">
-      <c r="A25" s="108" t="n"/>
-      <c r="B25" s="114" t="n"/>
-      <c r="C25" s="115" t="n"/>
-      <c r="D25" s="116" t="n"/>
-      <c r="E25" s="116" t="n"/>
-      <c r="F25" s="116" t="n"/>
-      <c r="G25" s="116" t="n"/>
-      <c r="H25" s="116" t="n"/>
-      <c r="I25" s="116" t="n"/>
-      <c r="J25" s="116" t="n"/>
-      <c r="K25" s="116" t="n"/>
-      <c r="L25" s="116" t="n"/>
-      <c r="M25" s="116" t="n"/>
-      <c r="N25" s="116" t="n"/>
-      <c r="O25" s="116" t="n"/>
-      <c r="P25" s="116" t="n"/>
-      <c r="Q25" s="116" t="n"/>
-      <c r="R25" s="116" t="n"/>
-      <c r="S25" s="116" t="n"/>
-      <c r="T25" s="116" t="n"/>
-      <c r="U25" s="116" t="n"/>
-      <c r="V25" s="116" t="n"/>
-      <c r="W25" s="116" t="n"/>
+      <c r="A25" s="115" t="n"/>
+      <c r="B25" s="110" t="n"/>
+      <c r="C25" s="114" t="n"/>
+      <c r="D25" s="115" t="n"/>
+      <c r="E25" s="115" t="n"/>
+      <c r="F25" s="115" t="n"/>
+      <c r="G25" s="115" t="n"/>
+      <c r="H25" s="115" t="n"/>
+      <c r="I25" s="115" t="n"/>
+      <c r="J25" s="115" t="n"/>
+      <c r="K25" s="115" t="n"/>
+      <c r="L25" s="115" t="n"/>
+      <c r="M25" s="115" t="n"/>
+      <c r="N25" s="115" t="n"/>
+      <c r="O25" s="115" t="n"/>
+      <c r="P25" s="115" t="n"/>
+      <c r="Q25" s="115" t="n"/>
+      <c r="R25" s="115" t="n"/>
+      <c r="S25" s="115" t="n"/>
+      <c r="T25" s="115" t="n"/>
+      <c r="U25" s="115" t="n"/>
+      <c r="V25" s="115" t="n"/>
+      <c r="W25" s="115" t="n"/>
       <c r="X25" s="117" t="n"/>
-      <c r="Y25" s="120" t="n"/>
-      <c r="Z25" s="121" t="n"/>
-      <c r="AA25" s="108" t="n"/>
+      <c r="Y25" s="118" t="n"/>
+      <c r="Z25" s="112" t="n"/>
+      <c r="AA25" s="115" t="n"/>
       <c r="AB25" s="113" t="n"/>
-      <c r="AC25" s="106" t="n"/>
-      <c r="AD25" s="152" t="n"/>
-      <c r="AE25" s="108" t="n"/>
-      <c r="AF25" s="151" t="n"/>
-      <c r="AG25" s="151" t="n"/>
-      <c r="AH25" s="151" t="n"/>
-      <c r="AI25" s="151" t="n"/>
-      <c r="AJ25" s="151" t="n"/>
-      <c r="AK25" s="152" t="n"/>
-      <c r="AL25" s="21" t="n"/>
-      <c r="AM25" s="22" t="n"/>
+      <c r="AC25" s="39" t="n"/>
+      <c r="AD25" s="148" t="n"/>
+      <c r="AE25" s="156" t="n"/>
+      <c r="AF25" s="147" t="n"/>
+      <c r="AG25" s="147" t="n"/>
+      <c r="AH25" s="147" t="n"/>
+      <c r="AI25" s="147" t="n"/>
+      <c r="AJ25" s="147" t="n"/>
+      <c r="AK25" s="148" t="n"/>
+      <c r="AL25" s="19" t="n"/>
+      <c r="AM25" s="20" t="n"/>
       <c r="AN25" s="5" t="n"/>
-      <c r="BK25" s="22" t="n"/>
+      <c r="BK25" s="20" t="n"/>
     </row>
     <row r="26" ht="99" customHeight="1" thickBot="1">
-      <c r="A26" s="108" t="n"/>
-      <c r="B26" s="114" t="n"/>
-      <c r="C26" s="122" t="n"/>
-      <c r="D26" s="124" t="n"/>
-      <c r="E26" s="124" t="n"/>
-      <c r="F26" s="124" t="n"/>
-      <c r="G26" s="124" t="n"/>
-      <c r="H26" s="124" t="n"/>
-      <c r="I26" s="124" t="n"/>
-      <c r="J26" s="124" t="n"/>
-      <c r="K26" s="124" t="n"/>
-      <c r="L26" s="124" t="n"/>
-      <c r="M26" s="124" t="n"/>
-      <c r="N26" s="124" t="n"/>
-      <c r="O26" s="124" t="n"/>
-      <c r="P26" s="124" t="n"/>
-      <c r="Q26" s="124" t="n"/>
-      <c r="R26" s="124" t="n"/>
-      <c r="S26" s="124" t="n"/>
-      <c r="T26" s="124" t="n"/>
-      <c r="U26" s="124" t="n"/>
-      <c r="V26" s="124" t="n"/>
-      <c r="W26" s="124" t="n"/>
-      <c r="X26" s="125" t="n"/>
-      <c r="Y26" s="126" t="n"/>
-      <c r="Z26" s="127" t="n"/>
-      <c r="AA26" s="128" t="n"/>
-      <c r="AB26" s="129" t="n"/>
-      <c r="AC26" s="106" t="n"/>
-      <c r="AD26" s="152" t="n"/>
-      <c r="AE26" s="108" t="n"/>
-      <c r="AF26" s="151" t="n"/>
-      <c r="AG26" s="151" t="n"/>
-      <c r="AH26" s="151" t="n"/>
-      <c r="AI26" s="151" t="n"/>
-      <c r="AJ26" s="151" t="n"/>
-      <c r="AK26" s="152" t="n"/>
-      <c r="AL26" s="21" t="n"/>
-      <c r="AM26" s="22" t="n"/>
+      <c r="A26" s="115" t="n"/>
+      <c r="B26" s="110" t="n"/>
+      <c r="C26" s="119" t="n"/>
+      <c r="D26" s="121" t="n"/>
+      <c r="E26" s="121" t="n"/>
+      <c r="F26" s="121" t="n"/>
+      <c r="G26" s="121" t="n"/>
+      <c r="H26" s="121" t="n"/>
+      <c r="I26" s="121" t="n"/>
+      <c r="J26" s="121" t="n"/>
+      <c r="K26" s="121" t="n"/>
+      <c r="L26" s="121" t="n"/>
+      <c r="M26" s="121" t="n"/>
+      <c r="N26" s="121" t="n"/>
+      <c r="O26" s="121" t="n"/>
+      <c r="P26" s="121" t="n"/>
+      <c r="Q26" s="121" t="n"/>
+      <c r="R26" s="121" t="n"/>
+      <c r="S26" s="121" t="n"/>
+      <c r="T26" s="121" t="n"/>
+      <c r="U26" s="121" t="n"/>
+      <c r="V26" s="121" t="n"/>
+      <c r="W26" s="121" t="n"/>
+      <c r="X26" s="122" t="n"/>
+      <c r="Y26" s="123" t="n"/>
+      <c r="Z26" s="124" t="n"/>
+      <c r="AA26" s="121" t="n"/>
+      <c r="AB26" s="125" t="n"/>
+      <c r="AC26" s="39" t="n"/>
+      <c r="AD26" s="148" t="n"/>
+      <c r="AE26" s="156" t="n"/>
+      <c r="AF26" s="147" t="n"/>
+      <c r="AG26" s="147" t="n"/>
+      <c r="AH26" s="147" t="n"/>
+      <c r="AI26" s="147" t="n"/>
+      <c r="AJ26" s="147" t="n"/>
+      <c r="AK26" s="148" t="n"/>
+      <c r="AL26" s="19" t="n"/>
+      <c r="AM26" s="20" t="n"/>
       <c r="AN26" s="5" t="n"/>
-      <c r="BK26" s="22" t="n"/>
+      <c r="BK26" s="20" t="n"/>
     </row>
     <row r="27" ht="33" customHeight="1"/>
     <row r="28" ht="33" customHeight="1"/>
     <row r="29" ht="33" customHeight="1"/>
   </sheetData>
-  <mergeCells count="73">
+  <mergeCells count="72">
     <mergeCell ref="O5:O6"/>
+    <mergeCell ref="Q14:S14"/>
+    <mergeCell ref="AE19:AK19"/>
+    <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="Q14:S14"/>
-    <mergeCell ref="L2:P2"/>
     <mergeCell ref="W5:W6"/>
-    <mergeCell ref="AH5:AH6"/>
-    <mergeCell ref="AE19:AK19"/>
     <mergeCell ref="Y5:Y6"/>
     <mergeCell ref="Q10:S10"/>
     <mergeCell ref="Q4:S6"/>
-    <mergeCell ref="AD5:AE5"/>
+    <mergeCell ref="L2:AH2"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="F5:F6"/>
+    <mergeCell ref="AD5:AE5"/>
+    <mergeCell ref="AB5:AB6"/>
     <mergeCell ref="AE24:AK24"/>
     <mergeCell ref="AA5:AA6"/>
     <mergeCell ref="AC18:AD18"/>
+    <mergeCell ref="L5:L6"/>
     <mergeCell ref="AC5:AC6"/>
-    <mergeCell ref="L5:L6"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="AK5:AK6"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="C4:P4"/>
     <mergeCell ref="AF5:AF6"/>
-    <mergeCell ref="AC24:AD24"/>
+    <mergeCell ref="L15:P15"/>
     <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="L15:P15"/>
     <mergeCell ref="AE20:AK20"/>
     <mergeCell ref="AE26:AK26"/>
-    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="AC24:AD24"/>
+    <mergeCell ref="AE16:AK17"/>
     <mergeCell ref="AC23:AD23"/>
     <mergeCell ref="AE25:AK25"/>
     <mergeCell ref="X5:X6"/>
+    <mergeCell ref="Z5:Z6"/>
     <mergeCell ref="I5:I6"/>
-    <mergeCell ref="Z5:Z6"/>
+    <mergeCell ref="AC26:AD26"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="AE22:AK22"/>
     <mergeCell ref="G5:G6"/>
-    <mergeCell ref="Q11:S11"/>
     <mergeCell ref="AJ5:AJ6"/>
-    <mergeCell ref="R2:AH2"/>
-    <mergeCell ref="AC26:AD26"/>
     <mergeCell ref="U5:U6"/>
-    <mergeCell ref="AE22:AK22"/>
     <mergeCell ref="AC20:AD20"/>
     <mergeCell ref="AE18:AK18"/>
     <mergeCell ref="AC19:AD19"/>
@@ -3387,29 +3386,28 @@
     <mergeCell ref="AE21:AK21"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="AC22:AD22"/>
     <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="AC22:AD22"/>
     <mergeCell ref="AC16:AD17"/>
     <mergeCell ref="D5:D6"/>
+    <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="P5:P6"/>
-    <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="C16:X16"/>
+    <mergeCell ref="AI5:AI6"/>
     <mergeCell ref="H5:H6"/>
-    <mergeCell ref="AI5:AI6"/>
     <mergeCell ref="AC21:AD21"/>
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="AE23:AK23"/>
-    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="Y16:AB16"/>
     <mergeCell ref="C5:C6"/>
-    <mergeCell ref="Y16:AB16"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="Q8:S8"/>
     <mergeCell ref="T5:T6"/>
     <mergeCell ref="V5:V6"/>
-    <mergeCell ref="AB5:AB6"/>
+    <mergeCell ref="K5:K6"/>
     <mergeCell ref="T4:AK4"/>
-    <mergeCell ref="AE16:AK17"/>
+    <mergeCell ref="M5:M6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1181102362204725" right="0.1181102362204725" top="0.7480314960629921" bottom="0.3543307086614174" header="0.3149606299212598" footer="0.3149606299212598"/>

--- a/Отчет_20-05-2025.xlsx
+++ b/Отчет_20-05-2025.xlsx
@@ -1579,7 +1579,7 @@
     <row r="2" ht="73.5" customHeight="1">
       <c r="A2" s="70" t="inlineStr">
         <is>
-          <t>Дата:  20.05.2025  2025 г.</t>
+          <t>Дата:  20.05.2025</t>
         </is>
       </c>
       <c r="L2" s="70" t="inlineStr">
